--- a/blocks_transformed.xlsx
+++ b/blocks_transformed.xlsx
@@ -15501,23 +15501,6 @@
       <c r="L366"/>
       <c r="M366"/>
     </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B367"/>
-      <c r="C367"/>
-      <c r="D367"/>
-      <c r="E367"/>
-      <c r="F367"/>
-      <c r="G367"/>
-      <c r="H367"/>
-      <c r="I367"/>
-      <c r="J367"/>
-      <c r="K367"/>
-      <c r="L367"/>
-      <c r="M367"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -32406,20 +32389,6 @@
       <c r="I366"/>
       <c r="J366"/>
     </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B367"/>
-      <c r="C367"/>
-      <c r="D367"/>
-      <c r="E367"/>
-      <c r="F367"/>
-      <c r="G367"/>
-      <c r="H367"/>
-      <c r="I367"/>
-      <c r="J367"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -39731,16 +39700,6 @@
       <c r="E366"/>
       <c r="F366"/>
     </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B367"/>
-      <c r="C367"/>
-      <c r="D367"/>
-      <c r="E367"/>
-      <c r="F367"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -45962,15 +45921,6 @@
       <c r="D366"/>
       <c r="E366"/>
     </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B367"/>
-      <c r="C367"/>
-      <c r="D367"/>
-      <c r="E367"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -56704,19 +56654,6 @@
       </c>
       <c r="I378"/>
     </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-      <c r="F379"/>
-      <c r="G379"/>
-      <c r="H379"/>
-      <c r="I379"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -56772,14 +56709,14 @@
       </c>
       <c r="B3"/>
       <c r="C3" t="n">
-        <v>0.00570583170068328</v>
+        <v>0.00570592174317097</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="n">
         <v>0.0209213091305784</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00522329052121595</v>
+        <v>0.0209213091305784</v>
       </c>
       <c r="G3" t="n">
         <v>0.026596709540236</v>
@@ -56792,14 +56729,14 @@
       </c>
       <c r="B4"/>
       <c r="C4" t="n">
-        <v>0.00600494973329591</v>
+        <v>0.00600472395844776</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="n">
         <v>0.014930301453524</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0044619539183488</v>
+        <v>0.014930301453524</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0119931791719496</v>
@@ -56812,14 +56749,14 @@
       </c>
       <c r="B5"/>
       <c r="C5" t="n">
-        <v>0.0091694201234902</v>
+        <v>0.00916949395588329</v>
       </c>
       <c r="D5"/>
       <c r="E5" t="n">
         <v>-0.00682136251527066</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0196988695361813</v>
+        <v>-0.00682136251527066</v>
       </c>
       <c r="G5" t="n">
         <v>0.0557293884846901</v>
@@ -56832,14 +56769,14 @@
       </c>
       <c r="B6"/>
       <c r="C6" t="n">
-        <v>0.00678166900747401</v>
+        <v>0.00678179567619663</v>
       </c>
       <c r="D6"/>
       <c r="E6" t="n">
         <v>-0.00162716575804378</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0212545028605344</v>
+        <v>-0.00162716575804378</v>
       </c>
       <c r="G6" t="n">
         <v>-0.00246333780902663</v>
@@ -56852,14 +56789,14 @@
       </c>
       <c r="B7"/>
       <c r="C7" t="n">
-        <v>0.00593424819649702</v>
+        <v>0.00593419004906925</v>
       </c>
       <c r="D7"/>
       <c r="E7" t="n">
         <v>-0.00431119720502648</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0250504182649562</v>
+        <v>-0.00431119720502648</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0789270043153438</v>
@@ -56872,14 +56809,14 @@
       </c>
       <c r="B8"/>
       <c r="C8" t="n">
-        <v>0.005219880443883</v>
+        <v>0.00521996365668009</v>
       </c>
       <c r="D8"/>
       <c r="E8" t="n">
         <v>0.0136724501881385</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0307196694154634</v>
+        <v>0.0136724501881385</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0737686954702799</v>
@@ -56892,14 +56829,14 @@
       </c>
       <c r="B9"/>
       <c r="C9" t="n">
-        <v>0.0044590548104706</v>
+        <v>0.00445884861253099</v>
       </c>
       <c r="D9"/>
       <c r="E9" t="n">
         <v>0.0238026088040821</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0082600246677611</v>
+        <v>0.0238026088040821</v>
       </c>
       <c r="G9" t="n">
         <v>0.0524552796212481</v>
@@ -56912,14 +56849,14 @@
       </c>
       <c r="B10"/>
       <c r="C10" t="n">
-        <v>0.00431777160354674</v>
+        <v>0.00431778296595731</v>
       </c>
       <c r="D10"/>
       <c r="E10" t="n">
         <v>-0.0038090568580631</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0103495356338144</v>
+        <v>-0.0038090568580631</v>
       </c>
       <c r="G10" t="n">
         <v>0.0032800965012747</v>
@@ -56932,14 +56869,14 @@
       </c>
       <c r="B11"/>
       <c r="C11" t="n">
-        <v>0.00401241323069224</v>
+        <v>0.00401267071345579</v>
       </c>
       <c r="D11"/>
       <c r="E11" t="n">
         <v>0.0200194998984986</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00679366455936536</v>
+        <v>0.0200194998984986</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0631050957747572</v>
@@ -56952,14 +56889,14 @@
       </c>
       <c r="B12"/>
       <c r="C12" t="n">
-        <v>0.00405650824054637</v>
+        <v>0.00405639475589847</v>
       </c>
       <c r="D12"/>
       <c r="E12" t="n">
         <v>0.00951674269795877</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.000736077515074651</v>
+        <v>0.00951674269795877</v>
       </c>
       <c r="G12" t="n">
         <v>0.035000825383154</v>
@@ -56972,14 +56909,14 @@
       </c>
       <c r="B13"/>
       <c r="C13" t="n">
-        <v>0.00418707755155001</v>
+        <v>0.0041869650265256</v>
       </c>
       <c r="D13"/>
       <c r="E13" t="n">
         <v>0.069745605494012</v>
       </c>
       <c r="F13" t="n">
-        <v>0.021310269911567</v>
+        <v>0.069745605494012</v>
       </c>
       <c r="G13" t="n">
         <v>0.0694515253335695</v>
@@ -56992,14 +56929,14 @@
       </c>
       <c r="B14"/>
       <c r="C14" t="n">
-        <v>0.0032268446104462</v>
+        <v>0.00322684697477094</v>
       </c>
       <c r="D14"/>
       <c r="E14" t="n">
         <v>-0.054720401427554</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.00632728044017616</v>
+        <v>-0.054720401427554</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0144044469347806</v>
@@ -57012,14 +56949,14 @@
       </c>
       <c r="B15"/>
       <c r="C15" t="n">
-        <v>0.000268933702948893</v>
+        <v>0.000268976361877282</v>
       </c>
       <c r="D15"/>
       <c r="E15" t="n">
         <v>-0.00221988662965389</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00427737932643302</v>
+        <v>-0.00221988662965389</v>
       </c>
       <c r="G15" t="n">
         <v>-0.00181443289093064</v>
@@ -57032,7 +56969,7 @@
       </c>
       <c r="B16"/>
       <c r="C16" t="n">
-        <v>-0.00127990597949745</v>
+        <v>-0.00127997535603885</v>
       </c>
       <c r="D16" t="n">
         <v>0.00525333435896469</v>
@@ -57041,7 +56978,7 @@
         <v>0.00555351550984851</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0106234853164366</v>
+        <v>0.00555351550984851</v>
       </c>
       <c r="G16" t="n">
         <v>0.0965363325004196</v>
@@ -57054,7 +56991,7 @@
       </c>
       <c r="B17"/>
       <c r="C17" t="n">
-        <v>-0.00145684552451231</v>
+        <v>-0.00145660375476853</v>
       </c>
       <c r="D17" t="n">
         <v>0.00257694927289132</v>
@@ -57063,7 +57000,7 @@
         <v>0.00272016565428146</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0000655056667917542</v>
+        <v>0.00272016565428146</v>
       </c>
       <c r="G17" t="n">
         <v>0.101246762287492</v>
@@ -57076,7 +57013,7 @@
       </c>
       <c r="B18"/>
       <c r="C18" t="n">
-        <v>-0.000410022481195593</v>
+        <v>-0.000410076835153816</v>
       </c>
       <c r="D18" t="n">
         <v>0.0183448239308426</v>
@@ -57085,7 +57022,7 @@
         <v>0.0195196049354154</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0119363907484873</v>
+        <v>0.0195196049354154</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0939900046314373</v>
@@ -57098,7 +57035,7 @@
       </c>
       <c r="B19"/>
       <c r="C19" t="n">
-        <v>0.000955674342995483</v>
+        <v>0.0009555418236733</v>
       </c>
       <c r="D19" t="n">
         <v>-0.0120531740547527</v>
@@ -57107,7 +57044,7 @@
         <v>-0.0126313880855196</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0195163523742616</v>
+        <v>-0.0126313880855196</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0420854786124307</v>
@@ -57120,7 +57057,7 @@
       </c>
       <c r="B20"/>
       <c r="C20" t="n">
-        <v>0.00203840003799405</v>
+        <v>0.00203842558774259</v>
       </c>
       <c r="D20" t="n">
         <v>0.00265967830915281</v>
@@ -57129,7 +57066,7 @@
         <v>0.00280802662616919</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0271258227293498</v>
+        <v>0.00280802662616919</v>
       </c>
       <c r="G20" t="n">
         <v>0.0156142346193837</v>
@@ -57142,7 +57079,7 @@
       </c>
       <c r="B21"/>
       <c r="C21" t="n">
-        <v>0.00089710190544956</v>
+        <v>0.000897068829450287</v>
       </c>
       <c r="D21" t="n">
         <v>-0.0191253640980329</v>
@@ -57151,7 +57088,7 @@
         <v>-0.0199725419128529</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0222660480176771</v>
+        <v>-0.0199725419128529</v>
       </c>
       <c r="G21" t="n">
         <v>0.0136835839024743</v>
@@ -57164,7 +57101,7 @@
       </c>
       <c r="B22"/>
       <c r="C22" t="n">
-        <v>-0.000184355940806569</v>
+        <v>-0.000184288460567839</v>
       </c>
       <c r="D22" t="n">
         <v>0.0194538024590281</v>
@@ -57173,7 +57110,7 @@
         <v>0.0207111259080621</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0137336324564803</v>
+        <v>0.0207111259080621</v>
       </c>
       <c r="G22" t="n">
         <v>0.0925151663822295</v>
@@ -57186,7 +57123,7 @@
       </c>
       <c r="B23"/>
       <c r="C23" t="n">
-        <v>-0.00100439924855911</v>
+        <v>-0.00100469625235</v>
       </c>
       <c r="D23" t="n">
         <v>-0.00368451159249883</v>
@@ -57195,7 +57132,7 @@
         <v>-0.00387770363436601</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.01711604676367</v>
+        <v>-0.00387770363436601</v>
       </c>
       <c r="G23" t="n">
         <v>0.0476265239051825</v>
@@ -57208,7 +57145,7 @@
       </c>
       <c r="B24"/>
       <c r="C24" t="n">
-        <v>0.000487865400526477</v>
+        <v>0.000488039656404649</v>
       </c>
       <c r="D24" t="n">
         <v>-0.010779137257575</v>
@@ -57217,7 +57154,7 @@
         <v>-0.0113032882448025</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.00693112951546704</v>
+        <v>-0.0113032882448025</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0488177544849675</v>
@@ -57230,7 +57167,7 @@
       </c>
       <c r="B25"/>
       <c r="C25" t="n">
-        <v>0.00408148602358516</v>
+        <v>0.00408150536345753</v>
       </c>
       <c r="D25" t="n">
         <v>-0.00855983727601073</v>
@@ -57239,7 +57176,7 @@
         <v>-0.00898617047887784</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00207990466458341</v>
+        <v>-0.00898617047887784</v>
       </c>
       <c r="G25" t="n">
         <v>0.0644176993120515</v>
@@ -57252,7 +57189,7 @@
       </c>
       <c r="B26"/>
       <c r="C26" t="n">
-        <v>0.00260315617215978</v>
+        <v>0.00260318963182993</v>
       </c>
       <c r="D26" t="n">
         <v>0.0392722384321527</v>
@@ -57261,7 +57198,7 @@
         <v>0.0422289069131585</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0196024314490675</v>
+        <v>0.0422289069131585</v>
       </c>
       <c r="G26" t="n">
         <v>-0.00812950327329975</v>
@@ -57274,7 +57211,7 @@
       </c>
       <c r="B27"/>
       <c r="C27" t="n">
-        <v>0.000845441547772552</v>
+        <v>0.000845489554959666</v>
       </c>
       <c r="D27" t="n">
         <v>-0.00108168296143463</v>
@@ -57283,7 +57220,7 @@
         <v>-0.00113983194275002</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.00993602803480398</v>
+        <v>-0.00113983194275002</v>
       </c>
       <c r="G27" t="n">
         <v>-0.118568970949206</v>
@@ -57296,7 +57233,7 @@
       </c>
       <c r="B28"/>
       <c r="C28" t="n">
-        <v>0.00160974251755475</v>
+        <v>0.00160972088272349</v>
       </c>
       <c r="D28" t="n">
         <v>0.00732339851600416</v>
@@ -57305,7 +57242,7 @@
         <v>0.00774933916382681</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0209343053868132</v>
+        <v>0.00774933916382681</v>
       </c>
       <c r="G28" t="n">
         <v>-0.0568293303400047</v>
@@ -57318,7 +57255,7 @@
       </c>
       <c r="B29"/>
       <c r="C29" t="n">
-        <v>0.00188008937116768</v>
+        <v>0.00188009763293806</v>
       </c>
       <c r="D29" t="n">
         <v>-0.00730075360297988</v>
@@ -57327,7 +57264,7 @@
         <v>-0.00766927995540012</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.00128792126801347</v>
+        <v>-0.00766927995540012</v>
       </c>
       <c r="G29" t="n">
         <v>-0.0630074943739212</v>
@@ -57340,7 +57277,7 @@
       </c>
       <c r="B30"/>
       <c r="C30" t="n">
-        <v>0.00164144394801458</v>
+        <v>0.00164135616024597</v>
       </c>
       <c r="D30" t="n">
         <v>0.019039488550038</v>
@@ -57349,7 +57286,7 @@
         <v>0.0202660906140069</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00867668938792843</v>
+        <v>0.0202660906140069</v>
       </c>
       <c r="G30" t="n">
         <v>0.0533667130392272</v>
@@ -57362,7 +57299,7 @@
       </c>
       <c r="B31"/>
       <c r="C31" t="n">
-        <v>0.00148334834025432</v>
+        <v>0.00148353682717861</v>
       </c>
       <c r="D31" t="n">
         <v>0.0186220310235119</v>
@@ -57371,7 +57308,7 @@
         <v>0.019817454314615</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.00232720836468747</v>
+        <v>0.019817454314615</v>
       </c>
       <c r="G31" t="n">
         <v>-0.0727265289944885</v>
@@ -57384,7 +57321,7 @@
       </c>
       <c r="B32"/>
       <c r="C32" t="n">
-        <v>0.00240082477655257</v>
+        <v>0.00240065898390673</v>
       </c>
       <c r="D32" t="n">
         <v>-0.00958645973017314</v>
@@ -57393,7 +57330,7 @@
         <v>-0.0100590792072053</v>
       </c>
       <c r="F32" t="n">
-        <v>0.000507106366483878</v>
+        <v>-0.0100590792072053</v>
       </c>
       <c r="G32" t="n">
         <v>0.0368161211002782</v>
@@ -57406,7 +57343,7 @@
       </c>
       <c r="B33"/>
       <c r="C33" t="n">
-        <v>0.00172143987418139</v>
+        <v>0.00172144995462586</v>
       </c>
       <c r="D33" t="n">
         <v>-0.0247301057791569</v>
@@ -57415,7 +57352,7 @@
         <v>-0.0257533578503137</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0146958770395464</v>
+        <v>-0.0257533578503137</v>
       </c>
       <c r="G33" t="n">
         <v>0.00670991696340995</v>
@@ -57428,7 +57365,7 @@
       </c>
       <c r="B34"/>
       <c r="C34" t="n">
-        <v>0.00314128386723178</v>
+        <v>0.00314131471332457</v>
       </c>
       <c r="D34" t="n">
         <v>0.0103337159713721</v>
@@ -57437,7 +57374,7 @@
         <v>0.0109513212801371</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00683415313015745</v>
+        <v>0.0109513212801371</v>
       </c>
       <c r="G34" t="n">
         <v>-0.0131571358576528</v>
@@ -57450,7 +57387,7 @@
       </c>
       <c r="B35"/>
       <c r="C35" t="n">
-        <v>0.00204579439102126</v>
+        <v>0.0020457217131078</v>
       </c>
       <c r="D35" t="n">
         <v>0.00659418198636263</v>
@@ -57459,7 +57396,7 @@
         <v>0.00697546061978827</v>
       </c>
       <c r="F35" t="n">
-        <v>0.00824608429828455</v>
+        <v>0.00697546061978827</v>
       </c>
       <c r="G35" t="n">
         <v>0.0662248983380183</v>
@@ -57472,7 +57409,7 @@
       </c>
       <c r="B36"/>
       <c r="C36" t="n">
-        <v>0.00183332465054287</v>
+        <v>0.00183362219068739</v>
       </c>
       <c r="D36" t="n">
         <v>0.0165308050912238</v>
@@ -57481,7 +57418,7 @@
         <v>0.017573530332645</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0197975102104504</v>
+        <v>0.017573530332645</v>
       </c>
       <c r="G36" t="n">
         <v>-0.0486252489033783</v>
@@ -57494,7 +57431,7 @@
       </c>
       <c r="B37"/>
       <c r="C37" t="n">
-        <v>0.0031119979489147</v>
+        <v>0.00311178802517942</v>
       </c>
       <c r="D37" t="n">
         <v>-0.00799770902952357</v>
@@ -57503,7 +57440,7 @@
         <v>-0.00839850817091303</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.0333433777925216</v>
+        <v>-0.00839850817091303</v>
       </c>
       <c r="G37" t="n">
         <v>-0.0931376916113287</v>
@@ -57516,7 +57453,7 @@
       </c>
       <c r="B38"/>
       <c r="C38" t="n">
-        <v>0.00453760633028377</v>
+        <v>0.00453736747699374</v>
       </c>
       <c r="D38" t="n">
         <v>0.00976531975967188</v>
@@ -57525,7 +57462,7 @@
         <v>0.01034596184821</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.00462646119870325</v>
+        <v>0.01034596184821</v>
       </c>
       <c r="G38" t="n">
         <v>-0.0830662435748373</v>
@@ -57538,7 +57475,7 @@
       </c>
       <c r="B39"/>
       <c r="C39" t="n">
-        <v>0.00280100944886374</v>
+        <v>0.00280131269561146</v>
       </c>
       <c r="D39" t="n">
         <v>0.0231996573710491</v>
@@ -57547,7 +57484,7 @@
         <v>0.0247458144671731</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0605538670742454</v>
+        <v>0.0247458144671731</v>
       </c>
       <c r="G39" t="n">
         <v>-0.035090303079115</v>
@@ -57560,7 +57497,7 @@
       </c>
       <c r="B40"/>
       <c r="C40" t="n">
-        <v>0.00357005391702492</v>
+        <v>0.00356997629214284</v>
       </c>
       <c r="D40" t="n">
         <v>-0.0127742338070269</v>
@@ -57569,7 +57506,7 @@
         <v>-0.0133822320649148</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.0161685140906878</v>
+        <v>-0.0133822320649148</v>
       </c>
       <c r="G40" t="n">
         <v>-0.060899867562477</v>
@@ -57582,7 +57519,7 @@
       </c>
       <c r="B41"/>
       <c r="C41" t="n">
-        <v>0.00174600004960768</v>
+        <v>0.00174614709725462</v>
       </c>
       <c r="D41" t="n">
         <v>0.0123994108944108</v>
@@ -57591,7 +57528,7 @@
         <v>0.013154231344739</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0191235869812667</v>
+        <v>0.013154231344739</v>
       </c>
       <c r="G41" t="n">
         <v>0.0346226126605238</v>
@@ -57604,7 +57541,7 @@
       </c>
       <c r="B42"/>
       <c r="C42" t="n">
-        <v>0.00126804240666312</v>
+        <v>0.00126778615695544</v>
       </c>
       <c r="D42" t="n">
         <v>-0.00904099563435423</v>
@@ -57613,7 +57550,7 @@
         <v>-0.00948940226426753</v>
       </c>
       <c r="F42" t="n">
-        <v>0.00332062321305227</v>
+        <v>-0.00948940226426753</v>
       </c>
       <c r="G42" t="n">
         <v>-0.0436599785258931</v>
@@ -57626,7 +57563,7 @@
       </c>
       <c r="B43"/>
       <c r="C43" t="n">
-        <v>0.0027935601968343</v>
+        <v>0.00279382711977672</v>
       </c>
       <c r="D43" t="n">
         <v>-0.0086714396199099</v>
@@ -57635,7 +57572,7 @@
         <v>-0.00910287250835218</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0314364954157198</v>
+        <v>-0.00910287250835218</v>
       </c>
       <c r="G43" t="n">
         <v>-0.087494567846381</v>
@@ -57648,7 +57585,7 @@
       </c>
       <c r="B44"/>
       <c r="C44" t="n">
-        <v>0.00213386396405291</v>
+        <v>0.0021337993136723</v>
       </c>
       <c r="D44" t="n">
         <v>0.00721192091264244</v>
@@ -57657,7 +57594,7 @@
         <v>0.00763139829015813</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.0208654633140082</v>
+        <v>0.00763139829015813</v>
       </c>
       <c r="G44" t="n">
         <v>0.0324686949371484</v>
@@ -57670,7 +57607,7 @@
       </c>
       <c r="B45"/>
       <c r="C45" t="n">
-        <v>0.00295257339826849</v>
+        <v>0.00295253166800347</v>
       </c>
       <c r="D45" t="n">
         <v>0.0196412825602761</v>
@@ -57679,7 +57616,7 @@
         <v>0.0209127312914852</v>
       </c>
       <c r="F45" t="n">
-        <v>0.00394704243396005</v>
+        <v>0.0209127312914852</v>
       </c>
       <c r="G45" t="n">
         <v>-0.0429163887975648</v>
@@ -57692,7 +57629,7 @@
       </c>
       <c r="B46"/>
       <c r="C46" t="n">
-        <v>0.00113300232071234</v>
+        <v>0.00113296783779182</v>
       </c>
       <c r="D46" t="n">
         <v>-0.00869123856010479</v>
@@ -57701,7 +57638,7 @@
         <v>-0.00912386181091218</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0039589883978195</v>
+        <v>-0.00912386181091218</v>
       </c>
       <c r="G46" t="n">
         <v>0.131997831623798</v>
@@ -57714,7 +57651,7 @@
       </c>
       <c r="B47"/>
       <c r="C47" t="n">
-        <v>0.00443839514272959</v>
+        <v>0.00443840151632857</v>
       </c>
       <c r="D47" t="n">
         <v>0.0236381295749655</v>
@@ -57723,7 +57660,7 @@
         <v>0.0252189982385582</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.00643798413023022</v>
+        <v>0.0252189982385582</v>
       </c>
       <c r="G47" t="n">
         <v>0.0185292831830663</v>
@@ -57736,7 +57673,7 @@
       </c>
       <c r="B48"/>
       <c r="C48" t="n">
-        <v>0.00138881250308698</v>
+        <v>0.00138880410420583</v>
       </c>
       <c r="D48" t="n">
         <v>-0.00965505605257899</v>
@@ -57745,7 +57682,7 @@
         <v>-0.0101303580419891</v>
       </c>
       <c r="F48" t="n">
-        <v>0.00320840041915771</v>
+        <v>-0.0101303580419891</v>
       </c>
       <c r="G48" t="n">
         <v>-0.111373820369808</v>
@@ -57758,7 +57695,7 @@
       </c>
       <c r="B49"/>
       <c r="C49" t="n">
-        <v>0.00135666095867037</v>
+        <v>0.00135670626228324</v>
       </c>
       <c r="D49" t="n">
         <v>-0.00499843512288045</v>
@@ -57767,7 +57704,7 @@
         <v>-0.00525697573299677</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.00648520173078593</v>
+        <v>-0.00525697573299677</v>
       </c>
       <c r="G49" t="n">
         <v>-0.148618349451832</v>
@@ -57780,7 +57717,7 @@
       </c>
       <c r="B50"/>
       <c r="C50" t="n">
-        <v>-0.000101495286146669</v>
+        <v>-0.000101560349749175</v>
       </c>
       <c r="D50" t="n">
         <v>-0.0147667813126606</v>
@@ -57789,7 +57726,7 @@
         <v>-0.015454166778083</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.022527767943366</v>
+        <v>-0.015454166778083</v>
       </c>
       <c r="G50" t="n">
         <v>0.0791623400925303</v>
@@ -57802,7 +57739,7 @@
       </c>
       <c r="B51"/>
       <c r="C51" t="n">
-        <v>0.00519788828281698</v>
+        <v>0.00519795528219635</v>
       </c>
       <c r="D51" t="n">
         <v>0.0280637312086154</v>
@@ -57811,7 +57748,7 @@
         <v>0.0300069965584839</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0168251535919937</v>
+        <v>0.0300069965584839</v>
       </c>
       <c r="G51" t="n">
         <v>-0.0361728570192756</v>
@@ -57824,7 +57761,7 @@
       </c>
       <c r="B52"/>
       <c r="C52" t="n">
-        <v>0.00464087419512538</v>
+        <v>0.00464066767744287</v>
       </c>
       <c r="D52" t="n">
         <v>0.0126075090402584</v>
@@ -57833,7 +57770,7 @@
         <v>0.0133763584525619</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.026522574289578</v>
+        <v>0.0133763584525619</v>
       </c>
       <c r="G52" t="n">
         <v>0.193041322983715</v>
@@ -57846,7 +57783,7 @@
       </c>
       <c r="B53"/>
       <c r="C53" t="n">
-        <v>0.00317321048662889</v>
+        <v>0.00317339621752488</v>
       </c>
       <c r="D53" t="n">
         <v>-0.0115832600845436</v>
@@ -57855,7 +57792,7 @@
         <v>-0.012142157793809</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0186861298553915</v>
+        <v>-0.012142157793809</v>
       </c>
       <c r="G53" t="n">
         <v>0.169736044131593</v>
@@ -57868,7 +57805,7 @@
       </c>
       <c r="B54"/>
       <c r="C54" t="n">
-        <v>0.00219493890536215</v>
+        <v>0.00219491103113745</v>
       </c>
       <c r="D54" t="n">
         <v>-0.0000949609483620328</v>
@@ -57877,7 +57814,7 @@
         <v>-0.000100032742896161</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.000101647908233637</v>
+        <v>-0.000100032742896161</v>
       </c>
       <c r="G54" t="n">
         <v>0.0322351307821203</v>
@@ -57890,7 +57827,7 @@
       </c>
       <c r="B55"/>
       <c r="C55" t="n">
-        <v>0.00337676517084384</v>
+        <v>0.00337679860120188</v>
       </c>
       <c r="D55" t="n">
         <v>0.0173898415064779</v>
@@ -57899,7 +57836,7 @@
         <v>0.018494706191853</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0134741022438223</v>
+        <v>0.018494706191853</v>
       </c>
       <c r="G55" t="n">
         <v>0.00170181017666415</v>
@@ -57912,7 +57849,7 @@
       </c>
       <c r="B56"/>
       <c r="C56" t="n">
-        <v>0.00552475830315036</v>
+        <v>0.00552479234491399</v>
       </c>
       <c r="D56" t="n">
         <v>0.00901746436965789</v>
@@ -57921,7 +57858,7 @@
         <v>0.00955033074224776</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0164069130701603</v>
+        <v>0.00955033074224776</v>
       </c>
       <c r="G56" t="n">
         <v>0.113738173853273</v>
@@ -57934,7 +57871,7 @@
       </c>
       <c r="B57"/>
       <c r="C57" t="n">
-        <v>0.00832585473915248</v>
+        <v>0.00832585419489851</v>
       </c>
       <c r="D57" t="n">
         <v>0.0274030130212157</v>
@@ -57943,7 +57880,7 @@
         <v>0.0292908108505712</v>
       </c>
       <c r="F57" t="n">
-        <v>0.00698459909407356</v>
+        <v>0.0292908108505712</v>
       </c>
       <c r="G57" t="n">
         <v>0.0776110568014374</v>
@@ -57956,7 +57893,7 @@
       </c>
       <c r="B58"/>
       <c r="C58" t="n">
-        <v>0.0106400976356102</v>
+        <v>0.0106398646594577</v>
       </c>
       <c r="D58" t="n">
         <v>0.0612332388479651</v>
@@ -57965,7 +57902,7 @@
         <v>0.0665765433609566</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0186450974974504</v>
+        <v>0.0665765433609566</v>
       </c>
       <c r="G58" t="n">
         <v>0.117559251262208</v>
@@ -57978,7 +57915,7 @@
       </c>
       <c r="B59"/>
       <c r="C59" t="n">
-        <v>0.00277178478377449</v>
+        <v>0.0027717905404514</v>
       </c>
       <c r="D59" t="n">
         <v>-0.0371195911242417</v>
@@ -57987,7 +57924,7 @@
         <v>-0.0384181262118597</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.00303675936903547</v>
+        <v>-0.0384181262118597</v>
       </c>
       <c r="G59" t="n">
         <v>-0.050057494788355</v>
@@ -58000,7 +57937,7 @@
       </c>
       <c r="B60"/>
       <c r="C60" t="n">
-        <v>0.00564061755600864</v>
+        <v>0.00564088194050782</v>
       </c>
       <c r="D60" t="n">
         <v>0.00200212536515254</v>
@@ -58009,7 +57946,7 @@
         <v>0.00211272242158955</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0174154949441934</v>
+        <v>0.00211272242158955</v>
       </c>
       <c r="G60" t="n">
         <v>0.0899490589001495</v>
@@ -58022,7 +57959,7 @@
       </c>
       <c r="B61"/>
       <c r="C61" t="n">
-        <v>0.00239888585203252</v>
+        <v>0.0023988146604057</v>
       </c>
       <c r="D61" t="n">
         <v>0.00855717957272839</v>
@@ -58031,7 +57968,7 @@
         <v>0.00906101156185368</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0143747317065497</v>
+        <v>0.00906101156185368</v>
       </c>
       <c r="G61" t="n">
         <v>0.0351188835228164</v>
@@ -58044,7 +57981,7 @@
       </c>
       <c r="B62"/>
       <c r="C62" t="n">
-        <v>0.000394638647089884</v>
+        <v>0.000394635014220324</v>
       </c>
       <c r="D62" t="n">
         <v>-0.00926930422209438</v>
@@ -58053,13 +57990,13 @@
         <v>-0.00972764633045653</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.0424428660683813</v>
+        <v>-0.00972764633045653</v>
       </c>
       <c r="G62" t="n">
         <v>0.0268738871400105</v>
       </c>
       <c r="H62" t="n">
-        <v>9.496413162275</v>
+        <v>9.47143481927294</v>
       </c>
     </row>
     <row r="63">
@@ -58068,7 +58005,7 @@
       </c>
       <c r="B63"/>
       <c r="C63" t="n">
-        <v>0.0062699970992437</v>
+        <v>0.0062699804419748</v>
       </c>
       <c r="D63" t="n">
         <v>-0.000665470295354353</v>
@@ -58077,13 +58014,13 @@
         <v>-0.000701597362450457</v>
       </c>
       <c r="F63" t="n">
-        <v>0.051174541633634</v>
+        <v>-0.000701597362450457</v>
       </c>
       <c r="G63" t="n">
         <v>0.0665874832741347</v>
       </c>
       <c r="H63" t="n">
-        <v>11.6976102438947</v>
+        <v>11.6161753166381</v>
       </c>
     </row>
     <row r="64">
@@ -58092,7 +58029,7 @@
       </c>
       <c r="B64"/>
       <c r="C64" t="n">
-        <v>0.0105510529567465</v>
+        <v>0.0105511494349666</v>
       </c>
       <c r="D64" t="n">
         <v>0.0185942058919149</v>
@@ -58101,13 +58038,13 @@
         <v>0.0197875134417211</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0197774914076012</v>
+        <v>0.0197875134417211</v>
       </c>
       <c r="G64" t="n">
         <v>0.00664667775767747</v>
       </c>
       <c r="H64" t="n">
-        <v>13.208858067762</v>
+        <v>13.2021445038204</v>
       </c>
     </row>
     <row r="65">
@@ -58116,7 +58053,7 @@
       </c>
       <c r="B65"/>
       <c r="C65" t="n">
-        <v>0.0102095869866634</v>
+        <v>0.0102094138286009</v>
       </c>
       <c r="D65" t="n">
         <v>0.0248660749618255</v>
@@ -58125,13 +58062,13 @@
         <v>0.026545444446529</v>
       </c>
       <c r="F65" t="n">
-        <v>0.00976659062117857</v>
+        <v>0.026545444446529</v>
       </c>
       <c r="G65" t="n">
         <v>-0.14431324962613</v>
       </c>
       <c r="H65" t="n">
-        <v>13.0245201335145</v>
+        <v>12.9475919800986</v>
       </c>
     </row>
     <row r="66">
@@ -58140,7 +58077,7 @@
       </c>
       <c r="B66"/>
       <c r="C66" t="n">
-        <v>0.00780093163532847</v>
+        <v>0.00780104553480543</v>
       </c>
       <c r="D66" t="n">
         <v>0.00344632851854731</v>
@@ -58149,13 +58086,13 @@
         <v>0.00363955653902703</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0226288095697447</v>
+        <v>0.00363955653902703</v>
       </c>
       <c r="G66" t="n">
         <v>0.129868334707044</v>
       </c>
       <c r="H66" t="n">
-        <v>13.777930650218</v>
+        <v>13.7719840030569</v>
       </c>
     </row>
     <row r="67">
@@ -58164,7 +58101,7 @@
       </c>
       <c r="B67"/>
       <c r="C67" t="n">
-        <v>0.00316504225339953</v>
+        <v>0.00316502260663798</v>
       </c>
       <c r="D67" t="n">
         <v>0.00494326245401977</v>
@@ -58173,13 +58110,13 @@
         <v>0.00522488511464836</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.00300161828446921</v>
+        <v>0.00522488511464836</v>
       </c>
       <c r="G67" t="n">
         <v>0.088027995027832</v>
       </c>
       <c r="H67" t="n">
-        <v>14.6197226800775</v>
+        <v>14.5938720002851</v>
       </c>
     </row>
     <row r="68">
@@ -58188,7 +58125,7 @@
       </c>
       <c r="B68"/>
       <c r="C68" t="n">
-        <v>0.00275934659774268</v>
+        <v>0.00275936071814309</v>
       </c>
       <c r="D68" t="n">
         <v>0.0142808467558253</v>
@@ -58197,13 +58134,13 @@
         <v>0.0151643473888114</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0108916039707436</v>
+        <v>0.0151643473888114</v>
       </c>
       <c r="G68" t="n">
         <v>-0.0761783007193175</v>
       </c>
       <c r="H68" t="n">
-        <v>15.325724765812</v>
+        <v>15.2928029767593</v>
       </c>
     </row>
     <row r="69">
@@ -58212,7 +58149,7 @@
       </c>
       <c r="B69"/>
       <c r="C69" t="n">
-        <v>0.00263228879766864</v>
+        <v>0.00263229252320007</v>
       </c>
       <c r="D69" t="n">
         <v>0.00880429716030662</v>
@@ -58221,13 +58158,13 @@
         <v>0.00932360895837547</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0108812913326881</v>
+        <v>0.00932360895837547</v>
       </c>
       <c r="G69" t="n">
         <v>0.0468373130093562</v>
       </c>
       <c r="H69" t="n">
-        <v>15.5696833504495</v>
+        <v>15.5322292403226</v>
       </c>
     </row>
     <row r="70">
@@ -58236,7 +58173,7 @@
       </c>
       <c r="B70"/>
       <c r="C70" t="n">
-        <v>0.00563072472790038</v>
+        <v>0.00563048772084507</v>
       </c>
       <c r="D70" t="n">
         <v>0.0134834510119117</v>
@@ -58245,13 +58182,13 @@
         <v>0.0143118288856678</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.0258257888437159</v>
+        <v>0.0143118288856678</v>
       </c>
       <c r="G70" t="n">
         <v>0.0837803294372019</v>
       </c>
       <c r="H70" t="n">
-        <v>15.946694234977</v>
+        <v>15.8778002880298</v>
       </c>
     </row>
     <row r="71">
@@ -58260,7 +58197,7 @@
       </c>
       <c r="B71"/>
       <c r="C71" t="n">
-        <v>0.00409268839733379</v>
+        <v>0.00409292742327727</v>
       </c>
       <c r="D71" t="n">
         <v>-0.0433855974091113</v>
@@ -58269,13 +58206,13 @@
         <v>-0.0447638853785897</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0176980362208816</v>
+        <v>-0.0447638853785897</v>
       </c>
       <c r="G71" t="n">
         <v>-0.0124098477374011</v>
       </c>
       <c r="H71" t="n">
-        <v>15.6416020976425</v>
+        <v>15.550019147945</v>
       </c>
     </row>
     <row r="72">
@@ -58284,7 +58221,7 @@
       </c>
       <c r="B72"/>
       <c r="C72" t="n">
-        <v>0.00436703317206844</v>
+        <v>0.00436697278479414</v>
       </c>
       <c r="D72" t="n">
         <v>0.0149618837800274</v>
@@ -58293,13 +58230,13 @@
         <v>0.0158931973651679</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.0193655343590695</v>
+        <v>0.0158931973651679</v>
       </c>
       <c r="G72" t="n">
         <v>0.0398424799519397</v>
       </c>
       <c r="H72" t="n">
-        <v>14.811853019348</v>
+        <v>14.7858089074822</v>
       </c>
     </row>
     <row r="73">
@@ -58308,7 +58245,7 @@
       </c>
       <c r="B73"/>
       <c r="C73" t="n">
-        <v>0.00199577681848195</v>
+        <v>0.00199573917113804</v>
       </c>
       <c r="D73" t="n">
         <v>0.00276115987124381</v>
@@ -58317,13 +58254,13 @@
         <v>0.00291532809197648</v>
       </c>
       <c r="F73" t="n">
-        <v>0.00750293373059829</v>
+        <v>0.00291532809197648</v>
       </c>
       <c r="G73" t="n">
         <v>-0.196908464413676</v>
       </c>
       <c r="H73" t="n">
-        <v>13.3157113878835</v>
+        <v>13.2551041292045</v>
       </c>
     </row>
     <row r="74">
@@ -58332,7 +58269,7 @@
       </c>
       <c r="B74"/>
       <c r="C74" t="n">
-        <v>0.00143147441845004</v>
+        <v>0.00143155771796932</v>
       </c>
       <c r="D74" t="n">
         <v>0.0314484786913383</v>
@@ -58341,13 +58278,13 @@
         <v>0.0336831710525933</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.00342364210756774</v>
+        <v>0.0336831710525933</v>
       </c>
       <c r="G74" t="n">
         <v>0.0548109582439347</v>
       </c>
       <c r="H74" t="n">
-        <v>12.741928020938</v>
+        <v>12.6945104842897</v>
       </c>
     </row>
     <row r="75">
@@ -58356,7 +58293,7 @@
       </c>
       <c r="B75"/>
       <c r="C75" t="n">
-        <v>-0.00539839140059239</v>
+        <v>-0.00539845009599915</v>
       </c>
       <c r="D75" t="n">
         <v>-0.0196329525738617</v>
@@ -58365,13 +58302,13 @@
         <v>-0.0204973693143744</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.00501423539891732</v>
+        <v>-0.0204973693143744</v>
       </c>
       <c r="G75" t="n">
         <v>0.00234316803904289</v>
       </c>
       <c r="H75" t="n">
-        <v>11.7274927706555</v>
+        <v>11.723967993638</v>
       </c>
     </row>
     <row r="76">
@@ -58380,7 +58317,7 @@
       </c>
       <c r="B76"/>
       <c r="C76" t="n">
-        <v>-0.00362130080084588</v>
+        <v>-0.00362125588775086</v>
       </c>
       <c r="D76" t="n">
         <v>0.00797799554387613</v>
@@ -58389,13 +58326,13 @@
         <v>0.00844503235608318</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.0159233351153443</v>
+        <v>0.00844503235608318</v>
       </c>
       <c r="G76" t="n">
         <v>-0.07484781903376</v>
       </c>
       <c r="H76" t="n">
-        <v>11.243477378086</v>
+        <v>11.1536293579182</v>
       </c>
     </row>
     <row r="77">
@@ -58404,7 +58341,7 @@
       </c>
       <c r="B77"/>
       <c r="C77" t="n">
-        <v>-0.00451189924291917</v>
+        <v>-0.0045118462828313</v>
       </c>
       <c r="D77" t="n">
         <v>0.00144230593638861</v>
@@ -58413,13 +58350,13 @@
         <v>0.0015218295736954</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.0198166031466696</v>
+        <v>0.0015218295736954</v>
       </c>
       <c r="G77" t="n">
         <v>0.00271143151357744</v>
       </c>
       <c r="H77" t="n">
-        <v>10.7273664884985</v>
+        <v>10.6696578906024</v>
       </c>
     </row>
     <row r="78">
@@ -58428,7 +58365,7 @@
       </c>
       <c r="B78"/>
       <c r="C78" t="n">
-        <v>-0.00437268127932899</v>
+        <v>-0.00437268881070629</v>
       </c>
       <c r="D78" t="n">
         <v>-0.0184163572782072</v>
@@ -58437,13 +58374,13 @@
         <v>-0.0192390440766026</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.0178775228844352</v>
+        <v>-0.0192390440766026</v>
       </c>
       <c r="G78" t="n">
         <v>0.0279857207205252</v>
       </c>
       <c r="H78" t="n">
-        <v>10.181972357061</v>
+        <v>10.2057259401396</v>
       </c>
     </row>
     <row r="79">
@@ -58452,7 +58389,7 @@
       </c>
       <c r="B79"/>
       <c r="C79" t="n">
-        <v>-0.00515006363351667</v>
+        <v>-0.00515006660359107</v>
       </c>
       <c r="D79" t="n">
         <v>-0.0218150403638697</v>
@@ -58461,13 +58398,13 @@
         <v>-0.0227508702934136</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.0336589362138162</v>
+        <v>-0.0227508702934136</v>
       </c>
       <c r="G79" t="n">
         <v>-0.0341817463186835</v>
       </c>
       <c r="H79" t="n">
-        <v>8.17350154073352</v>
+        <v>8.16196445328687</v>
       </c>
     </row>
     <row r="80">
@@ -58476,7 +58413,7 @@
       </c>
       <c r="B80"/>
       <c r="C80" t="n">
-        <v>0.000708904941879585</v>
+        <v>0.000708764249266469</v>
       </c>
       <c r="D80" t="n">
         <v>0.020064141216547</v>
@@ -58485,13 +58422,13 @@
         <v>0.0213675350601346</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0240600671145987</v>
+        <v>0.0213675350601346</v>
       </c>
       <c r="G80" t="n">
         <v>-0.0388804657694077</v>
       </c>
       <c r="H80" t="n">
-        <v>7.78353401688702</v>
+        <v>7.78281562072111</v>
       </c>
     </row>
     <row r="81">
@@ -58500,7 +58437,7 @@
       </c>
       <c r="B81"/>
       <c r="C81" t="n">
-        <v>0.00125794232471721</v>
+        <v>0.00125794274382063</v>
       </c>
       <c r="D81" t="n">
         <v>0.0156602039057754</v>
@@ -58509,13 +58446,13 @@
         <v>0.0166408855240663</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.0130555772465137</v>
+        <v>0.0166408855240663</v>
       </c>
       <c r="G81" t="n">
         <v>0.0406633924418598</v>
       </c>
       <c r="H81" t="n">
-        <v>7.27696355564752</v>
+        <v>7.19427454536635</v>
       </c>
     </row>
     <row r="82">
@@ -58524,7 +58461,7 @@
       </c>
       <c r="B82"/>
       <c r="C82" t="n">
-        <v>-0.00223786057895436</v>
+        <v>-0.00223768650961143</v>
       </c>
       <c r="D82" t="n">
         <v>-0.023942653309962</v>
@@ -58533,13 +58470,13 @@
         <v>-0.0249434032207594</v>
       </c>
       <c r="F82" t="n">
-        <v>0.00585044567752613</v>
+        <v>-0.0249434032207594</v>
       </c>
       <c r="G82" t="n">
         <v>-0.0249769247990494</v>
       </c>
       <c r="H82" t="n">
-        <v>6.08803092839302</v>
+        <v>6.06015679867458</v>
       </c>
     </row>
     <row r="83">
@@ -58548,7 +58485,7 @@
       </c>
       <c r="B83"/>
       <c r="C83" t="n">
-        <v>-0.00136739433564248</v>
+        <v>-0.00136765334660538</v>
       </c>
       <c r="D83" t="n">
         <v>0.00256845142746753</v>
@@ -58557,13 +58494,13 @@
         <v>0.00271151352754551</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.00892037089244324</v>
+        <v>0.00271151352754551</v>
       </c>
       <c r="G83" t="n">
         <v>-0.169780987681125</v>
       </c>
       <c r="H83" t="n">
-        <v>5.10508153843752</v>
+        <v>5.03134765191581</v>
       </c>
     </row>
     <row r="84">
@@ -58572,7 +58509,7 @@
       </c>
       <c r="B84"/>
       <c r="C84" t="n">
-        <v>0.000336020565734785</v>
+        <v>0.000336096045969292</v>
       </c>
       <c r="D84" t="n">
         <v>0.0013685837809323</v>
@@ -58581,13 +58518,13 @@
         <v>0.00144398864014317</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.011708977123134</v>
+        <v>0.00144398864014317</v>
       </c>
       <c r="G84" t="n">
         <v>-0.133271275679088</v>
       </c>
       <c r="H84" t="n">
-        <v>5.72304743495803</v>
+        <v>5.61463663904805</v>
       </c>
     </row>
     <row r="85">
@@ -58596,7 +58533,7 @@
       </c>
       <c r="B85"/>
       <c r="C85" t="n">
-        <v>0.00465583670395286</v>
+        <v>0.00465606128023754</v>
       </c>
       <c r="D85" t="n">
         <v>-0.0143556898189616</v>
@@ -58605,13 +58542,13 @@
         <v>-0.0150272773823543</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.00145896639740339</v>
+        <v>-0.0150272773823543</v>
       </c>
       <c r="G85" t="n">
         <v>-0.00298582509810696</v>
       </c>
       <c r="H85" t="n">
-        <v>5.15265568673352</v>
+        <v>5.18211856105028</v>
       </c>
     </row>
     <row r="86">
@@ -58620,7 +58557,7 @@
       </c>
       <c r="B86"/>
       <c r="C86" t="n">
-        <v>0.0106378757972361</v>
+        <v>0.0106378354314001</v>
       </c>
       <c r="D86" t="n">
         <v>0.0352789401189186</v>
@@ -58629,13 +58566,13 @@
         <v>0.0378586355403456</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.00718894701061457</v>
+        <v>0.0378586355403456</v>
       </c>
       <c r="G86" t="n">
         <v>0.0652458283076882</v>
       </c>
       <c r="H86" t="n">
-        <v>5.36642369737203</v>
+        <v>5.39531645146251</v>
       </c>
     </row>
     <row r="87">
@@ -58644,7 +58581,7 @@
       </c>
       <c r="B87"/>
       <c r="C87" t="n">
-        <v>0.00388502573994209</v>
+        <v>0.00388495205367034</v>
       </c>
       <c r="D87" t="n">
         <v>-0.0118636250411046</v>
@@ -58653,13 +58590,13 @@
         <v>0.000155481011395509</v>
       </c>
       <c r="F87" t="n">
-        <v>0.00813862849791125</v>
+        <v>0.000155481011395509</v>
       </c>
       <c r="G87" t="n">
         <v>0.0693085276660685</v>
       </c>
       <c r="H87" t="n">
-        <v>4.54734127540953</v>
+        <v>4.53086294684673</v>
       </c>
     </row>
     <row r="88">
@@ -58668,7 +58605,7 @@
       </c>
       <c r="B88"/>
       <c r="C88" t="n">
-        <v>0.000163786930301502</v>
+        <v>0.000163935543372684</v>
       </c>
       <c r="D88" t="n">
         <v>-0.0326156785934186</v>
@@ -58677,13 +58614,13 @@
         <v>-0.044060414114675</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0152576594015277</v>
+        <v>-0.044060414114675</v>
       </c>
       <c r="G88" t="n">
         <v>0.164353412376446</v>
       </c>
       <c r="H88" t="n">
-        <v>3.59535076347403</v>
+        <v>3.39709137769097</v>
       </c>
     </row>
     <row r="89">
@@ -58694,7 +58631,7 @@
         <v>-20.0062470638137</v>
       </c>
       <c r="C89" t="n">
-        <v>0.00236114016460354</v>
+        <v>0.00236089735050005</v>
       </c>
       <c r="D89" t="n">
         <v>0.0208348337545869</v>
@@ -58703,13 +58640,13 @@
         <v>0.0180657615049089</v>
       </c>
       <c r="F89" t="n">
-        <v>0.00721125837340164</v>
+        <v>0.0180657615049089</v>
       </c>
       <c r="G89" t="n">
         <v>0.0797080539624595</v>
       </c>
       <c r="H89" t="n">
-        <v>3.51311700769053</v>
+        <v>3.5745933613132</v>
       </c>
     </row>
     <row r="90">
@@ -58720,7 +58657,7 @@
         <v>-21.6443773277626</v>
       </c>
       <c r="C90" t="n">
-        <v>0.00140668821035117</v>
+        <v>0.00140681876732929</v>
       </c>
       <c r="D90" t="n">
         <v>0.00972968240224814</v>
@@ -58729,13 +58666,13 @@
         <v>0.00280556708169932</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.01034079025017</v>
+        <v>0.00280556708169932</v>
       </c>
       <c r="G90" t="n">
         <v>0.0410918160781373</v>
       </c>
       <c r="H90" t="n">
-        <v>2.84024961430702</v>
+        <v>2.84255214689644</v>
       </c>
     </row>
     <row r="91">
@@ -58746,7 +58683,7 @@
         <v>-22.0648274952528</v>
       </c>
       <c r="C91" t="n">
-        <v>0.00427112140977481</v>
+        <v>0.00427118119735548</v>
       </c>
       <c r="D91" t="n">
         <v>0.0123985662021937</v>
@@ -58755,13 +58692,13 @@
         <v>0.00825734458727645</v>
       </c>
       <c r="F91" t="n">
-        <v>0.000722195945947579</v>
+        <v>0.00825734458727645</v>
       </c>
       <c r="G91" t="n">
         <v>-0.0617972255084993</v>
       </c>
       <c r="H91" t="n">
-        <v>3.37679308955751</v>
+        <v>3.34306161412167</v>
       </c>
     </row>
     <row r="92">
@@ -58772,7 +58709,7 @@
         <v>-25.1580885611422</v>
       </c>
       <c r="C92" t="n">
-        <v>0.00431927242027719</v>
+        <v>0.00431899688310544</v>
       </c>
       <c r="D92" t="n">
         <v>0.0221529699084519</v>
@@ -58781,13 +58718,13 @@
         <v>-0.029396817478629</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.0121678277629194</v>
+        <v>-0.029396817478629</v>
       </c>
       <c r="G92" t="n">
         <v>0.00349690019539839</v>
       </c>
       <c r="H92" t="n">
-        <v>2.41856122757902</v>
+        <v>2.3737156062199</v>
       </c>
     </row>
     <row r="93">
@@ -58798,7 +58735,7 @@
         <v>-27.3074774601314</v>
       </c>
       <c r="C93" t="n">
-        <v>0.00413615132288081</v>
+        <v>0.00413638646721903</v>
       </c>
       <c r="D93" t="n">
         <v>-0.016642481482565</v>
@@ -58807,13 +58744,13 @@
         <v>0.00934228853094776</v>
       </c>
       <c r="F93" t="n">
-        <v>0.00172657017668776</v>
+        <v>0.00934228853094776</v>
       </c>
       <c r="G93" t="n">
         <v>0.0454345127563522</v>
       </c>
       <c r="H93" t="n">
-        <v>1.78931365259053</v>
+        <v>1.79184627891614</v>
       </c>
     </row>
     <row r="94">
@@ -58824,7 +58761,7 @@
         <v>-18.7037699378427</v>
       </c>
       <c r="C94" t="n">
-        <v>0.00177933122259155</v>
+        <v>0.00177941023670103</v>
       </c>
       <c r="D94" t="n">
         <v>-0.00662852340403797</v>
@@ -58833,13 +58770,13 @@
         <v>0.00628285290133856</v>
       </c>
       <c r="F94" t="n">
-        <v>0.00633681134487052</v>
+        <v>0.00628285290133856</v>
       </c>
       <c r="G94" t="n">
         <v>0.0612819048571742</v>
       </c>
       <c r="H94" t="n">
-        <v>1.41239404734202</v>
+        <v>1.35942307497837</v>
       </c>
     </row>
     <row r="95">
@@ -58850,7 +58787,7 @@
         <v>-26.3489747647108</v>
       </c>
       <c r="C95" t="n">
-        <v>0.00176473568400271</v>
+        <v>0.00176461935324923</v>
       </c>
       <c r="D95" t="n">
         <v>0.0140619706546063</v>
@@ -58859,13 +58796,13 @@
         <v>-0.0108464294342081</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.0100013885439525</v>
+        <v>-0.0108464294342081</v>
       </c>
       <c r="G95" t="n">
         <v>-0.0298251092498205</v>
       </c>
       <c r="H95" t="n">
-        <v>0.563982135046528</v>
+        <v>0.501219655039598</v>
       </c>
     </row>
     <row r="96">
@@ -58876,7 +58813,7 @@
         <v>-22.7673045554094</v>
       </c>
       <c r="C96" t="n">
-        <v>0.000220696714316126</v>
+        <v>0.00022052013121554</v>
       </c>
       <c r="D96" t="n">
         <v>-0.00705042764804942</v>
@@ -58885,13 +58822,13 @@
         <v>-0.00297491902995795</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.00589909726005899</v>
+        <v>-0.00297491902995795</v>
       </c>
       <c r="G96" t="n">
         <v>-0.105374811685342</v>
       </c>
       <c r="H96" t="n">
-        <v>0.269494702451018</v>
+        <v>0.258782673431832</v>
       </c>
     </row>
     <row r="97">
@@ -58902,7 +58839,7 @@
         <v>-20.8011959947811</v>
       </c>
       <c r="C97" t="n">
-        <v>0.00395155787822299</v>
+        <v>0.00395163230869766</v>
       </c>
       <c r="D97" t="n">
         <v>-0.0168257542928849</v>
@@ -58911,13 +58848,13 @@
         <v>0.0331797416715789</v>
       </c>
       <c r="F97" t="n">
-        <v>0.018884737491597</v>
+        <v>0.0331797416715789</v>
       </c>
       <c r="G97" t="n">
         <v>0.115789006969373</v>
       </c>
       <c r="H97" t="n">
-        <v>0.762879340061522</v>
+        <v>0.70142359931805</v>
       </c>
     </row>
     <row r="98">
@@ -58928,7 +58865,7 @@
         <v>-19.6414240544793</v>
       </c>
       <c r="C98" t="n">
-        <v>0.00143831425795149</v>
+        <v>0.0014383318604545</v>
       </c>
       <c r="D98" t="n">
         <v>0.101509612069763</v>
@@ -58937,13 +58874,13 @@
         <v>-0.0397506144790496</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.000353823903454842</v>
+        <v>-0.0397506144790496</v>
       </c>
       <c r="G98" t="n">
         <v>0.139896418779864</v>
       </c>
       <c r="H98" t="n">
-        <v>0.316945271991015</v>
+        <v>0.292834370445281</v>
       </c>
     </row>
     <row r="99">
@@ -58954,7 +58891,7 @@
         <v>-19.9643629531425</v>
       </c>
       <c r="C99" t="n">
-        <v>0.000524011952942161</v>
+        <v>0.000524151894429004</v>
       </c>
       <c r="D99" t="n">
         <v>0.000494736546047925</v>
@@ -58963,13 +58900,13 @@
         <v>-0.0137315597940217</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.00470157329531729</v>
+        <v>-0.0137315597940217</v>
       </c>
       <c r="G99" t="n">
         <v>0.0860084568090844</v>
       </c>
       <c r="H99" t="n">
-        <v>1.06583478711052</v>
+        <v>1.02166377118853</v>
       </c>
     </row>
     <row r="100">
@@ -58980,7 +58917,7 @@
         <v>-16.3714840152673</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.00100601072487194</v>
+        <v>-0.00100615157257344</v>
       </c>
       <c r="D100" t="n">
         <v>-0.000825207485453561</v>
@@ -58989,13 +58926,13 @@
         <v>-0.0197320408364794</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.0111646426446752</v>
+        <v>-0.0197320408364794</v>
       </c>
       <c r="G100" t="n">
         <v>-0.0863718502386277</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.495935462507981</v>
+        <v>-0.46779035503424</v>
       </c>
     </row>
     <row r="101">
@@ -59006,7 +58943,7 @@
         <v>-24.433075444095</v>
       </c>
       <c r="C101" t="n">
-        <v>0.000812782442641602</v>
+        <v>0.000812838305682462</v>
       </c>
       <c r="D101" t="n">
         <v>0.021603234102578</v>
@@ -59015,13 +58952,13 @@
         <v>0.0235854825295192</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0104532811925124</v>
+        <v>0.0235854825295192</v>
       </c>
       <c r="G101" t="n">
         <v>-0.206276842783995</v>
       </c>
       <c r="H101" t="n">
-        <v>-1.24877168568348</v>
+        <v>-1.26219075227702</v>
       </c>
     </row>
     <row r="102">
@@ -59032,7 +58969,7 @@
         <v>-22.0692224932177</v>
       </c>
       <c r="C102" t="n">
-        <v>0.00132589713051345</v>
+        <v>0.00132589593074117</v>
       </c>
       <c r="D102" t="n">
         <v>0.000617953640177582</v>
@@ -59041,13 +58978,13 @@
         <v>0.00363421055963187</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.00673197900604183</v>
+        <v>0.00363421055963187</v>
       </c>
       <c r="G102" t="n">
         <v>-0.028200805424861</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.82792549561797</v>
+        <v>-1.86842381237178</v>
       </c>
     </row>
     <row r="103">
@@ -59058,7 +58995,7 @@
         <v>-9.2030711589097</v>
       </c>
       <c r="C103" t="n">
-        <v>0.00653046744452235</v>
+        <v>0.00653037831945946</v>
       </c>
       <c r="D103" t="n">
         <v>0.0213434614637542</v>
@@ -59067,13 +59004,13 @@
         <v>0.0205619263694397</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.0133335112281401</v>
+        <v>0.0205619263694397</v>
       </c>
       <c r="G103" t="n">
         <v>0.0703384532121216</v>
       </c>
       <c r="H103" t="n">
-        <v>-1.71753951987548</v>
+        <v>-1.74887454382955</v>
       </c>
     </row>
     <row r="104">
@@ -59084,7 +59021,7 @@
         <v>-10.8522723133065</v>
       </c>
       <c r="C104" t="n">
-        <v>0.00771614982173618</v>
+        <v>0.00771620114380056</v>
       </c>
       <c r="D104" t="n">
         <v>0.0109287900155608</v>
@@ -59093,13 +59030,13 @@
         <v>0.0475548431489443</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0163946826485453</v>
+        <v>0.0475548431489443</v>
       </c>
       <c r="G104" t="n">
         <v>0.00835981499162664</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.938392752754979</v>
+        <v>-0.985228136233319</v>
       </c>
     </row>
     <row r="105">
@@ -59110,7 +59047,7 @@
         <v>-9.39413048742932</v>
       </c>
       <c r="C105" t="n">
-        <v>0.00283026636150785</v>
+        <v>0.00283029184356609</v>
       </c>
       <c r="D105" t="n">
         <v>0.00922679986041874</v>
@@ -59119,13 +59056,13 @@
         <v>-0.04075601232105</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.0113278476537655</v>
+        <v>-0.04075601232105</v>
       </c>
       <c r="G105" t="n">
         <v>0.042710639950128</v>
       </c>
       <c r="H105" t="n">
-        <v>-2.61292736887948</v>
+        <v>-2.66447761315908</v>
       </c>
     </row>
     <row r="106">
@@ -59136,7 +59073,7 @@
         <v>-16.1165445970991</v>
       </c>
       <c r="C106" t="n">
-        <v>0.00304797742839424</v>
+        <v>0.00304781153395428</v>
       </c>
       <c r="D106" t="n">
         <v>0.00336027134057559</v>
@@ -59145,13 +59082,13 @@
         <v>-0.000545261486773363</v>
       </c>
       <c r="F106" t="n">
-        <v>0.00162990121835582</v>
+        <v>-0.000545261486773363</v>
       </c>
       <c r="G106" t="n">
         <v>-0.101226030273232</v>
       </c>
       <c r="H106" t="n">
-        <v>-2.86679653331296</v>
+        <v>-2.85354231775584</v>
       </c>
     </row>
     <row r="107">
@@ -59162,7 +59099,7 @@
         <v>-10.9467098532039</v>
       </c>
       <c r="C107" t="n">
-        <v>0.00343566324035294</v>
+        <v>0.00343583785327306</v>
       </c>
       <c r="D107" t="n">
         <v>0.00782381047566405</v>
@@ -59171,13 +59108,13 @@
         <v>0.0160330478802111</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0529337887137844</v>
+        <v>0.0160330478802111</v>
       </c>
       <c r="G107" t="n">
         <v>0.0653614293422251</v>
       </c>
       <c r="H107" t="n">
-        <v>-2.32387581071647</v>
+        <v>-2.40844407721262</v>
       </c>
     </row>
     <row r="108">
@@ -59188,7 +59125,7 @@
         <v>-13.0846949979117</v>
       </c>
       <c r="C108" t="n">
-        <v>0.000364375234380709</v>
+        <v>0.000364354522857102</v>
       </c>
       <c r="D108" t="n">
         <v>-0.00576691491765802</v>
@@ -59197,13 +59134,13 @@
         <v>-0.0204985015089303</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.0545713621732147</v>
+        <v>-0.0204985015089303</v>
       </c>
       <c r="G108" t="n">
         <v>0.0372828361162281</v>
       </c>
       <c r="H108" t="n">
-        <v>-3.11639855413697</v>
+        <v>-3.07218732156839</v>
       </c>
     </row>
     <row r="109">
@@ -59214,7 +59151,7 @@
         <v>-11.7974088203745</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0042707644042741</v>
+        <v>0.00427067936722825</v>
       </c>
       <c r="D109" t="n">
         <v>0.00955745559783372</v>
@@ -59223,13 +59160,13 @@
         <v>0.0428336650824832</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0258586502177627</v>
+        <v>0.0428336650824832</v>
       </c>
       <c r="G109" t="n">
         <v>0.0115985619175181</v>
       </c>
       <c r="H109" t="n">
-        <v>-3.08531438700547</v>
+        <v>-3.13089184075316</v>
       </c>
     </row>
     <row r="110">
@@ -59240,7 +59177,7 @@
         <v>-12.3575403255613</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.00254461127875194</v>
+        <v>-0.00254446310987033</v>
       </c>
       <c r="D110" t="n">
         <v>-0.0798056029657839</v>
@@ -59249,13 +59186,13 @@
         <v>-0.00772630790768947</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0865903723751464</v>
+        <v>-0.00772630790768947</v>
       </c>
       <c r="G110" t="n">
         <v>0.0746580404445369</v>
       </c>
       <c r="H110" t="n">
-        <v>-3.07522086552298</v>
+        <v>-3.07734562355292</v>
       </c>
     </row>
     <row r="111">
@@ -59266,7 +59203,7 @@
         <v>-10.7821567734671</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.000493449586952188</v>
+        <v>-0.000493407022955861</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -59275,13 +59212,13 @@
         <v>0.0163741666806541</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.0136598486426882</v>
+        <v>0.0163741666806541</v>
       </c>
       <c r="G111" t="n">
         <v>0.0179013729774642</v>
       </c>
       <c r="H111" t="n">
-        <v>-2.81585694809348</v>
+        <v>-2.84799694492869</v>
       </c>
     </row>
     <row r="112">
@@ -59292,7 +59229,7 @@
         <v>-9.77127257091994</v>
       </c>
       <c r="C112" t="n">
-        <v>0.00135780888700054</v>
+        <v>0.00135768943649106</v>
       </c>
       <c r="D112" t="n">
         <v>0.00178565567021538</v>
@@ -59301,13 +59238,13 @@
         <v>0.0136625804075639</v>
       </c>
       <c r="F112" t="n">
-        <v>0.02039493799401</v>
+        <v>0.0136625804075639</v>
       </c>
       <c r="G112" t="n">
         <v>0.0673932979355856</v>
       </c>
       <c r="H112" t="n">
-        <v>-2.91249205121097</v>
+        <v>-2.97222029929146</v>
       </c>
     </row>
     <row r="113">
@@ -59318,7 +59255,7 @@
         <v>-5.74494263717975</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00481893142925749</v>
+        <v>0.0048188900150743</v>
       </c>
       <c r="D113" t="n">
         <v>0.0158178388154102</v>
@@ -59327,13 +59264,13 @@
         <v>0.0150267441915712</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.0162245723418613</v>
+        <v>0.0150267441915712</v>
       </c>
       <c r="G113" t="n">
         <v>0.0000771920503632728</v>
       </c>
       <c r="H113" t="n">
-        <v>-2.99327192489048</v>
+        <v>-2.99881669257322</v>
       </c>
     </row>
     <row r="114">
@@ -59344,7 +59281,7 @@
         <v>-4.50055113155155</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00360532869585617</v>
+        <v>0.00360533831094223</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -59353,13 +59290,13 @@
         <v>-0.0102104596693389</v>
       </c>
       <c r="F114" t="n">
-        <v>0.000209402120447066</v>
+        <v>-0.0102104596693389</v>
       </c>
       <c r="G114" t="n">
         <v>0.0970628112639726</v>
       </c>
       <c r="H114" t="n">
-        <v>-2.90611830849498</v>
+        <v>-2.887583848955</v>
       </c>
     </row>
     <row r="115">
@@ -59370,7 +59307,7 @@
         <v>-4.15493263548136</v>
       </c>
       <c r="C115" t="n">
-        <v>0.00161536867115508</v>
+        <v>0.00161538825171181</v>
       </c>
       <c r="D115" t="n">
         <v>0.0223385205624855</v>
@@ -59379,13 +59316,13 @@
         <v>0.0221296743894372</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0177851403951159</v>
+        <v>0.0221296743894372</v>
       </c>
       <c r="G115" t="n">
         <v>-0.0747908437314955</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.83393848073047</v>
+        <v>-2.83699992960576</v>
       </c>
     </row>
     <row r="116">
@@ -59396,7 +59333,7 @@
         <v>-2.95733402951917</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.00178933760314193</v>
+        <v>-0.00178946122837509</v>
       </c>
       <c r="D116" t="n">
         <v>0.0168927965079235</v>
@@ -59405,13 +59342,13 @@
         <v>0.00288801905206615</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.0149405547387884</v>
+        <v>0.00288801905206615</v>
       </c>
       <c r="G116" t="n">
         <v>0.0662419134279038</v>
       </c>
       <c r="H116" t="n">
-        <v>-3.14937605652997</v>
+        <v>-3.21431881260953</v>
       </c>
     </row>
     <row r="117">
@@ -59422,7 +59359,7 @@
         <v>-4.54130733919597</v>
       </c>
       <c r="C117" t="n">
-        <v>0.00597062630393674</v>
+        <v>0.00597072997258197</v>
       </c>
       <c r="D117" t="n">
         <v>0.012510745694688</v>
@@ -59431,13 +59368,13 @@
         <v>0.00142344446339582</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0210158683985657</v>
+        <v>0.00142344446339582</v>
       </c>
       <c r="G117" t="n">
         <v>0.103873696621099</v>
       </c>
       <c r="H117" t="n">
-        <v>-2.36545802026248</v>
+        <v>-2.28638710579029</v>
       </c>
     </row>
     <row r="118">
@@ -59448,7 +59385,7 @@
         <v>-3.59325646994777</v>
       </c>
       <c r="C118" t="n">
-        <v>0.00771153119556045</v>
+        <v>0.00771153723610585</v>
       </c>
       <c r="D118" t="n">
         <v>-0.00334720167696867</v>
@@ -59457,13 +59394,13 @@
         <v>0.0172684961538172</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.00673059631091188</v>
+        <v>0.0172684961538172</v>
       </c>
       <c r="G118" t="n">
         <v>0.0166100175907973</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.15010950437198</v>
+        <v>-2.23114056799407</v>
       </c>
     </row>
     <row r="119">
@@ -59474,7 +59411,7 @@
         <v>-1.87803221167457</v>
       </c>
       <c r="C119" t="n">
-        <v>0.00967638578248398</v>
+        <v>0.0096764325474239</v>
       </c>
       <c r="D119" t="n">
         <v>-0.00758869176160237</v>
@@ -59483,13 +59420,13 @@
         <v>-0.0126950476656953</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0492746968765454</v>
+        <v>-0.0126950476656953</v>
       </c>
       <c r="G119" t="n">
         <v>0.139871860796688</v>
       </c>
       <c r="H119" t="n">
-        <v>-2.52780207386548</v>
+        <v>-2.54874296930883</v>
       </c>
     </row>
     <row r="120">
@@ -59500,7 +59437,7 @@
         <v>-1.50215477553638</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00622972753715167</v>
+        <v>0.00622972523817511</v>
       </c>
       <c r="D120" t="n">
         <v>0.00419827507324477</v>
@@ -59509,13 +59446,13 @@
         <v>0.00323275386569488</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.0365798728101767</v>
+        <v>0.00323275386569488</v>
       </c>
       <c r="G120" t="n">
         <v>-0.105918238799153</v>
       </c>
       <c r="H120" t="n">
-        <v>-2.84417597678997</v>
+        <v>-2.9124743124506</v>
       </c>
     </row>
     <row r="121">
@@ -59526,7 +59463,7 @@
         <v>1.41626675148282</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00406228613788207</v>
+        <v>0.00406227477273013</v>
       </c>
       <c r="D121" t="n">
         <v>0.0157029647417009</v>
@@ -59535,13 +59472,13 @@
         <v>0.0296794986515403</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.0209866643531349</v>
+        <v>0.0296794986515403</v>
       </c>
       <c r="G121" t="n">
         <v>-0.131744402063196</v>
       </c>
       <c r="H121" t="n">
-        <v>-2.66906140331448</v>
+        <v>-2.64048037449438</v>
       </c>
     </row>
     <row r="122">
@@ -59552,7 +59489,7 @@
         <v>1.92360138218101</v>
       </c>
       <c r="C122" t="n">
-        <v>0.000843978337001339</v>
+        <v>0.000843876685214795</v>
       </c>
       <c r="D122" t="n">
         <v>0.0234082592888032</v>
@@ -59561,13 +59498,13 @@
         <v>-0.026105339998697</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0507735408569578</v>
+        <v>-0.026105339998697</v>
       </c>
       <c r="G122" t="n">
         <v>0.0964334258254915</v>
       </c>
       <c r="H122" t="n">
-        <v>-2.75341536581097</v>
+        <v>-2.74689358691313</v>
       </c>
     </row>
     <row r="123">
@@ -59578,7 +59515,7 @@
         <v>2.85586485894421</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.00200383548537886</v>
+        <v>-0.00200367190410278</v>
       </c>
       <c r="D123" t="n">
         <v>-0.00649886824100543</v>
@@ -59587,13 +59524,13 @@
         <v>0.0208524737184872</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.00293969718330533</v>
+        <v>0.0208524737184872</v>
       </c>
       <c r="G123" t="n">
         <v>0.0237037366463282</v>
       </c>
       <c r="H123" t="n">
-        <v>-3.25250470963448</v>
+        <v>-3.3113420398379</v>
       </c>
     </row>
     <row r="124">
@@ -59604,7 +59541,7 @@
         <v>2.30159455964041</v>
       </c>
       <c r="C124" t="n">
-        <v>0.00300305149764046</v>
+        <v>0.00300310746179067</v>
       </c>
       <c r="D124" t="n">
         <v>0.029949288249616</v>
@@ -59613,13 +59550,13 @@
         <v>-0.00867763834359891</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.0120672410977694</v>
+        <v>-0.00867763834359891</v>
       </c>
       <c r="G124" t="n">
         <v>0.110652750804023</v>
       </c>
       <c r="H124" t="n">
-        <v>-2.81531963611098</v>
+        <v>-2.78630466158867</v>
       </c>
     </row>
     <row r="125">
@@ -59630,7 +59567,7 @@
         <v>0.931777255730602</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0044813746644512</v>
+        <v>0.0044813700726678</v>
       </c>
       <c r="D125" t="n">
         <v>-0.0111554815964685</v>
@@ -59639,13 +59576,13 @@
         <v>0.0104253038411057</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0252691410584998</v>
+        <v>0.0104253038411057</v>
       </c>
       <c r="G125" t="n">
         <v>-0.0197585847853645</v>
       </c>
       <c r="H125" t="n">
-        <v>-3.33618166440748</v>
+        <v>-3.39902210268943</v>
       </c>
     </row>
     <row r="126">
@@ -59656,7 +59593,7 @@
         <v>1.4161315833308</v>
       </c>
       <c r="C126" t="n">
-        <v>0.00562783224369401</v>
+        <v>0.00562773028812646</v>
       </c>
       <c r="D126" t="n">
         <v>0.0218254705905099</v>
@@ -59665,13 +59602,13 @@
         <v>0.0213081265151391</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.00620015003903962</v>
+        <v>0.0213081265151391</v>
       </c>
       <c r="G126" t="n">
         <v>-0.0636744258744422</v>
       </c>
       <c r="H126" t="n">
-        <v>-2.99125074008097</v>
+        <v>-3.0014743268612</v>
       </c>
     </row>
     <row r="127">
@@ -59682,7 +59619,7 @@
         <v>-1.674339025974</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.00215042782735475</v>
+        <v>-0.00215055927680741</v>
       </c>
       <c r="D127" t="n">
         <v>-0.00312750540285611</v>
@@ -59691,13 +59628,13 @@
         <v>-0.00684954424810069</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.00716154703168126</v>
+        <v>-0.00684954424810069</v>
       </c>
       <c r="G127" t="n">
         <v>0.147058662766154</v>
       </c>
       <c r="H127" t="n">
-        <v>-3.47062718208247</v>
+        <v>-3.46041894711998</v>
       </c>
     </row>
     <row r="128">
@@ -59708,7 +59645,7 @@
         <v>-0.696969151820809</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.00217491314101625</v>
+        <v>-0.00217461358943893</v>
       </c>
       <c r="D128" t="n">
         <v>0.000781183766622728</v>
@@ -59717,13 +59654,13 @@
         <v>0.0411543902155653</v>
       </c>
       <c r="F128" t="n">
-        <v>0.00182867828175048</v>
+        <v>0.0411543902155653</v>
       </c>
       <c r="G128" t="n">
         <v>0.0517268313842392</v>
       </c>
       <c r="H128" t="n">
-        <v>-3.20062766734698</v>
+        <v>-3.18675019023674</v>
       </c>
     </row>
     <row r="129">
@@ -59734,7 +59671,7 @@
         <v>1.17813719753338</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.00285749070592756</v>
+        <v>-0.00285777386511432</v>
       </c>
       <c r="D129" t="n">
         <v>0.0054392560000398</v>
@@ -59743,13 +59680,13 @@
         <v>-0.0131995685454571</v>
       </c>
       <c r="F129" t="n">
-        <v>0.00402919805389512</v>
+        <v>-0.0131995685454571</v>
       </c>
       <c r="G129" t="n">
         <v>0.0834498218944129</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.90302649782848</v>
+        <v>-2.95997975517451</v>
       </c>
     </row>
     <row r="130">
@@ -59760,22 +59697,22 @@
         <v>-3.47057903298541</v>
       </c>
       <c r="C130" t="n">
-        <v>0.00433927720588656</v>
+        <v>0.00433950276681028</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.0149848247562678</v>
+        <v>-0.015785976115354</v>
       </c>
       <c r="E130" t="n">
         <v>-0.0143239335423466</v>
       </c>
       <c r="F130" t="n">
-        <v>0.00611426815035188</v>
+        <v>-0.0143239335423466</v>
       </c>
       <c r="G130" t="n">
         <v>0.0146697794986554</v>
       </c>
       <c r="H130" t="n">
-        <v>-2.91427890329697</v>
+        <v>-2.93563740420329</v>
       </c>
     </row>
     <row r="131">
@@ -59786,22 +59723,22 @@
         <v>4.28746982814177</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0135827977835801</v>
+        <v>0.0135826511993957</v>
       </c>
       <c r="D131" t="n">
-        <v>0.0430321399678082</v>
+        <v>0.0437876172106675</v>
       </c>
       <c r="E131" t="n">
         <v>0.0316130409637978</v>
       </c>
       <c r="F131" t="n">
-        <v>0.00114082680658889</v>
+        <v>0.0316130409637978</v>
       </c>
       <c r="G131" t="n">
         <v>-0.0408098771263514</v>
       </c>
       <c r="H131" t="n">
-        <v>-2.80835674194447</v>
+        <v>-2.86176627893005</v>
       </c>
     </row>
     <row r="132">
@@ -59812,22 +59749,22 @@
         <v>6.73685540211697</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0116007530259021</v>
+        <v>0.0116007224984527</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.00378790941527374</v>
+        <v>-0.00378782225389163</v>
       </c>
       <c r="E132" t="n">
         <v>-0.00614870428277481</v>
       </c>
       <c r="F132" t="n">
-        <v>0.022056663105551</v>
+        <v>-0.00614870428277481</v>
       </c>
       <c r="G132" t="n">
         <v>-0.0484330097951799</v>
       </c>
       <c r="H132" t="n">
-        <v>-2.03271977616197</v>
+        <v>-2.01592162834881</v>
       </c>
     </row>
     <row r="133">
@@ -59838,22 +59775,22 @@
         <v>1.85372948146617</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0108822536780711</v>
+        <v>0.010882500412333</v>
       </c>
       <c r="D133" t="n">
-        <v>0.0119764825484476</v>
+        <v>0.0119762530711953</v>
       </c>
       <c r="E133" t="n">
         <v>0.0297872370496108</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.00375591377654239</v>
+        <v>0.0297872370496108</v>
       </c>
       <c r="G133" t="n">
         <v>0.00153203289845738</v>
       </c>
       <c r="H133" t="n">
-        <v>-2.17113360304847</v>
+        <v>-2.16059579152558</v>
       </c>
     </row>
     <row r="134">
@@ -59864,22 +59801,22 @@
         <v>3.34812735592037</v>
       </c>
       <c r="C134" t="n">
-        <v>0.00616691964113558</v>
+        <v>0.00616681215192472</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.00982635902416096</v>
+        <v>-0.00982629157571635</v>
       </c>
       <c r="E134" t="n">
         <v>0.00945180860136396</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.0026448580411591</v>
+        <v>0.00945180860136396</v>
       </c>
       <c r="G134" t="n">
         <v>0.101780699686169</v>
       </c>
       <c r="H134" t="n">
-        <v>-2.13168309068897</v>
+        <v>-2.15527076863435</v>
       </c>
     </row>
     <row r="135">
@@ -59890,22 +59827,22 @@
         <v>3.71875927196556</v>
       </c>
       <c r="C135" t="n">
-        <v>0.00444817759990901</v>
+        <v>0.00444803765798119</v>
       </c>
       <c r="D135" t="n">
-        <v>0.0257760790974215</v>
+        <v>0.0257759766420085</v>
       </c>
       <c r="E135" t="n">
         <v>-0.00964521311020938</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0194876131663957</v>
+        <v>-0.00964521311020938</v>
       </c>
       <c r="G135" t="n">
         <v>-0.0483850193572879</v>
       </c>
       <c r="H135" t="n">
-        <v>-2.00195199889947</v>
+        <v>-1.96933200393512</v>
       </c>
     </row>
     <row r="136">
@@ -59916,22 +59853,22 @@
         <v>4.14228624802376</v>
       </c>
       <c r="C136" t="n">
-        <v>0.00442772553929682</v>
+        <v>0.00442777617935564</v>
       </c>
       <c r="D136" t="n">
-        <v>0.00585647997007577</v>
+        <v>0.0058567477194309</v>
       </c>
       <c r="E136" t="n">
         <v>0.0121070989921082</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.00769455740900415</v>
+        <v>0.0121070989921082</v>
       </c>
       <c r="G136" t="n">
         <v>0.0110680235711147</v>
       </c>
       <c r="H136" t="n">
-        <v>-2.23689056249497</v>
+        <v>-2.26183590801689</v>
       </c>
     </row>
     <row r="137">
@@ -59942,22 +59879,22 @@
         <v>6.54179762016996</v>
       </c>
       <c r="C137" t="n">
-        <v>0.00593789720814009</v>
+        <v>0.00593784931950658</v>
       </c>
       <c r="D137" t="n">
-        <v>0.0158508064401972</v>
+        <v>0.0144303600843583</v>
       </c>
       <c r="E137" t="n">
         <v>0.000934126217302378</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.000987251996491523</v>
+        <v>0.000934126217302378</v>
       </c>
       <c r="G137" t="n">
         <v>0.0701408367144651</v>
       </c>
       <c r="H137" t="n">
-        <v>-1.14392714580348</v>
+        <v>-1.17371271526565</v>
       </c>
     </row>
     <row r="138">
@@ -59968,22 +59905,22 @@
         <v>6.16424506068815</v>
       </c>
       <c r="C138" t="n">
-        <v>0.00429063570713062</v>
+        <v>0.00429084837385929</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.0123997898913255</v>
+        <v>-0.0109410380095407</v>
       </c>
       <c r="E138" t="n">
         <v>-0.0054999905610007</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0227690299606769</v>
+        <v>-0.0054999905610007</v>
       </c>
       <c r="G138" t="n">
         <v>-0.00339247434909051</v>
       </c>
       <c r="H138" t="n">
-        <v>-1.61130130538197</v>
+        <v>-1.61168451847742</v>
       </c>
     </row>
     <row r="139">
@@ -59994,22 +59931,22 @@
         <v>6.68920644749035</v>
       </c>
       <c r="C139" t="n">
-        <v>0.00162393670930783</v>
+        <v>0.00162384168708707</v>
       </c>
       <c r="D139" t="n">
-        <v>0.0200155061444742</v>
+        <v>0.0200156503729079</v>
       </c>
       <c r="E139" t="n">
         <v>0.0112024628197407</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0238716544047737</v>
+        <v>0.0112024628197407</v>
       </c>
       <c r="G139" t="n">
         <v>0.000177584467461855</v>
       </c>
       <c r="H139" t="n">
-        <v>-1.45473822603148</v>
+        <v>-1.46231460422218</v>
       </c>
     </row>
     <row r="140">
@@ -60020,22 +59957,22 @@
         <v>7.67968981146056</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.00487656355602084</v>
+        <v>-0.0048766566085181</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.0324779719934298</v>
+        <v>-0.032477953374249</v>
       </c>
       <c r="E140" t="n">
         <v>-0.0156051839096722</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.0160631743510571</v>
+        <v>-0.0156051839096722</v>
       </c>
       <c r="G140" t="n">
         <v>0.0377840209066722</v>
       </c>
       <c r="H140" t="n">
-        <v>-4.73617412004898</v>
+        <v>-4.71667460428696</v>
       </c>
     </row>
     <row r="141">
@@ -60046,22 +59983,22 @@
         <v>8.73691364715974</v>
       </c>
       <c r="C141" t="n">
-        <v>0.00426123832699243</v>
+        <v>0.00426130908642053</v>
       </c>
       <c r="D141" t="n">
-        <v>0.0362812223252083</v>
+        <v>0.0362809857218824</v>
       </c>
       <c r="E141" t="n">
         <v>0.0262734665475879</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0277271470078349</v>
+        <v>0.0262734665475879</v>
       </c>
       <c r="G141" t="n">
         <v>-0.0306961246474611</v>
       </c>
       <c r="H141" t="n">
-        <v>-3.26935124941848</v>
+        <v>-3.27324700090973</v>
       </c>
     </row>
     <row r="142">
@@ -60072,22 +60009,22 @@
         <v>2.53071511411793</v>
       </c>
       <c r="C142" t="n">
-        <v>0.00655025898615769</v>
+        <v>0.00655029961632003</v>
       </c>
       <c r="D142" t="n">
-        <v>0.0356727277060402</v>
+        <v>0.0343476009699222</v>
       </c>
       <c r="E142" t="n">
         <v>0.023331524363603</v>
       </c>
       <c r="F142" t="n">
-        <v>0.00509681581999111</v>
+        <v>0.023331524363603</v>
       </c>
       <c r="G142" t="n">
         <v>-0.132779131783365</v>
       </c>
       <c r="H142" t="n">
-        <v>-1.92290969807597</v>
+        <v>-1.99400356508249</v>
       </c>
     </row>
     <row r="143">
@@ -60098,22 +60035,22 @@
         <v>9.59912441273514</v>
       </c>
       <c r="C143" t="n">
-        <v>0.00511476743926131</v>
+        <v>0.00511471055010926</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.0110959709156995</v>
+        <v>-0.00900913422935723</v>
       </c>
       <c r="E143" t="n">
         <v>-0.0033367973562406</v>
       </c>
       <c r="F143" t="n">
-        <v>0.011252236701659</v>
+        <v>-0.0033367973562406</v>
       </c>
       <c r="G143" t="n">
         <v>-0.0917438980304963</v>
       </c>
       <c r="H143" t="n">
-        <v>-2.93344290096547</v>
+        <v>-2.86865261334526</v>
       </c>
     </row>
     <row r="144">
@@ -60124,22 +60061,22 @@
         <v>8.42415976586833</v>
       </c>
       <c r="C144" t="n">
-        <v>0.00516858691292921</v>
+        <v>0.00516857161008932</v>
       </c>
       <c r="D144" t="n">
-        <v>0.0143547212511002</v>
+        <v>0.0136708367542102</v>
       </c>
       <c r="E144" t="n">
         <v>0.0134840472741979</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0299610975255371</v>
+        <v>0.0134840472741979</v>
       </c>
       <c r="G144" t="n">
         <v>0.0116827373455539</v>
       </c>
       <c r="H144" t="n">
-        <v>-2.52811663683097</v>
+        <v>-2.54606937289603</v>
       </c>
     </row>
     <row r="145">
@@ -60150,22 +60087,22 @@
         <v>11.1251041826255</v>
       </c>
       <c r="C145" t="n">
-        <v>0.00431726310441594</v>
+        <v>0.00431725711986708</v>
       </c>
       <c r="D145" t="n">
-        <v>0.00880760685481086</v>
+        <v>0.00813579978206436</v>
       </c>
       <c r="E145" t="n">
         <v>-0.00438246602462389</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.0167804779393146</v>
+        <v>-0.00438246602462389</v>
       </c>
       <c r="G145" t="n">
         <v>0.0241780985158737</v>
       </c>
       <c r="H145" t="n">
-        <v>-2.46047090415648</v>
+        <v>-2.5318840161938</v>
       </c>
     </row>
     <row r="146">
@@ -60176,22 +60113,22 @@
         <v>8.99891933373671</v>
       </c>
       <c r="C146" t="n">
-        <v>0.00582226337929814</v>
+        <v>0.00582226817105003</v>
       </c>
       <c r="D146" t="n">
-        <v>0.00739761287920215</v>
+        <v>0.00806991045999084</v>
       </c>
       <c r="E146" t="n">
         <v>0.0153264681701222</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.0060601260765818</v>
+        <v>0.0153264681701222</v>
       </c>
       <c r="G146" t="n">
         <v>-0.120488420241086</v>
       </c>
       <c r="H146" t="n">
-        <v>-2.35842499913397</v>
+        <v>-2.29991621648556</v>
       </c>
     </row>
     <row r="147">
@@ -60202,22 +60139,22 @@
         <v>11.9852382061959</v>
       </c>
       <c r="C147" t="n">
-        <v>0.00592192561981975</v>
+        <v>0.00592205330574203</v>
       </c>
       <c r="D147" t="n">
-        <v>0.0139261286056493</v>
+        <v>0.0139262907020972</v>
       </c>
       <c r="E147" t="n">
         <v>0.0399750899120477</v>
       </c>
       <c r="F147" t="n">
-        <v>0.00562555349579075</v>
+        <v>0.0399750899120477</v>
       </c>
       <c r="G147" t="n">
         <v>0.0845423567418955</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.855005671274457</v>
+        <v>-0.927798388026336</v>
       </c>
     </row>
     <row r="148">
@@ -60228,22 +60165,22 @@
         <v>16.1671922000371</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0052436966859295</v>
+        <v>0.00524353438004166</v>
       </c>
       <c r="D148" t="n">
-        <v>0.0046204488035908</v>
+        <v>0.00396293853314189</v>
       </c>
       <c r="E148" t="n">
         <v>-0.0279448059535063</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0206331403152182</v>
+        <v>-0.0279448059535063</v>
       </c>
       <c r="G148" t="n">
         <v>0.0131488220133171</v>
       </c>
       <c r="H148" t="n">
-        <v>-1.31991082341996</v>
+        <v>-1.42543910757111</v>
       </c>
     </row>
     <row r="149">
@@ -60254,22 +60191,22 @@
         <v>9.37403689733732</v>
       </c>
       <c r="C149" t="n">
-        <v>0.00337779813823502</v>
+        <v>0.00337787340997231</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>0.000660141709643458</v>
       </c>
       <c r="E149" t="n">
         <v>-0.00437902667733603</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.0161711938656159</v>
+        <v>-0.00437902667733603</v>
       </c>
       <c r="G149" t="n">
         <v>0.0201356966647186</v>
       </c>
       <c r="H149" t="n">
-        <v>-2.29292006992846</v>
+        <v>-2.13636952945888</v>
       </c>
     </row>
     <row r="150">
@@ -60280,22 +60217,22 @@
         <v>10.9349314910275</v>
       </c>
       <c r="C150" t="n">
-        <v>0.00777622097563668</v>
+        <v>0.00777609046951433</v>
       </c>
       <c r="D150" t="n">
-        <v>0.0238424476076844</v>
+        <v>0.0238424881106245</v>
       </c>
       <c r="E150" t="n">
         <v>0.0141825901825614</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0233605758104378</v>
+        <v>0.0141825901825614</v>
       </c>
       <c r="G150" t="n">
         <v>-0.0251107338630483</v>
       </c>
       <c r="H150" t="n">
-        <v>-0.509663010132991</v>
+        <v>-0.510591975446643</v>
       </c>
     </row>
     <row r="151">
@@ -60306,22 +60243,22 @@
         <v>15.1142193840787</v>
       </c>
       <c r="C151" t="n">
-        <v>0.000844381744363076</v>
+        <v>0.000844651043522049</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.0210541470169563</v>
+        <v>-0.0210541658795589</v>
       </c>
       <c r="E151" t="n">
         <v>0.00120356485944484</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.0277492681159792</v>
+        <v>0.00120356485944484</v>
       </c>
       <c r="G151" t="n">
         <v>0.0990404982376401</v>
       </c>
       <c r="H151" t="n">
-        <v>-1.23826638459248</v>
+        <v>-1.31802451000339</v>
       </c>
     </row>
     <row r="152">
@@ -60332,22 +60269,22 @@
         <v>12.2315520342609</v>
       </c>
       <c r="C152" t="n">
-        <v>0.00632563993722002</v>
+        <v>0.00632533378819922</v>
       </c>
       <c r="D152" t="n">
-        <v>0.00912648399007177</v>
+        <v>0.00977208938421104</v>
       </c>
       <c r="E152" t="n">
         <v>0.0146373326868332</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0259007477318223</v>
+        <v>0.0146373326868332</v>
       </c>
       <c r="G152" t="n">
         <v>0.099747949882393</v>
       </c>
       <c r="H152" t="n">
-        <v>0.189208573772023</v>
+        <v>0.260412169302833</v>
       </c>
     </row>
     <row r="153">
@@ -60358,22 +60295,22 @@
         <v>9.74441750104709</v>
       </c>
       <c r="C153" t="n">
-        <v>0.00210835091832795</v>
+        <v>0.00210846811247301</v>
       </c>
       <c r="D153" t="n">
-        <v>0.0340118579238711</v>
+        <v>0.033381618203669</v>
       </c>
       <c r="E153" t="n">
         <v>0.00344494735552292</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.00873369132994206</v>
+        <v>0.00344494735552292</v>
       </c>
       <c r="G153" t="n">
         <v>-0.0379994784463449</v>
       </c>
       <c r="H153" t="n">
-        <v>0.494015595020524</v>
+        <v>0.493711242120055</v>
       </c>
     </row>
     <row r="154">
@@ -60384,22 +60321,22 @@
         <v>14.2299582562243</v>
       </c>
       <c r="C154" t="n">
-        <v>0.00106540693425128</v>
+        <v>0.00106544244335893</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.019911433969654</v>
+        <v>-0.0205670179285624</v>
       </c>
       <c r="E154" t="n">
         <v>-0.0237538529909509</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0266874590974764</v>
+        <v>-0.0237538529909509</v>
       </c>
       <c r="G154" t="n">
         <v>0.0712542107263232</v>
       </c>
       <c r="H154" t="n">
-        <v>-0.255726826069961</v>
+        <v>-0.356833473930695</v>
       </c>
     </row>
     <row r="155">
@@ -60410,7 +60347,7 @@
         <v>7.89241528456747</v>
       </c>
       <c r="C155" t="n">
-        <v>0.00432665892169481</v>
+        <v>0.00432666461218112</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -60419,13 +60356,13 @@
         <v>0.016487136123251</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.00557471614893412</v>
+        <v>0.016487136123251</v>
       </c>
       <c r="G155" t="n">
         <v>0.0519519587782957</v>
       </c>
       <c r="H155" t="n">
-        <v>0.711586796307532</v>
+        <v>0.71342052238951</v>
       </c>
     </row>
     <row r="156">
@@ -60436,22 +60373,22 @@
         <v>8.97562938514369</v>
       </c>
       <c r="C156" t="n">
-        <v>0.00681319539476366</v>
+        <v>0.00681326078115951</v>
       </c>
       <c r="D156" t="n">
-        <v>0.0287001767364301</v>
+        <v>0.0293241616292499</v>
       </c>
       <c r="E156" t="n">
         <v>0.0217510185464107</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0138747443659337</v>
+        <v>0.0217510185464107</v>
       </c>
       <c r="G156" t="n">
         <v>0.0701840721581748</v>
       </c>
       <c r="H156" t="n">
-        <v>1.02330062181903</v>
+        <v>0.974120014503771</v>
       </c>
     </row>
     <row r="157">
@@ -60462,22 +60399,22 @@
         <v>8.55503153161786</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0051316098264218</v>
+        <v>0.00513147976664374</v>
       </c>
       <c r="D157" t="n">
-        <v>0.00310940632672274</v>
+        <v>0.00310944252854162</v>
       </c>
       <c r="E157" t="n">
         <v>0.0117717502619152</v>
       </c>
       <c r="F157" t="n">
-        <v>0.00228441558017778</v>
+        <v>0.0117717502619152</v>
       </c>
       <c r="G157" t="n">
         <v>-0.0413126549060019</v>
       </c>
       <c r="H157" t="n">
-        <v>1.07673289696653</v>
+        <v>1.10815224943598</v>
       </c>
     </row>
     <row r="158">
@@ -60488,22 +60425,22 @@
         <v>12.0812305606991</v>
       </c>
       <c r="C158" t="n">
-        <v>0.00401011083273506</v>
+        <v>0.00401021189071216</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.00688794362526446</v>
+        <v>-0.00688797832011545</v>
       </c>
       <c r="E158" t="n">
         <v>-0.0154690755127174</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0257374279020333</v>
+        <v>-0.0154690755127174</v>
       </c>
       <c r="G158" t="n">
         <v>-0.0261532820497834</v>
       </c>
       <c r="H158" t="n">
-        <v>0.105483016246016</v>
+        <v>0.0741222797582096</v>
       </c>
     </row>
     <row r="159">
@@ -60514,22 +60451,22 @@
         <v>12.4343560498593</v>
       </c>
       <c r="C159" t="n">
-        <v>0.00298253730739795</v>
+        <v>0.00298255281613358</v>
       </c>
       <c r="D159" t="n">
-        <v>0.0154136318151759</v>
+        <v>0.0154138167689357</v>
       </c>
       <c r="E159" t="n">
         <v>-0.00580514948568034</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.00190341306677677</v>
+        <v>-0.00580514948568034</v>
       </c>
       <c r="G159" t="n">
         <v>-0.0111228956949656</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.300648785568459</v>
+        <v>-0.322043034395541</v>
       </c>
     </row>
     <row r="160">
@@ -60540,22 +60477,22 @@
         <v>6.56282178380647</v>
       </c>
       <c r="C160" t="n">
-        <v>0.00485943930936994</v>
+        <v>0.00485934414200351</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.00309215751790903</v>
+        <v>-0.00247226243971976</v>
       </c>
       <c r="E160" t="n">
         <v>0.0178694380704325</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0382747228843217</v>
+        <v>0.0178694380704325</v>
       </c>
       <c r="G160" t="n">
         <v>0.0700005565359199</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.131671631784986</v>
+        <v>-0.060660316790306</v>
       </c>
     </row>
     <row r="161">
@@ -60566,22 +60503,22 @@
         <v>1.33747068382666</v>
       </c>
       <c r="C161" t="n">
-        <v>0.00252580177664008</v>
+        <v>0.00252573810026213</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>-0.00123746484470688</v>
       </c>
       <c r="E161" t="n">
         <v>-0.007936961296517</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.00492523494804864</v>
+        <v>-0.007936961296517</v>
       </c>
       <c r="G161" t="n">
         <v>0.0533916553609535</v>
       </c>
       <c r="H161" t="n">
-        <v>-0.277171195557482</v>
+        <v>-0.247980279609095</v>
       </c>
     </row>
     <row r="162">
@@ -60592,22 +60529,22 @@
         <v>6.05929136252085</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.00331953001734409</v>
+        <v>-0.00331958998092041</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.0432390308335124</v>
+        <v>-0.0425935100896164</v>
       </c>
       <c r="E162" t="n">
         <v>-0.0479604595761254</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.041148900866272</v>
+        <v>-0.0479604595761254</v>
       </c>
       <c r="G162" t="n">
         <v>0.0602697512397139</v>
       </c>
       <c r="H162" t="n">
-        <v>-2.77115920083097</v>
+        <v>-2.83772998052784</v>
       </c>
     </row>
     <row r="163">
@@ -60618,22 +60555,22 @@
         <v>5.25857659720605</v>
       </c>
       <c r="C163" t="n">
-        <v>0.00450942784643349</v>
+        <v>0.00450958149603142</v>
       </c>
       <c r="D163" t="n">
-        <v>0.0560588671837423</v>
+        <v>0.05605904831013</v>
       </c>
       <c r="E163" t="n">
         <v>0.0198300586922029</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0406542476425713</v>
+        <v>0.0198300586922029</v>
       </c>
       <c r="G163" t="n">
         <v>0.0596051384038478</v>
       </c>
       <c r="H163" t="n">
-        <v>-1.31270002464847</v>
+        <v>-1.3113220869886</v>
       </c>
     </row>
     <row r="164">
@@ -60644,22 +60581,22 @@
         <v>2.12463143262125</v>
       </c>
       <c r="C164" t="n">
-        <v>0.00439003045226638</v>
+        <v>0.00439002101715147</v>
       </c>
       <c r="D164" t="n">
-        <v>0.0358269043539705</v>
+        <v>0.0363930117843814</v>
       </c>
       <c r="E164" t="n">
         <v>0.0415039516536915</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.00616759801440292</v>
+        <v>0.0415039516536915</v>
       </c>
       <c r="G164" t="n">
         <v>-0.0125615045429681</v>
       </c>
       <c r="H164" t="n">
-        <v>-1.49246452721599</v>
+        <v>-1.4272008735824</v>
       </c>
     </row>
     <row r="165">
@@ -60670,22 +60607,22 @@
         <v>4.00583407415744</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.00440056785110965</v>
+        <v>-0.00440053970198306</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.0371582179019936</v>
+        <v>-0.0377677275369401</v>
       </c>
       <c r="E165" t="n">
         <v>-0.057399679960997</v>
       </c>
       <c r="F165" t="n">
-        <v>0.00876786518122152</v>
+        <v>-0.057399679960997</v>
       </c>
       <c r="G165" t="n">
         <v>-0.0881128463570704</v>
       </c>
       <c r="H165" t="n">
-        <v>-2.90065213381246</v>
+        <v>-2.92927541575016</v>
       </c>
     </row>
     <row r="166">
@@ -60696,22 +60633,22 @@
         <v>3.05388072456064</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.00317476850419229</v>
+        <v>-0.00317473773636401</v>
       </c>
       <c r="D166" t="n">
-        <v>0.0226209375448376</v>
+        <v>0.0220386565850776</v>
       </c>
       <c r="E166" t="n">
         <v>0.00815627491072757</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.0646088126422875</v>
+        <v>0.00815627491072757</v>
       </c>
       <c r="G166" t="n">
         <v>-0.11750541120031</v>
       </c>
       <c r="H166" t="n">
-        <v>-2.85018304925596</v>
+        <v>-2.90606971255491</v>
       </c>
     </row>
     <row r="167">
@@ -60722,22 +60659,22 @@
         <v>-1.61073403819516</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.0063394408449966</v>
+        <v>-0.00633945063803232</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.0114389988325025</v>
+        <v>-0.0108369268126238</v>
       </c>
       <c r="E167" t="n">
         <v>-0.0087664612034084</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0292988693851326</v>
+        <v>-0.0087664612034084</v>
       </c>
       <c r="G167" t="n">
         <v>-0.268575927232719</v>
       </c>
       <c r="H167" t="n">
-        <v>-4.01614757469647</v>
+        <v>-4.0628676292127</v>
       </c>
     </row>
     <row r="168">
@@ -60748,22 +60685,22 @@
         <v>0.241043286619025</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.00596380916341577</v>
+        <v>-0.00596386865877108</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.00483981230759012</v>
+        <v>-0.0048397202031687</v>
       </c>
       <c r="E168" t="n">
         <v>-0.00421301365574944</v>
       </c>
       <c r="F168" t="n">
-        <v>-0.0122377958391269</v>
+        <v>-0.00421301365574944</v>
       </c>
       <c r="G168" t="n">
         <v>-0.230972995396866</v>
       </c>
       <c r="H168" t="n">
-        <v>-4.48520546297497</v>
+        <v>-4.41858176146547</v>
       </c>
     </row>
     <row r="169">
@@ -60774,22 +60711,22 @@
         <v>-6.45131366570178</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.0104979911854279</v>
+        <v>-0.0104978803009068</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.0091577344108531</v>
+        <v>-0.00977423358186913</v>
       </c>
       <c r="E169" t="n">
         <v>-0.0377931524741033</v>
       </c>
       <c r="F169" t="n">
-        <v>0.00832425796244607</v>
+        <v>-0.0377931524741033</v>
       </c>
       <c r="G169" t="n">
         <v>-0.336257477767989</v>
       </c>
       <c r="H169" t="n">
-        <v>-5.36621356144848</v>
+        <v>-5.39275589436523</v>
       </c>
     </row>
     <row r="170">
@@ -60800,22 +60737,22 @@
         <v>-0.0374584383805767</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.00972195614806282</v>
+        <v>-0.00972218762293942</v>
       </c>
       <c r="D170" t="n">
-        <v>0.00907460123040016</v>
+        <v>0.00967955948269017</v>
       </c>
       <c r="E170" t="n">
         <v>-0.00995349415389057</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.0378168696346046</v>
+        <v>-0.00995349415389057</v>
       </c>
       <c r="G170" t="n">
         <v>0.0306670802736422</v>
       </c>
       <c r="H170" t="n">
-        <v>-5.36228813018997</v>
+        <v>-5.35630676214898</v>
       </c>
     </row>
     <row r="171">
@@ -60826,22 +60763,22 @@
         <v>-10.0099205844584</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.0074138424241097</v>
+        <v>-0.00741373562817405</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.00121125307853953</v>
+        <v>-0.0012114016905751</v>
       </c>
       <c r="E171" t="n">
         <v>0.00244139493704587</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.00277411274734884</v>
+        <v>0.00244139493704587</v>
       </c>
       <c r="G171" t="n">
         <v>-0.0166062944084659</v>
       </c>
       <c r="H171" t="n">
-        <v>-5.09034195853548</v>
+        <v>-5.12822149711878</v>
       </c>
     </row>
     <row r="172">
@@ -60852,22 +60789,22 @@
         <v>-14.2204930955712</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.00111462958277375</v>
+        <v>-0.00111459960527061</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.00793665259988474</v>
+        <v>-0.00855231431014536</v>
       </c>
       <c r="E172" t="n">
         <v>0.0245586757328429</v>
       </c>
       <c r="F172" t="n">
-        <v>-0.0528446438012971</v>
+        <v>0.0245586757328429</v>
       </c>
       <c r="G172" t="n">
         <v>0.212717460654744</v>
       </c>
       <c r="H172" t="n">
-        <v>-5.90836681080198</v>
+        <v>-5.88482892667453</v>
       </c>
     </row>
     <row r="173">
@@ -60878,22 +60815,22 @@
         <v>-7.54128464637599</v>
       </c>
       <c r="C173" t="n">
-        <v>0.00674632890755689</v>
+        <v>0.00674618924827097</v>
       </c>
       <c r="D173" t="n">
-        <v>0.0499049087507344</v>
+        <v>0.0471655867891849</v>
       </c>
       <c r="E173" t="n">
         <v>-0.00174962688279923</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0112383224588957</v>
+        <v>-0.00174962688279923</v>
       </c>
       <c r="G173" t="n">
         <v>0.033999521265681</v>
       </c>
       <c r="H173" t="n">
-        <v>-5.89996758989147</v>
+        <v>-5.80098095975731</v>
       </c>
     </row>
     <row r="174">
@@ -60904,22 +60841,22 @@
         <v>-3.9538939726808</v>
       </c>
       <c r="C174" t="n">
-        <v>0.00976105557200846</v>
+        <v>0.00976124869148265</v>
       </c>
       <c r="D174" t="n">
-        <v>0.00115868122340856</v>
+        <v>0.00463492418634681</v>
       </c>
       <c r="E174" t="n">
         <v>0.00504329050749419</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.00371112877623059</v>
+        <v>0.00504329050749419</v>
       </c>
       <c r="G174" t="n">
         <v>0.144006067381003</v>
       </c>
       <c r="H174" t="n">
-        <v>-6.02017290855498</v>
+        <v>-5.99956187630006</v>
       </c>
     </row>
     <row r="175">
@@ -60930,22 +60867,22 @@
         <v>-2.61869122174661</v>
       </c>
       <c r="C175" t="n">
-        <v>0.00905458801144565</v>
+        <v>0.00905448214457216</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.00876687939799137</v>
+        <v>-0.00817767811777825</v>
       </c>
       <c r="E175" t="n">
         <v>0.0190388818445211</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0253015368308542</v>
+        <v>0.0190388818445211</v>
       </c>
       <c r="G175" t="n">
         <v>0.119749050380003</v>
       </c>
       <c r="H175" t="n">
-        <v>-5.84301498955747</v>
+        <v>-5.95461521793583</v>
       </c>
     </row>
     <row r="176">
@@ -60956,22 +60893,22 @@
         <v>2.23899156057459</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0038778561724877</v>
+        <v>0.00387787021528307</v>
       </c>
       <c r="D176" t="n">
-        <v>0.00291383096625664</v>
+        <v>0.00233110544773663</v>
       </c>
       <c r="E176" t="n">
         <v>-0.0378831561337813</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.054187734513448</v>
+        <v>-0.0378831561337813</v>
       </c>
       <c r="G176" t="n">
         <v>-0.105761400423837</v>
       </c>
       <c r="H176" t="n">
-        <v>-7.52236692703898</v>
+        <v>-7.3640593500086</v>
       </c>
     </row>
     <row r="177">
@@ -60982,22 +60919,22 @@
         <v>8.9960824868188</v>
       </c>
       <c r="C177" t="n">
-        <v>0.00974705634044692</v>
+        <v>0.00974705247383945</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.00116690607997461</v>
+        <v>-0.00116690051679802</v>
       </c>
       <c r="E177" t="n">
         <v>0.0450957827643901</v>
       </c>
       <c r="F177" t="n">
-        <v>0.0728793874327183</v>
+        <v>0.0450957827643901</v>
       </c>
       <c r="G177" t="n">
         <v>0.0816600252457986</v>
       </c>
       <c r="H177" t="n">
-        <v>-5.24767533862548</v>
+        <v>-5.38858456326638</v>
       </c>
     </row>
     <row r="178">
@@ -61008,22 +60945,22 @@
         <v>7.227178241226</v>
       </c>
       <c r="C178" t="n">
-        <v>0.00454723058425266</v>
+        <v>0.00454732101409316</v>
       </c>
       <c r="D178" t="n">
-        <v>0.0052235469033155</v>
+        <v>0.00580057889790497</v>
       </c>
       <c r="E178" t="n">
         <v>-0.0120266448898656</v>
       </c>
       <c r="F178" t="n">
-        <v>0.00698476981466101</v>
+        <v>-0.0120266448898656</v>
       </c>
       <c r="G178" t="n">
         <v>-0.0378710760121326</v>
       </c>
       <c r="H178" t="n">
-        <v>-6.13486542582597</v>
+        <v>-6.15773005283913</v>
       </c>
     </row>
     <row r="179">
@@ -61034,22 +60971,22 @@
         <v>8.81458872945218</v>
       </c>
       <c r="C179" t="n">
-        <v>0.0054277974858028</v>
+        <v>0.00542763787328937</v>
       </c>
       <c r="D179" t="n">
-        <v>0.0390506161435042</v>
+        <v>0.0379555044730484</v>
       </c>
       <c r="E179" t="n">
         <v>0.0115668226838164</v>
       </c>
       <c r="F179" t="n">
-        <v>0.0247739974221384</v>
+        <v>0.0115668226838164</v>
       </c>
       <c r="G179" t="n">
         <v>0.0744808592020831</v>
       </c>
       <c r="H179" t="n">
-        <v>-5.32305313113247</v>
+        <v>-5.3753797667159</v>
       </c>
     </row>
     <row r="180">
@@ -61060,22 +60997,22 @@
         <v>10.1745036386484</v>
       </c>
       <c r="C180" t="n">
-        <v>0.00153326947851973</v>
+        <v>0.00153341430251075</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.0175944558112544</v>
+        <v>-0.0170267972326505</v>
       </c>
       <c r="E180" t="n">
         <v>0.00572889328886994</v>
       </c>
       <c r="F180" t="n">
-        <v>-0.00567521719939101</v>
+        <v>0.00572889328886994</v>
       </c>
       <c r="G180" t="n">
         <v>0.0408052888604225</v>
       </c>
       <c r="H180" t="n">
-        <v>-6.36267309214697</v>
+        <v>-6.36659587299368</v>
       </c>
     </row>
     <row r="181">
@@ -61086,22 +61023,22 @@
         <v>11.8989734834506</v>
       </c>
       <c r="C181" t="n">
-        <v>0.00196060334383485</v>
+        <v>0.00196065765279929</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.000567894394805979</v>
+        <v>-0.000567962377742592</v>
       </c>
       <c r="E181" t="n">
         <v>0.0134675905854929</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.0320987461289057</v>
+        <v>0.0134675905854929</v>
       </c>
       <c r="G181" t="n">
         <v>-0.0433610087214689</v>
       </c>
       <c r="H181" t="n">
-        <v>-6.48085201227848</v>
+        <v>-6.40131298908344</v>
       </c>
     </row>
     <row r="182">
@@ -61112,22 +61049,22 @@
         <v>11.6449985382698</v>
       </c>
       <c r="C182" t="n">
-        <v>0.00768128248062183</v>
+        <v>0.0076810481655043</v>
       </c>
       <c r="D182" t="n">
-        <v>0.0297563906481577</v>
+        <v>0.0292214842786893</v>
       </c>
       <c r="E182" t="n">
         <v>0.0240521748335798</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0596638803330203</v>
+        <v>0.0240521748335798</v>
       </c>
       <c r="G182" t="n">
         <v>0.0366056892541273</v>
       </c>
       <c r="H182" t="n">
-        <v>-5.51170341955296</v>
+        <v>-5.53072300615522</v>
       </c>
     </row>
     <row r="183">
@@ -61138,22 +61075,22 @@
         <v>13.067939458676</v>
       </c>
       <c r="C183" t="n">
-        <v>0.00495414815421302</v>
+        <v>0.00495434284355234</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.0365584146450915</v>
+        <v>-0.0359871603336801</v>
       </c>
       <c r="E183" t="n">
         <v>-0.00594145107824762</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.00363317678596076</v>
+        <v>-0.00594145107824762</v>
       </c>
       <c r="G183" t="n">
         <v>-0.0130681819906666</v>
       </c>
       <c r="H183" t="n">
-        <v>-5.42106392363946</v>
+        <v>-5.41200686169299</v>
       </c>
     </row>
     <row r="184">
@@ -61164,22 +61101,22 @@
         <v>12.6965156054602</v>
       </c>
       <c r="C184" t="n">
-        <v>0.00856444348862251</v>
+        <v>0.00856428608461712</v>
       </c>
       <c r="D184" t="n">
-        <v>0.068174927737179</v>
+        <v>0.0686718057687226</v>
       </c>
       <c r="E184" t="n">
         <v>0.0123597441713663</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0210159869830955</v>
+        <v>0.0123597441713663</v>
       </c>
       <c r="G184" t="n">
         <v>0.0594739339211579</v>
       </c>
       <c r="H184" t="n">
-        <v>-4.45039975629899</v>
+        <v>-4.49720461273373</v>
       </c>
     </row>
     <row r="185">
@@ -61190,22 +61127,22 @@
         <v>14.6655304031474</v>
       </c>
       <c r="C185" t="n">
-        <v>0.00173920570237396</v>
+        <v>0.0017394081940747</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.0352690199987729</v>
+        <v>-0.0381095596307008</v>
       </c>
       <c r="E185" t="n">
         <v>-0.0130620408330113</v>
       </c>
       <c r="F185" t="n">
-        <v>0.0302146004642658</v>
+        <v>-0.0130620408330113</v>
       </c>
       <c r="G185" t="n">
         <v>0.0203460300753013</v>
       </c>
       <c r="H185" t="n">
-        <v>-4.67831967501448</v>
+        <v>-4.60718837129951</v>
       </c>
     </row>
     <row r="186">
@@ -61216,22 +61153,22 @@
         <v>12.1780021797676</v>
       </c>
       <c r="C186" t="n">
-        <v>0.00393541180521506</v>
+        <v>0.00393531451218188</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.00554007988614025</v>
+        <v>-0.00388026023434174</v>
       </c>
       <c r="E186" t="n">
         <v>-0.0141451752507633</v>
       </c>
       <c r="F186" t="n">
-        <v>0.00825867685749149</v>
+        <v>-0.0141451752507633</v>
       </c>
       <c r="G186" t="n">
         <v>-0.118055087627139</v>
       </c>
       <c r="H186" t="n">
-        <v>-4.76347380871998</v>
+        <v>-4.72322956608429</v>
       </c>
     </row>
     <row r="187">
@@ -61242,22 +61179,22 @@
         <v>10.4462629474928</v>
       </c>
       <c r="C187" t="n">
-        <v>0.00511176163582139</v>
+        <v>0.00511183106942159</v>
       </c>
       <c r="D187" t="n">
-        <v>0.0206200059007227</v>
+        <v>0.0216936936298668</v>
       </c>
       <c r="E187" t="n">
         <v>0.0324143297790709</v>
       </c>
       <c r="F187" t="n">
-        <v>0.00476808003393625</v>
+        <v>0.0324143297790709</v>
       </c>
       <c r="G187" t="n">
         <v>0.036031229854121</v>
       </c>
       <c r="H187" t="n">
-        <v>-4.01023783577147</v>
+        <v>-3.96538786415106</v>
       </c>
     </row>
     <row r="188">
@@ -61268,22 +61205,22 @@
         <v>10.1025488940329</v>
       </c>
       <c r="C188" t="n">
-        <v>0.00476838659718215</v>
+        <v>0.00476820829518854</v>
       </c>
       <c r="D188" t="n">
-        <v>0.00807328579581235</v>
+        <v>0.00806877961811203</v>
       </c>
       <c r="E188" t="n">
         <v>-0.00363137770046951</v>
       </c>
       <c r="F188" t="n">
-        <v>0.00902693927551201</v>
+        <v>-0.00363137770046951</v>
       </c>
       <c r="G188" t="n">
         <v>0.00880923522242139</v>
       </c>
       <c r="H188" t="n">
-        <v>-4.82485048424497</v>
+        <v>-4.7820193142158</v>
       </c>
     </row>
     <row r="189">
@@ -61294,22 +61231,22 @@
         <v>10.8861050396561</v>
       </c>
       <c r="C189" t="n">
-        <v>0.0038188936708865</v>
+        <v>0.00381890971853061</v>
       </c>
       <c r="D189" t="n">
-        <v>0.0179713778830703</v>
+        <v>0.0174429215974898</v>
       </c>
       <c r="E189" t="n">
         <v>-0.00252965206324429</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.0636908921804373</v>
+        <v>-0.00252965206324429</v>
       </c>
       <c r="G189" t="n">
         <v>-0.0176727108285553</v>
       </c>
       <c r="H189" t="n">
-        <v>-4.48015274071848</v>
+        <v>-4.47382507655457</v>
       </c>
     </row>
     <row r="190">
@@ -61320,22 +61257,22 @@
         <v>10.4318832422743</v>
       </c>
       <c r="C190" t="n">
-        <v>0.00300892797411301</v>
+        <v>0.00300906858485028</v>
       </c>
       <c r="D190" t="n">
-        <v>0.0042105480551422</v>
+        <v>0.0042104068492903</v>
       </c>
       <c r="E190" t="n">
         <v>0.0212092871323497</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.0315897182412872</v>
+        <v>0.0212092871323497</v>
       </c>
       <c r="G190" t="n">
         <v>-0.0348108112567687</v>
       </c>
       <c r="H190" t="n">
-        <v>-4.14285998494997</v>
+        <v>-4.16822517896835</v>
       </c>
     </row>
     <row r="191">
@@ -61346,22 +61283,22 @@
         <v>10.8176771287655</v>
       </c>
       <c r="C191" t="n">
-        <v>0.00383153244572476</v>
+        <v>0.00383147928252559</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.00795775667636889</v>
+        <v>-0.00795753140397837</v>
       </c>
       <c r="E191" t="n">
         <v>-0.00269355339291621</v>
       </c>
       <c r="F191" t="n">
-        <v>0.0137185262785193</v>
+        <v>-0.00269355339291621</v>
       </c>
       <c r="G191" t="n">
         <v>0.0475091470675197</v>
       </c>
       <c r="H191" t="n">
-        <v>-4.29998472309748</v>
+        <v>-4.2905845402741</v>
       </c>
     </row>
     <row r="192">
@@ -61372,22 +61309,22 @@
         <v>7.02275304173973</v>
       </c>
       <c r="C192" t="n">
-        <v>0.00315845547484006</v>
+        <v>0.00315845288176853</v>
       </c>
       <c r="D192" t="n">
-        <v>0.00264557740471982</v>
+        <v>0.00211754201058856</v>
       </c>
       <c r="E192" t="n">
         <v>0.00726346587196591</v>
       </c>
       <c r="F192" t="n">
-        <v>-0.00348360386041602</v>
+        <v>0.00726346587196591</v>
       </c>
       <c r="G192" t="n">
         <v>0.036574578750443</v>
       </c>
       <c r="H192" t="n">
-        <v>-3.22046857715297</v>
+        <v>-3.18433463135689</v>
       </c>
     </row>
     <row r="193">
@@ -61398,22 +61335,22 @@
         <v>12.1191095414079</v>
       </c>
       <c r="C193" t="n">
-        <v>0.00375924390514637</v>
+        <v>0.00375927239401541</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.00585423241596628</v>
+        <v>-0.00532208866325412</v>
       </c>
       <c r="E193" t="n">
         <v>0.00920830538580919</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0107339918966671</v>
+        <v>0.00920830538580919</v>
       </c>
       <c r="G193" t="n">
         <v>0.0416293239017307</v>
       </c>
       <c r="H193" t="n">
-        <v>-2.65592627177247</v>
+        <v>-2.64087301993365</v>
       </c>
     </row>
     <row r="194">
@@ -61424,22 +61361,22 @@
         <v>9.00616947117413</v>
       </c>
       <c r="C194" t="n">
-        <v>0.00729176664900599</v>
+        <v>0.00729167631806771</v>
       </c>
       <c r="D194" t="n">
-        <v>0.00476693297504482</v>
+        <v>0.00423953085674222</v>
       </c>
       <c r="E194" t="n">
-        <v>0.00143848473415176</v>
+        <v>0.00116270359410819</v>
       </c>
       <c r="F194" t="n">
-        <v>0.0374820138940937</v>
+        <v>0.00116270359410819</v>
       </c>
       <c r="G194" t="n">
         <v>-0.00725069817916157</v>
       </c>
       <c r="H194" t="n">
-        <v>-1.95265024826498</v>
+        <v>-1.89318238178843</v>
       </c>
     </row>
     <row r="195">
@@ -61450,22 +61387,22 @@
         <v>6.58843689063733</v>
       </c>
       <c r="C195" t="n">
-        <v>0.00192027850321086</v>
+        <v>0.00192034486147286</v>
       </c>
       <c r="D195" t="n">
-        <v>0.00158652828967565</v>
+        <v>0.002115353837008</v>
       </c>
       <c r="E195" t="n">
-        <v>-0.0113075352510696</v>
+        <v>-0.012215518387773</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.0244789202619415</v>
+        <v>-0.012215518387773</v>
       </c>
       <c r="G195" t="n">
         <v>0.0103893625652871</v>
       </c>
       <c r="H195" t="n">
-        <v>-2.33783893965948</v>
+        <v>-2.27045071128418</v>
       </c>
     </row>
     <row r="196">
@@ -61476,22 +61413,22 @@
         <v>7.59403684482851</v>
       </c>
       <c r="C196" t="n">
-        <v>0.00429561700724612</v>
+        <v>0.00429570734468765</v>
       </c>
       <c r="D196" t="n">
-        <v>0.00421271190986605</v>
+        <v>0.0052603438187111</v>
       </c>
       <c r="E196" t="n">
-        <v>0.0164839963027914</v>
+        <v>0.010180336981036</v>
       </c>
       <c r="F196" t="n">
-        <v>0.0223654633826289</v>
+        <v>0.010180336981036</v>
       </c>
       <c r="G196" t="n">
         <v>0.121472537122419</v>
       </c>
       <c r="H196" t="n">
-        <v>-1.96225657147897</v>
+        <v>-1.92435711744495</v>
       </c>
     </row>
     <row r="197">
@@ -61502,22 +61439,22 @@
         <v>8.63317524256372</v>
       </c>
       <c r="C197" t="n">
-        <v>0.00145011135716988</v>
+        <v>0.00145004931556336</v>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>-0.0015805749147253</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.0130858262783109</v>
+        <v>-0.00922152999928194</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.00502269482843687</v>
+        <v>-0.00922152999928194</v>
       </c>
       <c r="G197" t="n">
         <v>0.0201805938894051</v>
       </c>
       <c r="H197" t="n">
-        <v>-2.34638349104248</v>
+        <v>-2.47333436168272</v>
       </c>
     </row>
     <row r="198">
@@ -61528,22 +61465,22 @@
         <v>8.06956065856092</v>
       </c>
       <c r="C198" t="n">
-        <v>0.00223705306305799</v>
+        <v>0.00223715669087099</v>
       </c>
       <c r="D198" t="n">
-        <v>0.00210192295275347</v>
+        <v>0.00210295970222107</v>
       </c>
       <c r="E198" t="n">
-        <v>0.00143764509071342</v>
+        <v>0.00437523102886583</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.00232738513365138</v>
+        <v>0.00437523102886583</v>
       </c>
       <c r="G198" t="n">
         <v>-0.0769749484946862</v>
       </c>
       <c r="H198" t="n">
-        <v>-2.69632701579896</v>
+        <v>-2.6189554072065</v>
       </c>
     </row>
     <row r="199">
@@ -61554,22 +61491,22 @@
         <v>9.05585515371609</v>
       </c>
       <c r="C199" t="n">
-        <v>0.00332652082748197</v>
+        <v>0.00332639820178038</v>
       </c>
       <c r="D199" t="n">
-        <v>0.0220984094374463</v>
+        <v>0.0226125776858312</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0160256559811982</v>
+        <v>0.0190037190778964</v>
       </c>
       <c r="F199" t="n">
-        <v>-0.0143624894661523</v>
+        <v>0.0190037190778964</v>
       </c>
       <c r="G199" t="n">
         <v>-0.0641632543955213</v>
       </c>
       <c r="H199" t="n">
-        <v>-2.40611719295648</v>
+        <v>-2.36617230828925</v>
       </c>
     </row>
     <row r="200">
@@ -61580,22 +61517,22 @@
         <v>7.81178364803131</v>
       </c>
       <c r="C200" t="n">
-        <v>0.00272413947566186</v>
+        <v>0.00272413406015737</v>
       </c>
       <c r="D200" t="n">
-        <v>0.0156810632299678</v>
+        <v>0.016178688668103</v>
       </c>
       <c r="E200" t="n">
-        <v>-0.00468275750227143</v>
+        <v>-0.0050624878003962</v>
       </c>
       <c r="F200" t="n">
-        <v>0.00997672696248042</v>
+        <v>-0.0050624878003962</v>
       </c>
       <c r="G200" t="n">
         <v>0.0129881327249288</v>
       </c>
       <c r="H200" t="n">
-        <v>-0.969566476499982</v>
+        <v>-0.925906204187042</v>
       </c>
     </row>
     <row r="201">
@@ -61606,22 +61543,22 @@
         <v>6.89521153941551</v>
       </c>
       <c r="C201" t="n">
-        <v>0.000544749024339986</v>
+        <v>0.000544715387235328</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.0340023529790576</v>
+        <v>-0.0345257653907325</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.0213467299405687</v>
+        <v>-0.022348980341472</v>
       </c>
       <c r="F201" t="n">
-        <v>-0.0412192472408233</v>
+        <v>-0.022348980341472</v>
       </c>
       <c r="G201" t="n">
         <v>-0.0890780032471694</v>
       </c>
       <c r="H201" t="n">
-        <v>-1.32830579034247</v>
+        <v>-1.38406536922279</v>
       </c>
     </row>
     <row r="202">
@@ -61632,22 +61569,22 @@
         <v>4.21667153540269</v>
       </c>
       <c r="C202" t="n">
-        <v>0.00348488276541037</v>
+        <v>0.00348490666771983</v>
       </c>
       <c r="D202" t="n">
-        <v>0.00983968857116757</v>
+        <v>0.00881300756571601</v>
       </c>
       <c r="E202" t="n">
-        <v>0.0164716004621175</v>
+        <v>0.0165738626518035</v>
       </c>
       <c r="F202" t="n">
-        <v>0.0283014714082306</v>
+        <v>0.0165738626518035</v>
       </c>
       <c r="G202" t="n">
         <v>0.030422661117556</v>
       </c>
       <c r="H202" t="n">
-        <v>-0.528269021963975</v>
+        <v>-0.471950099391557</v>
       </c>
     </row>
     <row r="203">
@@ -61658,22 +61595,22 @@
         <v>8.60598643683988</v>
       </c>
       <c r="C203" t="n">
-        <v>0.00141664881455839</v>
+        <v>0.00141661199688858</v>
       </c>
       <c r="D203" t="n">
-        <v>0.00463904617558697</v>
+        <v>0.00515725976261638</v>
       </c>
       <c r="E203" t="n">
-        <v>-0.00281786426487063</v>
+        <v>0.00108525489274669</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.00240651677986303</v>
+        <v>0.00108525489274669</v>
       </c>
       <c r="G203" t="n">
         <v>0.00447948466131898</v>
       </c>
       <c r="H203" t="n">
-        <v>-1.15764954682047</v>
+        <v>-1.07758226063235</v>
       </c>
     </row>
     <row r="204">
@@ -61684,22 +61621,22 @@
         <v>7.26426394979908</v>
       </c>
       <c r="C204" t="n">
-        <v>0.0048256062102201</v>
+        <v>0.00482553171557498</v>
       </c>
       <c r="D204" t="n">
-        <v>0.0221793724465966</v>
+        <v>0.0226834335463266</v>
       </c>
       <c r="E204" t="n">
-        <v>0.00857320682893814</v>
+        <v>0.00576276519256158</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.0212563868658284</v>
+        <v>0.00576276519256158</v>
       </c>
       <c r="G204" t="n">
         <v>0.135308744708579</v>
       </c>
       <c r="H204" t="n">
-        <v>-1.03844771161896</v>
+        <v>-1.01175320884609</v>
       </c>
     </row>
     <row r="205">
@@ -61710,22 +61647,22 @@
         <v>7.62980764764127</v>
       </c>
       <c r="C205" t="n">
-        <v>0.00274412325626372</v>
+        <v>0.00274432771105992</v>
       </c>
       <c r="D205" t="n">
-        <v>0.00100695260488415</v>
+        <v>0.000503827726259232</v>
       </c>
       <c r="E205" t="n">
-        <v>0.00451170064905515</v>
+        <v>0.00271775559853626</v>
       </c>
       <c r="F205" t="n">
-        <v>0.0195212214124725</v>
+        <v>0.00271775559853626</v>
       </c>
       <c r="G205" t="n">
         <v>0.0272518243116755</v>
       </c>
       <c r="H205" t="n">
-        <v>-1.88854396069047</v>
+        <v>-1.89887355542586</v>
       </c>
     </row>
     <row r="206">
@@ -61736,22 +61673,22 @@
         <v>6.69248825892048</v>
       </c>
       <c r="C206" t="n">
-        <v>0.00273630661653446</v>
+        <v>0.00273620401453023</v>
       </c>
       <c r="D206" t="n">
-        <v>0.00451132760867434</v>
+        <v>0.00501261584535584</v>
       </c>
       <c r="E206" t="n">
-        <v>-0.0137061135676522</v>
+        <v>-0.0124856069714134</v>
       </c>
       <c r="F206" t="n">
-        <v>0.0232364852173266</v>
+        <v>-0.0124856069714134</v>
       </c>
       <c r="G206" t="n">
         <v>0.0264509388385337</v>
       </c>
       <c r="H206" t="n">
-        <v>-2.86513877465896</v>
+        <v>-2.83132900762463</v>
       </c>
     </row>
     <row r="207">
@@ -61762,22 +61699,22 @@
         <v>7.02677990103268</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.0010355338608905</v>
+        <v>-0.00103553469072182</v>
       </c>
       <c r="D207" t="n">
-        <v>0.00597902754480373</v>
+        <v>0.00597909157874454</v>
       </c>
       <c r="E207" t="n">
-        <v>-0.00115028774451353</v>
+        <v>-0.00339920148929007</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.0450770651518768</v>
+        <v>-0.00339920148929007</v>
       </c>
       <c r="G207" t="n">
         <v>0.00101721578742797</v>
       </c>
       <c r="H207" t="n">
-        <v>-3.71773935878547</v>
+        <v>-3.7349330824924</v>
       </c>
     </row>
     <row r="208">
@@ -61788,22 +61725,22 @@
         <v>4.95503822300688</v>
       </c>
       <c r="C208" t="n">
-        <v>0.00388393484037763</v>
+        <v>0.00388392693324846</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.0136367213542128</v>
+        <v>-0.0141491349604124</v>
       </c>
       <c r="E208" t="n">
-        <v>0.00795333487919425</v>
+        <v>0.0120056963011201</v>
       </c>
       <c r="F208" t="n">
-        <v>0.0548809705107036</v>
+        <v>0.0120056963011201</v>
       </c>
       <c r="G208" t="n">
         <v>0.0400840100930564</v>
       </c>
       <c r="H208" t="n">
-        <v>-4.37471585019298</v>
+        <v>-4.29380932224416</v>
       </c>
     </row>
     <row r="209">
@@ -61814,22 +61751,22 @@
         <v>4.62997466757907</v>
       </c>
       <c r="C209" t="n">
-        <v>0.00685365624141809</v>
+        <v>0.00685366735420079</v>
       </c>
       <c r="D209" t="n">
-        <v>0.030841986518138</v>
+        <v>0.0303821304232228</v>
       </c>
       <c r="E209" t="n">
-        <v>0.0310058681901939</v>
+        <v>0.0240820375105617</v>
       </c>
       <c r="F209" t="n">
-        <v>0.0366731051619196</v>
+        <v>0.0240820375105617</v>
       </c>
       <c r="G209" t="n">
         <v>-0.0388378589213865</v>
       </c>
       <c r="H209" t="n">
-        <v>-2.54731578623046</v>
+        <v>-2.58978512071794</v>
       </c>
     </row>
     <row r="210">
@@ -61840,22 +61777,22 @@
         <v>3.75402864701626</v>
       </c>
       <c r="C210" t="n">
-        <v>0.00187463003170851</v>
+        <v>0.00187463647025954</v>
       </c>
       <c r="D210" t="n">
-        <v>0</v>
+        <v>0.000978837140867661</v>
       </c>
       <c r="E210" t="n">
-        <v>-0.0162864407900924</v>
+        <v>-0.0130121580385234</v>
       </c>
       <c r="F210" t="n">
-        <v>-0.00753749273064575</v>
+        <v>-0.0130121580385234</v>
       </c>
       <c r="G210" t="n">
         <v>-0.0738631382383161</v>
       </c>
       <c r="H210" t="n">
-        <v>-3.80976036957797</v>
+        <v>-3.8054554264217</v>
       </c>
     </row>
     <row r="211">
@@ -61866,22 +61803,22 @@
         <v>4.21924411688945</v>
       </c>
       <c r="C211" t="n">
-        <v>0.00169071206408233</v>
+        <v>0.00169058523754639</v>
       </c>
       <c r="D211" t="n">
-        <v>-0.000489682609932984</v>
+        <v>-0.000489641655337714</v>
       </c>
       <c r="E211" t="n">
-        <v>-0.00728711623676848</v>
+        <v>-0.00495564199015508</v>
       </c>
       <c r="F211" t="n">
-        <v>-0.0186812672491605</v>
+        <v>-0.00495564199015508</v>
       </c>
       <c r="G211" t="n">
         <v>-0.0887336798598186</v>
       </c>
       <c r="H211" t="n">
-        <v>-5.85538285617946</v>
+        <v>-5.73159443822148</v>
       </c>
     </row>
     <row r="212">
@@ -61892,22 +61829,22 @@
         <v>3.00213403218365</v>
       </c>
       <c r="C212" t="n">
-        <v>0.0062098648075839</v>
+        <v>0.00620999265161792</v>
       </c>
       <c r="D212" t="n">
-        <v>0.00341626089888791</v>
+        <v>0.00341614643810928</v>
       </c>
       <c r="E212" t="n">
-        <v>0.0394297728568684</v>
+        <v>0.0390587777817961</v>
       </c>
       <c r="F212" t="n">
-        <v>0.0433803945631528</v>
+        <v>0.0390587777817961</v>
       </c>
       <c r="G212" t="n">
         <v>0.0585358976114678</v>
       </c>
       <c r="H212" t="n">
-        <v>-3.40953201129498</v>
+        <v>-3.18874467425624</v>
       </c>
     </row>
     <row r="213">
@@ -61918,22 +61855,22 @@
         <v>-0.744194436999147</v>
       </c>
       <c r="C213" t="n">
-        <v>0.00192824000958058</v>
+        <v>0.00192826880978103</v>
       </c>
       <c r="D213" t="n">
-        <v>0.017266999164514</v>
+        <v>0.0167954612316965</v>
       </c>
       <c r="E213" t="n">
-        <v>-0.00159087160693883</v>
+        <v>-0.00244450571756349</v>
       </c>
       <c r="F213" t="n">
-        <v>0.00596442221917748</v>
+        <v>-0.00244450571756349</v>
       </c>
       <c r="G213" t="n">
         <v>0.0604477465928843</v>
       </c>
       <c r="H213" t="n">
-        <v>-3.04922610752648</v>
+        <v>-3.21353727226802</v>
       </c>
     </row>
     <row r="214">
@@ -61944,22 +61881,22 @@
         <v>-2.33656633264195</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.000525009310194058</v>
+        <v>-0.000525127197872344</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.0190625853789834</v>
+        <v>-0.0190719374853883</v>
       </c>
       <c r="E214" t="n">
-        <v>-0.0456898505970429</v>
+        <v>-0.048460642160908</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.00965677935361153</v>
+        <v>-0.048460642160908</v>
       </c>
       <c r="G214" t="n">
         <v>0.0105476195540355</v>
       </c>
       <c r="H214" t="n">
-        <v>-4.69838875148096</v>
+        <v>-4.65785860181778</v>
       </c>
     </row>
     <row r="215">
@@ -61970,22 +61907,22 @@
         <v>-3.79077513951276</v>
       </c>
       <c r="C215" t="n">
-        <v>0.00139736095685183</v>
+        <v>0.0013974289166292</v>
       </c>
       <c r="D215" t="n">
-        <v>0.00437949885894096</v>
+        <v>0.00486613728475849</v>
       </c>
       <c r="E215" t="n">
-        <v>0.0261051714379965</v>
+        <v>0.0244704028690919</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.0116737172533661</v>
+        <v>0.0244704028690919</v>
       </c>
       <c r="G215" t="n">
         <v>-0.0633281262692282</v>
       </c>
       <c r="H215" t="n">
-        <v>-4.83399133864047</v>
+        <v>-4.79796617620954</v>
       </c>
     </row>
     <row r="216">
@@ -61996,22 +61933,22 @@
         <v>1.30277506870443</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.000194591030628466</v>
+        <v>-0.000194545210717045</v>
       </c>
       <c r="D216" t="n">
-        <v>0.00916110958507321</v>
+        <v>0.00916113955884423</v>
       </c>
       <c r="E216" t="n">
-        <v>-0.00645722248476854</v>
+        <v>-0.00142874269542226</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.00679345032470824</v>
+        <v>-0.00142874269542226</v>
       </c>
       <c r="G216" t="n">
         <v>0.0242467678396556</v>
       </c>
       <c r="H216" t="n">
-        <v>-5.66188296457698</v>
+        <v>-5.61652682456831</v>
       </c>
     </row>
     <row r="217">
@@ -62022,22 +61959,22 @@
         <v>2.07464795042964</v>
       </c>
       <c r="C217" t="n">
-        <v>0.00341485332887714</v>
+        <v>0.0034147744028532</v>
       </c>
       <c r="D217" t="n">
-        <v>0.0262941303940103</v>
+        <v>0.0262941149215434</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0170117319349323</v>
+        <v>0.0166010384473863</v>
       </c>
       <c r="F217" t="n">
-        <v>-0.0568184628648911</v>
+        <v>0.0166010384473863</v>
       </c>
       <c r="G217" t="n">
         <v>-0.0183087154604173</v>
       </c>
       <c r="H217" t="n">
-        <v>-4.79509441164447</v>
+        <v>-4.77523260751908</v>
       </c>
     </row>
     <row r="218">
@@ -62048,22 +61985,22 @@
         <v>-0.543045698708175</v>
       </c>
       <c r="C218" t="n">
-        <v>0.00308655386760126</v>
+        <v>0.00308659115249377</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.0142861158086873</v>
+        <v>-0.0142861654883841</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.017728329042785</v>
+        <v>-0.0180726098595656</v>
       </c>
       <c r="F218" t="n">
-        <v>0.0214418122768016</v>
+        <v>-0.0180726098595656</v>
       </c>
       <c r="G218" t="n">
         <v>0.00296621363890015</v>
       </c>
       <c r="H218" t="n">
-        <v>-5.08716577531798</v>
+        <v>-5.05307079337485</v>
       </c>
     </row>
     <row r="219">
@@ -62074,22 +62011,22 @@
         <v>1.11441663212102</v>
       </c>
       <c r="C219" t="n">
-        <v>0.00658806571059678</v>
+        <v>0.00658809203894517</v>
       </c>
       <c r="D219" t="n">
-        <v>0.013621734361525</v>
+        <v>0.0136218433924524</v>
       </c>
       <c r="E219" t="n">
-        <v>0.0376733763135757</v>
+        <v>0.0357373001200711</v>
       </c>
       <c r="F219" t="n">
-        <v>0.0242309197221147</v>
+        <v>0.0357373001200711</v>
       </c>
       <c r="G219" t="n">
         <v>0.0435523345340796</v>
       </c>
       <c r="H219" t="n">
-        <v>-2.50747805713947</v>
+        <v>-2.57617421588662</v>
       </c>
     </row>
     <row r="220">
@@ -62100,22 +62037,22 @@
         <v>0.137463273116219</v>
       </c>
       <c r="C220" t="n">
-        <v>0.00107542087313206</v>
+        <v>0.0010754332434777</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.00566844574317393</v>
+        <v>-0.0066193974898443</v>
       </c>
       <c r="E220" t="n">
-        <v>-0.0159977456062892</v>
+        <v>-0.00612633381219041</v>
       </c>
       <c r="F220" t="n">
-        <v>-0.0202864345601821</v>
+        <v>-0.00612633381219041</v>
       </c>
       <c r="G220" t="n">
         <v>0.0490264950770323</v>
       </c>
       <c r="H220" t="n">
-        <v>-4.00526966349096</v>
+        <v>-3.94071497807238</v>
       </c>
     </row>
     <row r="221">
@@ -62126,22 +62063,22 @@
         <v>-5.17752422734858</v>
       </c>
       <c r="C221" t="n">
-        <v>0.00269546305955082</v>
+        <v>0.0026953989343701</v>
       </c>
       <c r="D221" t="n">
-        <v>-0.000945580821809955</v>
+        <v>-0.00047308617024111</v>
       </c>
       <c r="E221" t="n">
-        <v>0.00514880084021385</v>
+        <v>0.00178610805699186</v>
       </c>
       <c r="F221" t="n">
-        <v>0.00868357451894042</v>
+        <v>0.00178610805699186</v>
       </c>
       <c r="G221" t="n">
         <v>-0.00805832111371618</v>
       </c>
       <c r="H221" t="n">
-        <v>-3.75552483714646</v>
+        <v>-3.47285179155715</v>
       </c>
     </row>
     <row r="222">
@@ -62152,22 +62089,22 @@
         <v>-12.0930854724224</v>
       </c>
       <c r="C222" t="n">
-        <v>0.00320951134441216</v>
+        <v>0.00320955049384253</v>
       </c>
       <c r="D222" t="n">
-        <v>0.032042212825556</v>
+        <v>0.0325001358364307</v>
       </c>
       <c r="E222" t="n">
-        <v>0.0290957515284207</v>
+        <v>0.023219661290665</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.0123061307091197</v>
+        <v>0.023219661290665</v>
       </c>
       <c r="G222" t="n">
         <v>-0.0383311688951053</v>
       </c>
       <c r="H222" t="n">
-        <v>-2.65112075978896</v>
+        <v>-2.73587404173793</v>
       </c>
     </row>
     <row r="223">
@@ -62178,22 +62115,22 @@
         <v>-7.71985615264019</v>
       </c>
       <c r="C223" t="n">
-        <v>0.00150200360302222</v>
+        <v>0.00150212538133943</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.0200761755962748</v>
+        <v>-0.0200760893605736</v>
       </c>
       <c r="E223" t="n">
-        <v>-0.0271734538337389</v>
+        <v>-0.0246101106564112</v>
       </c>
       <c r="F223" t="n">
-        <v>0.00370730879176229</v>
+        <v>-0.0246101106564112</v>
       </c>
       <c r="G223" t="n">
         <v>-0.0765403233670225</v>
       </c>
       <c r="H223" t="n">
-        <v>-2.94150479976247</v>
+        <v>-2.9465810653037</v>
       </c>
     </row>
     <row r="224">
@@ -62204,22 +62141,22 @@
         <v>-6.590218249621</v>
       </c>
       <c r="C224" t="n">
-        <v>0.00242743325857209</v>
+        <v>0.00242737111743008</v>
       </c>
       <c r="D224" t="n">
-        <v>0.0219197030065512</v>
+        <v>0.0219196501452661</v>
       </c>
       <c r="E224" t="n">
-        <v>0.00413600380447487</v>
+        <v>0.0035004520964721</v>
       </c>
       <c r="F224" t="n">
-        <v>0.010070093425246</v>
+        <v>0.0035004520964721</v>
       </c>
       <c r="G224" t="n">
         <v>-0.0251858499682731</v>
       </c>
       <c r="H224" t="n">
-        <v>-3.25115369854095</v>
+        <v>-3.12074917287546</v>
       </c>
     </row>
     <row r="225">
@@ -62230,22 +62167,22 @@
         <v>-3.9876413563878</v>
       </c>
       <c r="C225" t="n">
-        <v>0.000939564891765166</v>
+        <v>0.000939505252803841</v>
       </c>
       <c r="D225" t="n">
-        <v>0.0117331773516982</v>
+        <v>0.0112868746886647</v>
       </c>
       <c r="E225" t="n">
-        <v>0.0132588847618447</v>
+        <v>0.0129131651955783</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.0556997379084798</v>
+        <v>0.0129131651955783</v>
       </c>
       <c r="G225" t="n">
         <v>0.0513219855275935</v>
       </c>
       <c r="H225" t="n">
-        <v>-2.77388765408948</v>
+        <v>-2.90100741214022</v>
       </c>
     </row>
     <row r="226">
@@ -62256,22 +62193,22 @@
         <v>-3.0454286032606</v>
       </c>
       <c r="C226" t="n">
-        <v>0.0020333339339107</v>
+        <v>0.00203337419897576</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.0179156505110596</v>
+        <v>-0.016988835452552</v>
       </c>
       <c r="E226" t="n">
-        <v>-0.00217527941742279</v>
+        <v>0.00710419650265948</v>
       </c>
       <c r="F226" t="n">
-        <v>0.0349181701771268</v>
+        <v>0.00710419650265948</v>
       </c>
       <c r="G226" t="n">
         <v>0.0463684728515021</v>
       </c>
       <c r="H226" t="n">
-        <v>-3.00341645012796</v>
+        <v>-2.81711795069599</v>
       </c>
     </row>
     <row r="227">
@@ -62282,22 +62219,22 @@
         <v>-1.70306929909741</v>
       </c>
       <c r="C227" t="n">
-        <v>0.00365171176639745</v>
+        <v>0.00365163473370078</v>
       </c>
       <c r="D227" t="n">
-        <v>0.0263895207779106</v>
+        <v>0.0259420010928144</v>
       </c>
       <c r="E227" t="n">
-        <v>0.00382040032222708</v>
+        <v>-0.00420725377762121</v>
       </c>
       <c r="F227" t="n">
-        <v>0.0198726280199963</v>
+        <v>-0.00420725377762121</v>
       </c>
       <c r="G227" t="n">
         <v>-0.0653831762986785</v>
       </c>
       <c r="H227" t="n">
-        <v>-2.48087671909847</v>
+        <v>-2.50486525851375</v>
       </c>
     </row>
     <row r="228">
@@ -62308,22 +62245,22 @@
         <v>-2.28678727465521</v>
       </c>
       <c r="C228" t="n">
-        <v>0.00196237335485705</v>
+        <v>0.00196237395122623</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.010393246616923</v>
+        <v>-0.0108501039100259</v>
       </c>
       <c r="E228" t="n">
-        <v>0.00887802704178764</v>
+        <v>0.00690479172005176</v>
       </c>
       <c r="F228" t="n">
-        <v>0.00900401464676115</v>
+        <v>0.00690479172005176</v>
       </c>
       <c r="G228" t="n">
         <v>-0.0650292710964999</v>
       </c>
       <c r="H228" t="n">
-        <v>-2.64622398682496</v>
+        <v>-2.60828711131954</v>
       </c>
     </row>
     <row r="229">
@@ -62334,22 +62271,22 @@
         <v>-4.29754734006501</v>
       </c>
       <c r="C229" t="n">
-        <v>0.00102678989030203</v>
+        <v>0.00102685158242899</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.00408358297485645</v>
+        <v>-0.00362985804913052</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.0270714663402973</v>
+        <v>-0.0252123048262485</v>
       </c>
       <c r="F229" t="n">
-        <v>0.00101011490509606</v>
+        <v>-0.0252123048262485</v>
       </c>
       <c r="G229" t="n">
         <v>0.0293574973295208</v>
       </c>
       <c r="H229" t="n">
-        <v>-3.95236987560247</v>
+        <v>-3.88569974683031</v>
       </c>
     </row>
     <row r="230">
@@ -62360,22 +62297,22 @@
         <v>-3.28530356832982</v>
       </c>
       <c r="C230" t="n">
-        <v>0.00654931874661013</v>
+        <v>0.00654938899218571</v>
       </c>
       <c r="D230" t="n">
-        <v>0.0312138440291108</v>
+        <v>0.0312140511796839</v>
       </c>
       <c r="E230" t="n">
-        <v>0.0390899851980411</v>
+        <v>0.0388373948595255</v>
       </c>
       <c r="F230" t="n">
-        <v>0.00235399837471206</v>
+        <v>0.0388373948595255</v>
       </c>
       <c r="G230" t="n">
         <v>-0.028754045063673</v>
       </c>
       <c r="H230" t="n">
-        <v>-1.10044338447396</v>
+        <v>-0.856886362694076</v>
       </c>
     </row>
     <row r="231">
@@ -62386,22 +62323,22 @@
         <v>-4.49529633011162</v>
       </c>
       <c r="C231" t="n">
-        <v>0.00547487653411149</v>
+        <v>0.00547477452452938</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.00352879675490758</v>
+        <v>-0.00352891168044689</v>
       </c>
       <c r="E231" t="n">
-        <v>-0.00221862513167448</v>
+        <v>-0.00530963676992968</v>
       </c>
       <c r="F231" t="n">
-        <v>0.0383154082992618</v>
+        <v>-0.00530963676992968</v>
       </c>
       <c r="G231" t="n">
         <v>0.0726243855615536</v>
       </c>
       <c r="H231" t="n">
-        <v>-1.50559454494748</v>
+        <v>-1.41057498526182</v>
       </c>
     </row>
     <row r="232">
@@ -62412,22 +62349,22 @@
         <v>-1.89222224138243</v>
       </c>
       <c r="C232" t="n">
-        <v>0.00279262220843091</v>
+        <v>0.00279252513991235</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.0111510828802821</v>
+        <v>-0.0107001154021731</v>
       </c>
       <c r="E232" t="n">
-        <v>0.00242903845444786</v>
+        <v>-0.00321659741603852</v>
       </c>
       <c r="F232" t="n">
-        <v>-0.0731199123602684</v>
+        <v>-0.00321659741603852</v>
       </c>
       <c r="G232" t="n">
         <v>-0.0141312195577967</v>
       </c>
       <c r="H232" t="n">
-        <v>-2.42787081470198</v>
+        <v>-2.5252803612876</v>
       </c>
     </row>
     <row r="233">
@@ -62438,22 +62375,22 @@
         <v>-1.62561563291323</v>
       </c>
       <c r="C233" t="n">
-        <v>0.000957062325212199</v>
+        <v>0.00095721829928852</v>
       </c>
       <c r="D233" t="n">
-        <v>0.00752553474366824</v>
+        <v>0.00708269828493169</v>
       </c>
       <c r="E233" t="n">
-        <v>-0.0146586717190429</v>
+        <v>-0.00602686703880373</v>
       </c>
       <c r="F233" t="n">
-        <v>-0.0206912415632301</v>
+        <v>-0.00602686703880373</v>
       </c>
       <c r="G233" t="n">
         <v>0.0103062549515398</v>
       </c>
       <c r="H233" t="n">
-        <v>-2.70750839065946</v>
+        <v>-2.77143161800838</v>
       </c>
     </row>
     <row r="234">
@@ -62464,22 +62401,22 @@
         <v>0.32301206473396</v>
       </c>
       <c r="C234" t="n">
-        <v>0.00128450921613599</v>
+        <v>0.00128450923829426</v>
       </c>
       <c r="D234" t="n">
-        <v>0.00264907356277622</v>
+        <v>0.00264910069639601</v>
       </c>
       <c r="E234" t="n">
-        <v>-0.0000794311546794546</v>
+        <v>-0.00206377813191683</v>
       </c>
       <c r="F234" t="n">
-        <v>0.0261043327423183</v>
+        <v>-0.00206377813191683</v>
       </c>
       <c r="G234" t="n">
         <v>-0.00292703038604003</v>
       </c>
       <c r="H234" t="n">
-        <v>-2.83547966682098</v>
+        <v>-2.78794485801913</v>
       </c>
     </row>
     <row r="235">
@@ -62490,22 +62427,22 @@
         <v>-4.23753096738785</v>
       </c>
       <c r="C235" t="n">
-        <v>0.00228441136833002</v>
+        <v>0.00228433951153395</v>
       </c>
       <c r="D235" t="n">
-        <v>0.026646960527315</v>
+        <v>0.0266468648883151</v>
       </c>
       <c r="E235" t="n">
-        <v>0.0122042335271688</v>
+        <v>0.0136302692761605</v>
       </c>
       <c r="F235" t="n">
-        <v>0.0034713219472966</v>
+        <v>0.0136302692761605</v>
       </c>
       <c r="G235" t="n">
         <v>0.0284406962454975</v>
       </c>
       <c r="H235" t="n">
-        <v>-2.79252311179548</v>
+        <v>-2.75674057354289</v>
       </c>
     </row>
     <row r="236">
@@ -62516,22 +62453,22 @@
         <v>2.66465572226936</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.00125305683203081</v>
+        <v>-0.00125310759372077</v>
       </c>
       <c r="D236" t="n">
-        <v>-0.0577589133094811</v>
+        <v>-0.0572775235965599</v>
       </c>
       <c r="E236" t="n">
-        <v>-0.0399890533967966</v>
+        <v>-0.0400319550192103</v>
       </c>
       <c r="F236" t="n">
-        <v>-0.00227513190661899</v>
+        <v>-0.0400319550192103</v>
       </c>
       <c r="G236" t="n">
         <v>-0.0313631935861904</v>
       </c>
       <c r="H236" t="n">
-        <v>-4.63858904747498</v>
+        <v>-4.39912961812566</v>
       </c>
     </row>
     <row r="237">
@@ -62542,22 +62479,22 @@
         <v>7.64300246133654</v>
       </c>
       <c r="C237" t="n">
-        <v>0.00253811327331555</v>
+        <v>0.00253829703697139</v>
       </c>
       <c r="D237" t="n">
-        <v>0.0430756292384471</v>
+        <v>0.042640243498294</v>
       </c>
       <c r="E237" t="n">
-        <v>0.0242726345716795</v>
+        <v>0.0239865131797696</v>
       </c>
       <c r="F237" t="n">
-        <v>0.0185055579381652</v>
+        <v>0.0239865131797696</v>
       </c>
       <c r="G237" t="n">
         <v>-0.0468550642500949</v>
       </c>
       <c r="H237" t="n">
-        <v>-3.53778675832847</v>
+        <v>-3.58194766608145</v>
       </c>
     </row>
     <row r="238">
@@ -62568,22 +62505,22 @@
         <v>0.287948476193746</v>
       </c>
       <c r="C238" t="n">
-        <v>0.00956669573588886</v>
+        <v>0.00956652078575448</v>
       </c>
       <c r="D238" t="n">
-        <v>0.0303715790912742</v>
+        <v>0.0299622914732058</v>
       </c>
       <c r="E238" t="n">
-        <v>0.038942619380407</v>
+        <v>0.0419309279500704</v>
       </c>
       <c r="F238" t="n">
-        <v>0.0415903315337127</v>
+        <v>0.0419309279500704</v>
       </c>
       <c r="G238" t="n">
         <v>0.00358076183226697</v>
       </c>
       <c r="H238" t="n">
-        <v>-0.138491681791979</v>
+        <v>-0.0952448988931991</v>
       </c>
     </row>
     <row r="239">
@@ -62594,22 +62531,22 @@
         <v>-1.94515780689606</v>
       </c>
       <c r="C239" t="n">
-        <v>0.00567512868326059</v>
+        <v>0.0056751469643217</v>
       </c>
       <c r="D239" t="n">
-        <v>0.0112597359637032</v>
+        <v>0.0120886623555991</v>
       </c>
       <c r="E239" t="n">
-        <v>-0.0146942226525786</v>
+        <v>-0.0164424485269299</v>
       </c>
       <c r="F239" t="n">
-        <v>-0.0101971840256372</v>
+        <v>-0.0164424485269299</v>
       </c>
       <c r="G239" t="n">
         <v>-0.0727282214452849</v>
       </c>
       <c r="H239" t="n">
-        <v>-2.02164247857148</v>
+        <v>-2.02170250041797</v>
       </c>
     </row>
     <row r="240">
@@ -62620,22 +62557,22 @@
         <v>-6.05661541695486</v>
       </c>
       <c r="C240" t="n">
-        <v>0.00428196856264407</v>
+        <v>0.00428203851552578</v>
       </c>
       <c r="D240" t="n">
-        <v>-0.0178278254809889</v>
+        <v>-0.0186846287149862</v>
       </c>
       <c r="E240" t="n">
-        <v>0.00055564831581556</v>
+        <v>-0.000852509276188407</v>
       </c>
       <c r="F240" t="n">
-        <v>-0.0118572134688693</v>
+        <v>-0.000852509276188407</v>
       </c>
       <c r="G240" t="n">
         <v>-0.0788400264111386</v>
       </c>
       <c r="H240" t="n">
-        <v>-2.25303130427496</v>
+        <v>-2.25269239631175</v>
       </c>
     </row>
     <row r="241">
@@ -62646,22 +62583,22 @@
         <v>-4.48408844761867</v>
       </c>
       <c r="C241" t="n">
-        <v>0.00338359141207789</v>
+        <v>0.00338355938420865</v>
       </c>
       <c r="D241" t="n">
-        <v>0.0142263618362151</v>
+        <v>0.0146448447214773</v>
       </c>
       <c r="E241" t="n">
-        <v>0.016921026697502</v>
+        <v>0.0169359629239647</v>
       </c>
       <c r="F241" t="n">
-        <v>-0.00432159525358689</v>
+        <v>0.0169359629239647</v>
       </c>
       <c r="G241" t="n">
         <v>-0.220462010984514</v>
       </c>
       <c r="H241" t="n">
-        <v>-2.18082103994746</v>
+        <v>-2.14408979011252</v>
       </c>
     </row>
     <row r="242">
@@ -62672,22 +62609,22 @@
         <v>-0.914364066875468</v>
       </c>
       <c r="C242" t="n">
-        <v>0.00371045068091469</v>
+        <v>0.00371050949959262</v>
       </c>
       <c r="D242" t="n">
-        <v>-0.000418506119254758</v>
+        <v>-0.00041859747449724</v>
       </c>
       <c r="E242" t="n">
-        <v>-0.00510316271841393</v>
+        <v>-0.00624252947338899</v>
       </c>
       <c r="F242" t="n">
-        <v>0.00369134357137213</v>
+        <v>-0.00624252947338899</v>
       </c>
       <c r="G242" t="n">
         <v>-0.215667110684967</v>
       </c>
       <c r="H242" t="n">
-        <v>-3.28460786555196</v>
+        <v>-3.32437455570827</v>
       </c>
     </row>
     <row r="243">
@@ -62698,22 +62635,22 @@
         <v>5.41519428087773</v>
       </c>
       <c r="C243" t="n">
-        <v>0.00470160214127535</v>
+        <v>0.00470152797505552</v>
       </c>
       <c r="D243" t="n">
-        <v>0.00292160499653971</v>
+        <v>0.00292150796753443</v>
       </c>
       <c r="E243" t="n">
-        <v>0.00621366806093526</v>
+        <v>0.00574096696663151</v>
       </c>
       <c r="F243" t="n">
-        <v>0.0140726470267323</v>
+        <v>0.00574096696663151</v>
       </c>
       <c r="G243" t="n">
         <v>0.0643169011837088</v>
       </c>
       <c r="H243" t="n">
-        <v>-3.11550001479647</v>
+        <v>-3.26857228438205</v>
       </c>
     </row>
     <row r="244">
@@ -62724,22 +62661,22 @@
         <v>1.32054836368091</v>
       </c>
       <c r="C244" t="n">
-        <v>0.0019270544535317</v>
+        <v>0.00192706893676675</v>
       </c>
       <c r="D244" t="n">
-        <v>0.0244323421080308</v>
+        <v>0.0232389617176896</v>
       </c>
       <c r="E244" t="n">
-        <v>-0.0066957832167418</v>
+        <v>0.00599789914229554</v>
       </c>
       <c r="F244" t="n">
-        <v>-0.00853545161298364</v>
+        <v>0.00599789914229554</v>
       </c>
       <c r="G244" t="n">
         <v>-0.0433030464476873</v>
       </c>
       <c r="H244" t="n">
-        <v>-3.15368191204096</v>
+        <v>-2.84853086119782</v>
       </c>
     </row>
     <row r="245">
@@ -62750,22 +62687,22 @@
         <v>2.37517003531512</v>
       </c>
       <c r="C245" t="n">
-        <v>0.00102515559060734</v>
+        <v>0.00102511949600448</v>
       </c>
       <c r="D245" t="n">
-        <v>-0.0106997813748944</v>
+        <v>-0.00988074891330459</v>
       </c>
       <c r="E245" t="n">
-        <v>0.0148289993319812</v>
+        <v>0.000110267140608578</v>
       </c>
       <c r="F245" t="n">
-        <v>-0.0188140512913897</v>
+        <v>0.000110267140608578</v>
       </c>
       <c r="G245" t="n">
         <v>0.117497902659229</v>
       </c>
       <c r="H245" t="n">
-        <v>-4.10962354830347</v>
+        <v>-4.15993987877458</v>
       </c>
     </row>
     <row r="246">
@@ -62776,22 +62713,22 @@
         <v>0.820312477344311</v>
       </c>
       <c r="C246" t="n">
-        <v>0.00237369062438031</v>
+        <v>0.00237372326218743</v>
       </c>
       <c r="D246" t="n">
-        <v>0.0252734791976179</v>
+        <v>0.0252835819837349</v>
       </c>
       <c r="E246" t="n">
-        <v>-0.00342271288028861</v>
+        <v>-0.000535620167965156</v>
       </c>
       <c r="F246" t="n">
-        <v>-0.00608736782820962</v>
+        <v>-0.000535620167965156</v>
       </c>
       <c r="G246" t="n">
         <v>0.0628282288454702</v>
       </c>
       <c r="H246" t="n">
-        <v>-4.51224711865296</v>
+        <v>-4.39497683506334</v>
       </c>
     </row>
     <row r="247">
@@ -62802,22 +62739,22 @@
         <v>2.1080262921985</v>
       </c>
       <c r="C247" t="n">
-        <v>0.00479072565334615</v>
+        <v>0.00479068358929258</v>
       </c>
       <c r="D247" t="n">
-        <v>-0.00200961336381056</v>
+        <v>-0.00201050197656993</v>
       </c>
       <c r="E247" t="n">
-        <v>0.0165334733008375</v>
+        <v>0.017465129528655</v>
       </c>
       <c r="F247" t="n">
-        <v>0.0334462496922621</v>
+        <v>0.017465129528655</v>
       </c>
       <c r="G247" t="n">
         <v>-0.00321864668217486</v>
       </c>
       <c r="H247" t="n">
-        <v>-4.45345597000545</v>
+        <v>-4.35963737912912</v>
       </c>
     </row>
     <row r="248">
@@ -62828,22 +62765,22 @@
         <v>0.115788756120715</v>
       </c>
       <c r="C248" t="n">
-        <v>0.0037387162176179</v>
+        <v>0.00373887460868172</v>
       </c>
       <c r="D248" t="n">
-        <v>-0.000804608593830913</v>
+        <v>-0.000402103567296308</v>
       </c>
       <c r="E248" t="n">
-        <v>-0.00760920624088701</v>
+        <v>-0.00792258996605621</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.0372700018115664</v>
+        <v>-0.00792258996605621</v>
       </c>
       <c r="G248" t="n">
         <v>-0.17276539413492</v>
       </c>
       <c r="H248" t="n">
-        <v>-5.55333978795498</v>
+        <v>-5.23890931460487</v>
       </c>
     </row>
     <row r="249">
@@ -62854,22 +62791,22 @@
         <v>1.3259292408119</v>
       </c>
       <c r="C249" t="n">
-        <v>0.00628131667988807</v>
+        <v>0.00628125433309101</v>
       </c>
       <c r="D249" t="n">
-        <v>0.0197173599156777</v>
+        <v>0.0197173522736449</v>
       </c>
       <c r="E249" t="n">
-        <v>0.0283352273078794</v>
+        <v>0.0285589549295704</v>
       </c>
       <c r="F249" t="n">
-        <v>0.0303202667947895</v>
+        <v>0.0285589549295704</v>
       </c>
       <c r="G249" t="n">
         <v>-0.155129726661336</v>
       </c>
       <c r="H249" t="n">
-        <v>-4.51799887086548</v>
+        <v>-4.41783297044765</v>
       </c>
     </row>
     <row r="250">
@@ -62880,22 +62817,22 @@
         <v>2.4655254186401</v>
       </c>
       <c r="C250" t="n">
-        <v>0.00293237243032607</v>
+        <v>0.00293228192335881</v>
       </c>
       <c r="D250" t="n">
-        <v>0.0151462423752431</v>
+        <v>0.0151461324708215</v>
       </c>
       <c r="E250" t="n">
-        <v>-0.0092334142102235</v>
+        <v>-0.0149137235524188</v>
       </c>
       <c r="F250" t="n">
-        <v>-0.0178331849778246</v>
+        <v>-0.0149137235524188</v>
       </c>
       <c r="G250" t="n">
         <v>0.0807103618211098</v>
       </c>
       <c r="H250" t="n">
-        <v>-5.67356831816196</v>
+        <v>-5.78604776646442</v>
       </c>
     </row>
     <row r="251">
@@ -62906,22 +62843,22 @@
         <v>0.814828181754307</v>
       </c>
       <c r="C251" t="n">
-        <v>0.00280049321773479</v>
+        <v>0.00280062221825439</v>
       </c>
       <c r="D251" t="n">
-        <v>-0.00940811891627114</v>
+        <v>-0.0094081597141118</v>
       </c>
       <c r="E251" t="n">
-        <v>0.00278569127626138</v>
+        <v>0.00895970534815316</v>
       </c>
       <c r="F251" t="n">
-        <v>-0.0147641726558794</v>
+        <v>0.00895970534815316</v>
       </c>
       <c r="G251" t="n">
         <v>0.00237933135186275</v>
       </c>
       <c r="H251" t="n">
-        <v>-6.08517697734946</v>
+        <v>-6.12302391458419</v>
       </c>
     </row>
     <row r="252">
@@ -62932,22 +62869,22 @@
         <v>0.240755313694484</v>
       </c>
       <c r="C252" t="n">
-        <v>0.00542447196720364</v>
+        <v>0.00542433295509337</v>
       </c>
       <c r="D252" t="n">
-        <v>0.0229816747045914</v>
+        <v>0.0229817043360372</v>
       </c>
       <c r="E252" t="n">
-        <v>0.014097267691179</v>
+        <v>0.0143207168866457</v>
       </c>
       <c r="F252" t="n">
-        <v>0.082847309779865</v>
+        <v>0.0143207168866457</v>
       </c>
       <c r="G252" t="n">
         <v>-0.0758733034230188</v>
       </c>
       <c r="H252" t="n">
-        <v>-5.43161235175497</v>
+        <v>-5.39794907955895</v>
       </c>
     </row>
     <row r="253">
@@ -62958,22 +62895,22 @@
         <v>7.31943496223768</v>
       </c>
       <c r="C253" t="n">
-        <v>0.00343233368054285</v>
+        <v>0.00343236245727052</v>
       </c>
       <c r="D253" t="n">
-        <v>0.00267378611177005</v>
+        <v>0.00267373324231812</v>
       </c>
       <c r="E253" t="n">
-        <v>-0.00156023432453001</v>
+        <v>-0.00312761236097625</v>
       </c>
       <c r="F253" t="n">
-        <v>-0.0392177289135134</v>
+        <v>-0.00312761236097625</v>
       </c>
       <c r="G253" t="n">
         <v>-0.131839548790338</v>
       </c>
       <c r="H253" t="n">
-        <v>-6.38487801579348</v>
+        <v>-6.39435070985373</v>
       </c>
     </row>
     <row r="254">
@@ -62984,22 +62921,22 @@
         <v>2.40721232423188</v>
       </c>
       <c r="C254" t="n">
-        <v>0.00350126466476119</v>
+        <v>0.00350128242590575</v>
       </c>
       <c r="D254" t="n">
-        <v>0.00758155537388649</v>
+        <v>0.00720534763757907</v>
       </c>
       <c r="E254" t="n">
-        <v>0.00731692085726809</v>
+        <v>0.00900917990933614</v>
       </c>
       <c r="F254" t="n">
-        <v>-0.0181642605510035</v>
+        <v>0.00900917990933614</v>
       </c>
       <c r="G254" t="n">
         <v>-0.140933389386372</v>
       </c>
       <c r="H254" t="n">
-        <v>-6.87675095960096</v>
+        <v>-6.68526029486549</v>
       </c>
     </row>
     <row r="255">
@@ -63010,22 +62947,22 @@
         <v>1.08827012964408</v>
       </c>
       <c r="C255" t="n">
-        <v>0.00225881456111576</v>
+        <v>0.00225877192120016</v>
       </c>
       <c r="D255" t="n">
-        <v>0.000378850412932508</v>
+        <v>0.000757846337416268</v>
       </c>
       <c r="E255" t="n">
-        <v>-0.010074199257927</v>
+        <v>-0.0131039263506727</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.00536819989170034</v>
+        <v>-0.0131039263506727</v>
       </c>
       <c r="G255" t="n">
         <v>-0.0482065619146717</v>
       </c>
       <c r="H255" t="n">
-        <v>-7.93592351060448</v>
+        <v>-7.70608524301726</v>
       </c>
     </row>
     <row r="256">
@@ -63036,22 +62973,22 @@
         <v>1.11080794100727</v>
       </c>
       <c r="C256" t="n">
-        <v>0.00571642912884229</v>
+        <v>0.00571642346762591</v>
       </c>
       <c r="D256" t="n">
-        <v>0.0211441736372766</v>
+        <v>0.0215070673281623</v>
       </c>
       <c r="E256" t="n">
-        <v>0.0247283393075408</v>
+        <v>0.0149644207712161</v>
       </c>
       <c r="F256" t="n">
-        <v>0.0240826633586897</v>
+        <v>0.0149644207712161</v>
       </c>
       <c r="G256" t="n">
         <v>0.205307858466967</v>
       </c>
       <c r="H256" t="n">
-        <v>-5.62533646057998</v>
+        <v>-5.79230374236203</v>
       </c>
     </row>
     <row r="257">
@@ -63062,22 +62999,22 @@
         <v>4.48225435314448</v>
       </c>
       <c r="C257" t="n">
-        <v>0.00230497852029465</v>
+        <v>0.00230495361067895</v>
       </c>
       <c r="D257" t="n">
-        <v>0.00185111403897675</v>
+        <v>0.00111108491843304</v>
       </c>
       <c r="E257" t="n">
-        <v>-0.00246019780442008</v>
+        <v>0.0078709590230428</v>
       </c>
       <c r="F257" t="n">
-        <v>-0.0132317570703808</v>
+        <v>0.0078709590230428</v>
       </c>
       <c r="G257" t="n">
         <v>0.0546057859764604</v>
       </c>
       <c r="H257" t="n">
-        <v>-3.69838954504446</v>
+        <v>-3.74553390950079</v>
       </c>
     </row>
     <row r="258">
@@ -63088,22 +63025,22 @@
         <v>2.96816975758365</v>
       </c>
       <c r="C258" t="n">
-        <v>0.00447524830239132</v>
+        <v>0.0044752793555114</v>
       </c>
       <c r="D258" t="n">
-        <v>-0.0063339156932507</v>
+        <v>-0.00596136468574215</v>
       </c>
       <c r="E258" t="n">
-        <v>0.0042950970409521</v>
+        <v>0.00490982567240295</v>
       </c>
       <c r="F258" t="n">
-        <v>0.0170980356023085</v>
+        <v>0.00490982567240295</v>
       </c>
       <c r="G258" t="n">
         <v>0.142611895873971</v>
       </c>
       <c r="H258" t="n">
-        <v>-2.98715290079897</v>
+        <v>-2.88608968744657</v>
       </c>
     </row>
     <row r="259">
@@ -63114,22 +63051,22 @@
         <v>2.69489980975686</v>
       </c>
       <c r="C259" t="n">
-        <v>0.00492180182769708</v>
+        <v>0.00492178352092409</v>
       </c>
       <c r="D259" t="n">
-        <v>0.0211540510622532</v>
+        <v>0.0207968546238213</v>
       </c>
       <c r="E259" t="n">
-        <v>0.0146672799600438</v>
+        <v>0.0155984547601697</v>
       </c>
       <c r="F259" t="n">
-        <v>-0.00473785331492138</v>
+        <v>0.0155984547601697</v>
       </c>
       <c r="G259" t="n">
         <v>0.0510743915674281</v>
       </c>
       <c r="H259" t="n">
-        <v>-2.74837947797747</v>
+        <v>-2.73616022691434</v>
       </c>
     </row>
     <row r="260">
@@ -63140,22 +63077,22 @@
         <v>3.15052255421807</v>
       </c>
       <c r="C260" t="n">
-        <v>0.00293773369946759</v>
+        <v>0.00293770358532708</v>
       </c>
       <c r="D260" t="n">
-        <v>0.00760046456014063</v>
+        <v>0.00796244370580279</v>
       </c>
       <c r="E260" t="n">
-        <v>-0.00327235527437075</v>
+        <v>-0.00365791994438958</v>
       </c>
       <c r="F260" t="n">
-        <v>-0.0176027097990286</v>
+        <v>-0.00365791994438958</v>
       </c>
       <c r="G260" t="n">
         <v>-0.0917892788284052</v>
       </c>
       <c r="H260" t="n">
-        <v>-2.75281481194797</v>
+        <v>-2.69491191261609</v>
       </c>
     </row>
     <row r="261">
@@ -63166,22 +63103,22 @@
         <v>3.98417429316425</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.000787138923161734</v>
+        <v>-0.000787036376031836</v>
       </c>
       <c r="D261" t="n">
-        <v>-0.0124591161654051</v>
+        <v>-0.0128302940694223</v>
       </c>
       <c r="E261" t="n">
-        <v>-0.0190599834005836</v>
+        <v>-0.0188061601794791</v>
       </c>
       <c r="F261" t="n">
-        <v>-0.0020370089131303</v>
+        <v>-0.0188061601794791</v>
       </c>
       <c r="G261" t="n">
         <v>-0.0115634963324238</v>
       </c>
       <c r="H261" t="n">
-        <v>-4.12591813966847</v>
+        <v>-4.05446047905986</v>
       </c>
     </row>
     <row r="262">
@@ -63192,22 +63129,22 @@
         <v>0.779930464756447</v>
       </c>
       <c r="C262" t="n">
-        <v>0.00419157903770984</v>
+        <v>0.00419150598078666</v>
       </c>
       <c r="D262" t="n">
-        <v>0.00619095810666348</v>
+        <v>0.00655512986355866</v>
       </c>
       <c r="E262" t="n">
-        <v>0.032452669169734</v>
+        <v>0.0355698467233276</v>
       </c>
       <c r="F262" t="n">
-        <v>-0.00182475757259137</v>
+        <v>0.0355698467233276</v>
       </c>
       <c r="G262" t="n">
         <v>0.0025537558279396</v>
       </c>
       <c r="H262" t="n">
-        <v>-0.923631841449953</v>
+        <v>-0.720861247808623</v>
       </c>
     </row>
     <row r="263">
@@ -63218,22 +63155,22 @@
         <v>6.03482831978365</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.000189916445738625</v>
+        <v>-0.000189837279307881</v>
       </c>
       <c r="D263" t="n">
-        <v>-0.00438920625485473</v>
+        <v>-0.00549248343784825</v>
       </c>
       <c r="E263" t="n">
-        <v>-0.0197982077954366</v>
+        <v>-0.0308270723231017</v>
       </c>
       <c r="F263" t="n">
-        <v>-0.0221297262669848</v>
+        <v>-0.0308270723231017</v>
       </c>
       <c r="G263" t="n">
         <v>0.110354829209645</v>
       </c>
       <c r="H263" t="n">
-        <v>-3.88654316862447</v>
+        <v>-4.04311204219939</v>
       </c>
     </row>
     <row r="264">
@@ -63244,22 +63181,22 @@
         <v>7.32554004607783</v>
       </c>
       <c r="C264" t="n">
-        <v>0.00461859908323969</v>
+        <v>0.00461850929374918</v>
       </c>
       <c r="D264" t="n">
-        <v>0.0267030674081186</v>
+        <v>0.0274249389777568</v>
       </c>
       <c r="E264" t="n">
-        <v>0.00726278644153222</v>
+        <v>0.0155880055046742</v>
       </c>
       <c r="F264" t="n">
-        <v>0.0392192666631761</v>
+        <v>0.0155880055046742</v>
       </c>
       <c r="G264" t="n">
         <v>-0.0756703416022679</v>
       </c>
       <c r="H264" t="n">
-        <v>-2.28567132600397</v>
+        <v>-2.11979572889818</v>
       </c>
     </row>
     <row r="265">
@@ -63270,22 +63207,22 @@
         <v>6.55054546168103</v>
       </c>
       <c r="C265" t="n">
-        <v>0.00350438329013958</v>
+        <v>0.00350444396360228</v>
       </c>
       <c r="D265" t="n">
-        <v>0.00495925389286711</v>
+        <v>0.0053136374523195</v>
       </c>
       <c r="E265" t="n">
-        <v>0.0105015474811347</v>
+        <v>0.00781198251850768</v>
       </c>
       <c r="F265" t="n">
-        <v>0.00518850400226256</v>
+        <v>0.00781198251850768</v>
       </c>
       <c r="G265" t="n">
         <v>0.124602746525012</v>
       </c>
       <c r="H265" t="n">
-        <v>-0.329371558544469</v>
+        <v>-0.335703183709926</v>
       </c>
     </row>
     <row r="266">
@@ -63296,22 +63233,22 @@
         <v>5.83755699546025</v>
       </c>
       <c r="C266" t="n">
-        <v>0.00228227919519863</v>
+        <v>0.00228231803355072</v>
       </c>
       <c r="D266" t="n">
-        <v>0.00947384757269543</v>
+        <v>0.00947376562099933</v>
       </c>
       <c r="E266" t="n">
-        <v>-0.00053606092133851</v>
+        <v>0.00253128944718917</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.00193394531981106</v>
+        <v>0.00253128944718917</v>
       </c>
       <c r="G266" t="n">
         <v>0.00963589922718722</v>
       </c>
       <c r="H266" t="n">
-        <v>-2.48247065472996</v>
+        <v>-2.2954006607697</v>
       </c>
     </row>
     <row r="267">
@@ -63322,22 +63259,22 @@
         <v>7.15195296105542</v>
       </c>
       <c r="C267" t="n">
-        <v>0.00136743371148995</v>
+        <v>0.00136743042011034</v>
       </c>
       <c r="D267" t="n">
-        <v>0.00766033742094407</v>
+        <v>0.00766037562560662</v>
       </c>
       <c r="E267" t="n">
-        <v>0.0107136396194125</v>
+        <v>0.009013272183517</v>
       </c>
       <c r="F267" t="n">
-        <v>-0.0336890515615957</v>
+        <v>0.009013272183517</v>
       </c>
       <c r="G267" t="n">
         <v>-0.00550694585210643</v>
       </c>
       <c r="H267" t="n">
-        <v>-3.49868481197447</v>
+        <v>-3.38398600878447</v>
       </c>
     </row>
     <row r="268">
@@ -63348,22 +63285,22 @@
         <v>6.30244178046263</v>
       </c>
       <c r="C268" t="n">
-        <v>0.0071127942044189</v>
+        <v>0.00711274551154872</v>
       </c>
       <c r="D268" t="n">
-        <v>0.0065720544675596</v>
+        <v>0.00657211432100269</v>
       </c>
       <c r="E268" t="n">
-        <v>0.00734574265033139</v>
+        <v>0.00677602387529141</v>
       </c>
       <c r="F268" t="n">
-        <v>0.0508883075593767</v>
+        <v>0.00677602387529141</v>
       </c>
       <c r="G268" t="n">
         <v>-0.10521753532717</v>
       </c>
       <c r="H268" t="n">
-        <v>-2.50569730675697</v>
+        <v>-2.60986207916124</v>
       </c>
     </row>
     <row r="269">
@@ -63374,22 +63311,22 @@
         <v>5.22902222060282</v>
       </c>
       <c r="C269" t="n">
-        <v>0.00492145071507188</v>
+        <v>0.0049214281971981</v>
       </c>
       <c r="D269" t="n">
-        <v>0.0173360625688241</v>
+        <v>0.0176698915155065</v>
       </c>
       <c r="E269" t="n">
-        <v>0.00902862726831444</v>
+        <v>0.0151432766897841</v>
       </c>
       <c r="F269" t="n">
-        <v>0.0068963208077637</v>
+        <v>0.0151432766897841</v>
       </c>
       <c r="G269" t="n">
         <v>0.0326285622595988</v>
       </c>
       <c r="H269" t="n">
-        <v>-2.12752825192546</v>
+        <v>-2.07715732586201</v>
       </c>
     </row>
     <row r="270">
@@ -63400,22 +63337,22 @@
         <v>7.65994577045402</v>
       </c>
       <c r="C270" t="n">
-        <v>0.00277410034987113</v>
+        <v>0.00277420791711958</v>
       </c>
       <c r="D270" t="n">
-        <v>-0.0236625828420536</v>
+        <v>-0.0243671158384426</v>
       </c>
       <c r="E270" t="n">
-        <v>-0.00940557316058133</v>
+        <v>-0.0147592856702143</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.0182243270099756</v>
+        <v>-0.0147592856702143</v>
       </c>
       <c r="G270" t="n">
         <v>-0.0703398258765295</v>
       </c>
       <c r="H270" t="n">
-        <v>-2.26352995098696</v>
+        <v>-2.20872089978777</v>
       </c>
     </row>
     <row r="271">
@@ -63426,22 +63363,22 @@
         <v>6.97166594826421</v>
       </c>
       <c r="C271" t="n">
-        <v>0.00311779478371843</v>
+        <v>0.00311765366967265</v>
       </c>
       <c r="D271" t="n">
-        <v>0.0342809859804367</v>
+        <v>0.0346171655641152</v>
       </c>
       <c r="E271" t="n">
-        <v>0.0113197602459056</v>
+        <v>0.0116093701473456</v>
       </c>
       <c r="F271" t="n">
-        <v>0.00304977063519107</v>
+        <v>0.0116093701473456</v>
       </c>
       <c r="G271" t="n">
         <v>-0.0818880523000702</v>
       </c>
       <c r="H271" t="n">
-        <v>-1.41138603266647</v>
+        <v>-1.36040424823955</v>
       </c>
     </row>
     <row r="272">
@@ -63452,22 +63389,22 @@
         <v>8.88430022413442</v>
       </c>
       <c r="C272" t="n">
-        <v>0.000844587545367759</v>
+        <v>0.000844590519633925</v>
       </c>
       <c r="D272" t="n">
-        <v>0</v>
+        <v>-0.000336137213708732</v>
       </c>
       <c r="E272" t="n">
-        <v>0.00653110228743881</v>
+        <v>0.00631200725963676</v>
       </c>
       <c r="F272" t="n">
-        <v>-0.000314030670271137</v>
+        <v>0.00631200725963676</v>
       </c>
       <c r="G272" t="n">
         <v>0.0373735951035883</v>
       </c>
       <c r="H272" t="n">
-        <v>-0.372862901956966</v>
+        <v>-0.311369459680309</v>
       </c>
     </row>
     <row r="273">
@@ -63478,22 +63415,22 @@
         <v>8.15131953259962</v>
       </c>
       <c r="C273" t="n">
-        <v>0.00411236300342654</v>
+        <v>0.00411243056172417</v>
       </c>
       <c r="D273" t="n">
-        <v>0.00866099717797919</v>
+        <v>0.00899422044655118</v>
       </c>
       <c r="E273" t="n">
-        <v>0.012384059199718</v>
+        <v>0.0131015318452841</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.0303023761077839</v>
+        <v>0.0131015318452841</v>
       </c>
       <c r="G273" t="n">
         <v>0.0414186167685617</v>
       </c>
       <c r="H273" t="n">
-        <v>0.163227633993531</v>
+        <v>0.204076368627913</v>
       </c>
     </row>
     <row r="274">
@@ -63504,22 +63441,22 @@
         <v>7.33743338425979</v>
       </c>
       <c r="C274" t="n">
-        <v>0.00142274501168771</v>
+        <v>0.00142283446826497</v>
       </c>
       <c r="D274" t="n">
-        <v>0.00298906753608463</v>
+        <v>0.00265769160483043</v>
       </c>
       <c r="E274" t="n">
-        <v>-0.0149713245229828</v>
+        <v>-0.0108284422631453</v>
       </c>
       <c r="F274" t="n">
-        <v>0.0204913399174353</v>
+        <v>-0.0108284422631453</v>
       </c>
       <c r="G274" t="n">
         <v>0.0176177435177634</v>
       </c>
       <c r="H274" t="n">
-        <v>0.104553863458042</v>
+        <v>0.343537538860138</v>
       </c>
     </row>
     <row r="275">
@@ -63530,22 +63467,22 @@
         <v>8.343515202995</v>
       </c>
       <c r="C275" t="n">
-        <v>0.00571062984891224</v>
+        <v>0.00571066687178146</v>
       </c>
       <c r="D275" t="n">
-        <v>0.0195388465353945</v>
+        <v>0.0201837397654652</v>
       </c>
       <c r="E275" t="n">
-        <v>0.0293726042223748</v>
+        <v>0.0280920054501088</v>
       </c>
       <c r="F275" t="n">
-        <v>0.012144004356176</v>
+        <v>0.0280920054501088</v>
       </c>
       <c r="G275" t="n">
         <v>0.0245675948524982</v>
       </c>
       <c r="H275" t="n">
-        <v>0.82118615410654</v>
+        <v>0.814455280890381</v>
       </c>
     </row>
     <row r="276">
@@ -63556,22 +63493,22 @@
         <v>9.47965997966519</v>
       </c>
       <c r="C276" t="n">
-        <v>0.00444406077879123</v>
+        <v>0.00444394921755098</v>
       </c>
       <c r="D276" t="n">
-        <v>-0.000325732770542153</v>
+        <v>-0.000651530884426599</v>
       </c>
       <c r="E276" t="n">
-        <v>0.00286922973192105</v>
+        <v>-0.0006314403224561</v>
       </c>
       <c r="F276" t="n">
-        <v>0.01531233874391</v>
+        <v>-0.0006314403224561</v>
       </c>
       <c r="G276" t="n">
         <v>0.0979602606013641</v>
       </c>
       <c r="H276" t="n">
-        <v>0.439196199721041</v>
+        <v>0.506640095280631</v>
       </c>
     </row>
     <row r="277">
@@ -63582,22 +63519,22 @@
         <v>9.81718896720238</v>
       </c>
       <c r="C277" t="n">
-        <v>0.00252525869324227</v>
+        <v>0.00252532783878756</v>
       </c>
       <c r="D277" t="n">
-        <v>-0.00130468548595797</v>
+        <v>-0.0013045673924843</v>
       </c>
       <c r="E277" t="n">
-        <v>-0.00458159583208761</v>
+        <v>-0.00392269526617373</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.00148061015336598</v>
+        <v>-0.00392269526617373</v>
       </c>
       <c r="G277" t="n">
         <v>0.0167863023998462</v>
       </c>
       <c r="H277" t="n">
-        <v>-0.378955226496463</v>
+        <v>-0.420975751607146</v>
       </c>
     </row>
     <row r="278">
@@ -63608,22 +63545,22 @@
         <v>9.71621136100658</v>
       </c>
       <c r="C278" t="n">
-        <v>0.00407532218950912</v>
+        <v>0.00407519971755743</v>
       </c>
       <c r="D278" t="n">
-        <v>0.0135138306858069</v>
+        <v>0.0135138670709969</v>
       </c>
       <c r="E278" t="n">
-        <v>0.00283643079529305</v>
+        <v>0.00216584112301188</v>
       </c>
       <c r="F278" t="n">
-        <v>0.0289722479533925</v>
+        <v>0.00216584112301188</v>
       </c>
       <c r="G278" t="n">
         <v>0.0775923960940537</v>
       </c>
       <c r="H278" t="n">
-        <v>0.750129210098047</v>
+        <v>0.550210115892071</v>
       </c>
     </row>
     <row r="279">
@@ -63634,22 +63571,22 @@
         <v>10.2144487087758</v>
       </c>
       <c r="C279" t="n">
-        <v>0.00386736258859077</v>
+        <v>0.00386745910284425</v>
       </c>
       <c r="D279" t="n">
-        <v>0.0201780715203252</v>
+        <v>0.019868870906949</v>
       </c>
       <c r="E279" t="n">
-        <v>-0.000445446983905917</v>
+        <v>-0.000384003988460613</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.0277643002558037</v>
+        <v>-0.000384003988460613</v>
       </c>
       <c r="G279" t="n">
         <v>-0.00814400861785192</v>
       </c>
       <c r="H279" t="n">
-        <v>0.363190370299519</v>
+        <v>0.379206563316322</v>
       </c>
     </row>
     <row r="280">
@@ -63660,22 +63597,22 @@
         <v>11.721973675177</v>
       </c>
       <c r="C280" t="n">
-        <v>0.00251751813053058</v>
+        <v>0.0025175535527735</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.00443327213327915</v>
+        <v>-0.00539003129420745</v>
       </c>
       <c r="E280" t="n">
-        <v>0.0117182576180825</v>
+        <v>0.0245304772632498</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.00646502266415894</v>
+        <v>0.0245304772632498</v>
       </c>
       <c r="G280" t="n">
         <v>0.00379715711300666</v>
       </c>
       <c r="H280" t="n">
-        <v>1.04232862994603</v>
+        <v>1.22654755383455</v>
       </c>
     </row>
     <row r="281">
@@ -63686,22 +63623,22 @@
         <v>9.56001426905118</v>
       </c>
       <c r="C281" t="n">
-        <v>0.00199092669023937</v>
+        <v>0.00199091497679049</v>
       </c>
       <c r="D281" t="n">
-        <v>-0.0256605181982037</v>
+        <v>-0.025026860450116</v>
       </c>
       <c r="E281" t="n">
-        <v>-0.0170523963497766</v>
+        <v>-0.0299239355646153</v>
       </c>
       <c r="F281" t="n">
-        <v>0.0100304892952341</v>
+        <v>-0.0299239355646153</v>
       </c>
       <c r="G281" t="n">
         <v>0.068836422727947</v>
       </c>
       <c r="H281" t="n">
-        <v>0.77963866019753</v>
+        <v>0.871524002128778</v>
       </c>
     </row>
     <row r="282">
@@ -63712,22 +63649,22 @@
         <v>10.7556345377214</v>
       </c>
       <c r="C282" t="n">
-        <v>0.00269228598523874</v>
+        <v>0.00269223289129705</v>
       </c>
       <c r="D282" t="n">
-        <v>0.0345004974054559</v>
+        <v>0.0351279333209034</v>
       </c>
       <c r="E282" t="n">
-        <v>0.0226258071166479</v>
+        <v>0.0229089369277427</v>
       </c>
       <c r="F282" t="n">
-        <v>-0.00387758871126298</v>
+        <v>0.0229089369277427</v>
       </c>
       <c r="G282" t="n">
         <v>0.0644623469125962</v>
       </c>
       <c r="H282" t="n">
-        <v>2.52083589207905</v>
+        <v>2.60438701192801</v>
       </c>
     </row>
     <row r="283">
@@ -63738,22 +63675,22 @@
         <v>12.2923017583166</v>
       </c>
       <c r="C283" t="n">
-        <v>0.000111217969688049</v>
+        <v>0.000111141526499381</v>
       </c>
       <c r="D283" t="n">
-        <v>-0.0156057063170278</v>
+        <v>-0.015929317545087</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.0240207118373856</v>
+        <v>-0.0240266063409837</v>
       </c>
       <c r="F283" t="n">
-        <v>-0.00394491570875388</v>
+        <v>-0.0240266063409837</v>
       </c>
       <c r="G283" t="n">
         <v>-0.0277816392733028</v>
       </c>
       <c r="H283" t="n">
-        <v>0.725393474465523</v>
+        <v>0.935468060501251</v>
       </c>
     </row>
     <row r="284">
@@ -63764,22 +63701,22 @@
         <v>11.3251492928648</v>
       </c>
       <c r="C284" t="n">
-        <v>0.00421315784157361</v>
+        <v>0.00421316589600362</v>
       </c>
       <c r="D284" t="n">
-        <v>0.00915129948066884</v>
+        <v>0.00946685826728544</v>
       </c>
       <c r="E284" t="n">
-        <v>0.0316846898805316</v>
+        <v>0.0312306097767046</v>
       </c>
       <c r="F284" t="n">
-        <v>0.0231213845934786</v>
+        <v>0.0312306097767046</v>
       </c>
       <c r="G284" t="n">
         <v>0.0560290343889331</v>
       </c>
       <c r="H284" t="n">
-        <v>1.27754014566203</v>
+        <v>1.48931979178046</v>
       </c>
     </row>
     <row r="285">
@@ -63790,22 +63727,22 @@
         <v>11.365171654308</v>
       </c>
       <c r="C285" t="n">
-        <v>0.00388142730905283</v>
+        <v>0.00388151276088422</v>
       </c>
       <c r="D285" t="n">
-        <v>0.021613227267685</v>
+        <v>0.021613316460293</v>
       </c>
       <c r="E285" t="n">
-        <v>-0.000732481852678823</v>
+        <v>-0.0000123056768526197</v>
       </c>
       <c r="F285" t="n">
-        <v>0.0195741757449222</v>
+        <v>-0.0000123056768526197</v>
       </c>
       <c r="G285" t="n">
         <v>-0.0378309224795244</v>
       </c>
       <c r="H285" t="n">
-        <v>2.18644291170554</v>
+        <v>2.41666686397072</v>
       </c>
     </row>
     <row r="286">
@@ -63816,22 +63753,22 @@
         <v>11.7996347247312</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.000389366965952931</v>
+        <v>-0.000389396131041053</v>
       </c>
       <c r="D286" t="n">
-        <v>-0.00997826822301384</v>
+        <v>-0.0109241055535092</v>
       </c>
       <c r="E286" t="n">
-        <v>-0.00146408657027131</v>
+        <v>-0.00756815420048174</v>
       </c>
       <c r="F286" t="n">
-        <v>-0.0358427413336537</v>
+        <v>-0.00756815420048174</v>
       </c>
       <c r="G286" t="n">
         <v>0.0106597714433905</v>
       </c>
       <c r="H286" t="n">
-        <v>0.896882716580041</v>
+        <v>0.778626486747952</v>
       </c>
     </row>
     <row r="287">
@@ -63842,22 +63779,22 @@
         <v>12.3540955558474</v>
       </c>
       <c r="C287" t="n">
-        <v>0.00240164610085536</v>
+        <v>0.00240158064124785</v>
       </c>
       <c r="D287" t="n">
-        <v>0.017162948968358</v>
+        <v>0.0189846940992675</v>
       </c>
       <c r="E287" t="n">
-        <v>-0.00825741791041512</v>
+        <v>-0.00207601124350987</v>
       </c>
       <c r="F287" t="n">
-        <v>-0.0106872867573919</v>
+        <v>-0.00207601124350987</v>
       </c>
       <c r="G287" t="n">
         <v>0.0218762593789004</v>
       </c>
       <c r="H287" t="n">
-        <v>1.06562872023754</v>
+        <v>1.00490971850616</v>
       </c>
     </row>
     <row r="288">
@@ -63868,22 +63805,22 @@
         <v>9.29192606287656</v>
       </c>
       <c r="C288" t="n">
-        <v>0.00148689635737487</v>
+        <v>0.0014868904675307</v>
       </c>
       <c r="D288" t="n">
-        <v>0.0136038039886897</v>
+        <v>0.0123982635108977</v>
       </c>
       <c r="E288" t="n">
-        <v>0.00930765842652637</v>
+        <v>0.00909985469733421</v>
       </c>
       <c r="F288" t="n">
-        <v>-0.0079648481310306</v>
+        <v>0.00909985469733421</v>
       </c>
       <c r="G288" t="n">
         <v>-0.200322775909989</v>
       </c>
       <c r="H288" t="n">
-        <v>0.759467839701042</v>
+        <v>0.794264753479412</v>
       </c>
     </row>
     <row r="289">
@@ -63894,22 +63831,22 @@
         <v>8.45826138225475</v>
       </c>
       <c r="C289" t="n">
-        <v>0.0022538376674337</v>
+        <v>0.00225389919644137</v>
       </c>
       <c r="D289" t="n">
-        <v>-0.0137914141674456</v>
+        <v>-0.013485028887473</v>
       </c>
       <c r="E289" t="n">
-        <v>0.000653624402084496</v>
+        <v>-0.000379950868558687</v>
       </c>
       <c r="F289" t="n">
-        <v>0.00965664353687945</v>
+        <v>-0.000379950868558687</v>
       </c>
       <c r="G289" t="n">
         <v>-0.13269559541768</v>
       </c>
       <c r="H289" t="n">
-        <v>1.03947598606853</v>
+        <v>1.12251392468262</v>
       </c>
     </row>
     <row r="290">
@@ -63920,22 +63857,22 @@
         <v>9.75015908201092</v>
       </c>
       <c r="C290" t="n">
-        <v>0.00403490649662519</v>
+        <v>0.00403489027160386</v>
       </c>
       <c r="D290" t="n">
-        <v>0.0115119739731577</v>
+        <v>0.011212426353584</v>
       </c>
       <c r="E290" t="n">
-        <v>0.00596563365824831</v>
+        <v>0.00600400018624914</v>
       </c>
       <c r="F290" t="n">
-        <v>0.0191698270889011</v>
+        <v>0.00600400018624914</v>
       </c>
       <c r="G290" t="n">
         <v>0.0288106004121174</v>
       </c>
       <c r="H290" t="n">
-        <v>2.48592474525603</v>
+        <v>2.62996670184285</v>
       </c>
     </row>
     <row r="291">
@@ -63946,22 +63883,22 @@
         <v>11.0969799388341</v>
       </c>
       <c r="C291" t="n">
-        <v>0.00415157126419352</v>
+        <v>0.00415155605363626</v>
       </c>
       <c r="D291" t="n">
-        <v>0.0116768486564984</v>
+        <v>0.0119763138199058</v>
       </c>
       <c r="E291" t="n">
-        <v>0.0135591215748612</v>
+        <v>0.0143208155600565</v>
       </c>
       <c r="F291" t="n">
-        <v>0.00377553281726151</v>
+        <v>0.0143208155600565</v>
       </c>
       <c r="G291" t="n">
         <v>0.049331351192631</v>
       </c>
       <c r="H291" t="n">
-        <v>3.07135312579052</v>
+        <v>3.14794007701411</v>
       </c>
     </row>
     <row r="292">
@@ -63972,22 +63909,22 @@
         <v>9.37563349912032</v>
       </c>
       <c r="C292" t="n">
-        <v>0.00540366366529543</v>
+        <v>0.00540375168982976</v>
       </c>
       <c r="D292" t="n">
-        <v>-0.00179964514673525</v>
+        <v>-0.00179965339993426</v>
       </c>
       <c r="E292" t="n">
-        <v>-0.0120995991620463</v>
+        <v>-0.0233016258002046</v>
       </c>
       <c r="F292" t="n">
-        <v>0.00947918035080253</v>
+        <v>-0.0233016258002046</v>
       </c>
       <c r="G292" t="n">
         <v>0.0494460474912239</v>
       </c>
       <c r="H292" t="n">
-        <v>3.04603524443703</v>
+        <v>3.00042812081933</v>
       </c>
     </row>
     <row r="293">
@@ -63998,22 +63935,22 @@
         <v>9.06763679582953</v>
       </c>
       <c r="C293" t="n">
-        <v>0.00202711250421039</v>
+        <v>0.00202704246917573</v>
       </c>
       <c r="D293" t="n">
-        <v>0.0179686096325238</v>
+        <v>0.0173895774305661</v>
       </c>
       <c r="E293" t="n">
-        <v>0.035134336007296</v>
+        <v>0.0511525809144722</v>
       </c>
       <c r="F293" t="n">
-        <v>0.0105988711827409</v>
+        <v>0.0511525809144722</v>
       </c>
       <c r="G293" t="n">
         <v>0.0840451806265099</v>
       </c>
       <c r="H293" t="n">
-        <v>2.09846180713052</v>
+        <v>2.15685113430654</v>
       </c>
     </row>
     <row r="294">
@@ -64024,22 +63961,22 @@
         <v>9.23237624410672</v>
       </c>
       <c r="C294" t="n">
-        <v>0.000537531886958931</v>
+        <v>0.000537517411159705</v>
       </c>
       <c r="D294" t="n">
-        <v>-0.00443792185963066</v>
+        <v>-0.00384608811161158</v>
       </c>
       <c r="E294" t="n">
-        <v>-0.0154153806521578</v>
+        <v>-0.0202796752440122</v>
       </c>
       <c r="F294" t="n">
-        <v>-0.0116601982467106</v>
+        <v>-0.0202796752440122</v>
       </c>
       <c r="G294" t="n">
         <v>-0.0559885145396075</v>
       </c>
       <c r="H294" t="n">
-        <v>1.42201086140002</v>
+        <v>1.5275604259608</v>
       </c>
     </row>
     <row r="295">
@@ -64050,22 +63987,22 @@
         <v>7.64513159602791</v>
       </c>
       <c r="C295" t="n">
-        <v>0.00419812125959584</v>
+        <v>0.00419816896996572</v>
       </c>
       <c r="D295" t="n">
-        <v>0.0125624388748493</v>
+        <v>0.0125623245727997</v>
       </c>
       <c r="E295" t="n">
-        <v>0.00757450231449663</v>
+        <v>0.00805653412303187</v>
       </c>
       <c r="F295" t="n">
-        <v>-0.0154710178248125</v>
+        <v>0.00805653412303187</v>
       </c>
       <c r="G295" t="n">
         <v>-0.0998973693230552</v>
       </c>
       <c r="H295" t="n">
-        <v>2.15412425099153</v>
+        <v>2.17497125338403</v>
       </c>
     </row>
     <row r="296">
@@ -64076,22 +64013,22 @@
         <v>8.61303152814811</v>
       </c>
       <c r="C296" t="n">
-        <v>0.00239983956272649</v>
+        <v>0.00239978432169163</v>
       </c>
       <c r="D296" t="n">
-        <v>0.0186363186998655</v>
+        <v>0.0183549966870906</v>
       </c>
       <c r="E296" t="n">
-        <v>-0.00351088171759173</v>
+        <v>-0.00432419665981154</v>
       </c>
       <c r="F296" t="n">
-        <v>0.0372325699140053</v>
+        <v>-0.00432419665981154</v>
       </c>
       <c r="G296" t="n">
         <v>0.0364557905400078</v>
       </c>
       <c r="H296" t="n">
-        <v>3.83652637691202</v>
+        <v>3.87736029379226</v>
       </c>
     </row>
     <row r="297">
@@ -64102,22 +64039,22 @@
         <v>10.8247430146753</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.000711824051625953</v>
+        <v>-0.000711727431911058</v>
       </c>
       <c r="D297" t="n">
-        <v>-0.0133645885801972</v>
+        <v>-0.013663260348963</v>
       </c>
       <c r="E297" t="n">
-        <v>-0.0251881037543153</v>
+        <v>-0.0243907448634593</v>
       </c>
       <c r="F297" t="n">
-        <v>-0.0206617450960831</v>
+        <v>-0.0243907448634593</v>
       </c>
       <c r="G297" t="n">
         <v>-0.056972542615096</v>
       </c>
       <c r="H297" t="n">
-        <v>1.48487823686153</v>
+        <v>1.59092879958548</v>
       </c>
     </row>
     <row r="298">
@@ -64128,22 +64065,22 @@
         <v>10.0746863304865</v>
       </c>
       <c r="C298" t="n">
-        <v>0.00357843059663931</v>
+        <v>0.00357837111728632</v>
       </c>
       <c r="D298" t="n">
-        <v>0.0235482357148715</v>
+        <v>0.0243927227895258</v>
       </c>
       <c r="E298" t="n">
-        <v>0.0246348504868008</v>
+        <v>0.0241764635085957</v>
       </c>
       <c r="F298" t="n">
-        <v>0.00767648023176637</v>
+        <v>0.0241764635085957</v>
       </c>
       <c r="G298" t="n">
         <v>0.043951170085772</v>
       </c>
       <c r="H298" t="n">
-        <v>2.90906789229904</v>
+        <v>3.07109556448173</v>
       </c>
     </row>
     <row r="299">
@@ -64154,22 +64091,22 @@
         <v>9.4854437340147</v>
       </c>
       <c r="C299" t="n">
-        <v>0.00685529003002294</v>
+        <v>0.00685529336821933</v>
       </c>
       <c r="D299" t="n">
-        <v>-0.00227463534089978</v>
+        <v>-0.00284409262913421</v>
       </c>
       <c r="E299" t="n">
-        <v>0.0273257438312609</v>
+        <v>0.0274604321097849</v>
       </c>
       <c r="F299" t="n">
-        <v>0.047541114712927</v>
+        <v>0.0274604321097849</v>
       </c>
       <c r="G299" t="n">
         <v>-0.0591536172422167</v>
       </c>
       <c r="H299" t="n">
-        <v>1.38529856328655</v>
+        <v>1.34388582264397</v>
       </c>
     </row>
     <row r="300">
@@ -64180,22 +64117,22 @@
         <v>7.56832065920089</v>
       </c>
       <c r="C300" t="n">
-        <v>0.0057590119598494</v>
+        <v>0.00575904155050022</v>
       </c>
       <c r="D300" t="n">
-        <v>0.00537335084088575</v>
+        <v>0.00509333612785401</v>
       </c>
       <c r="E300" t="n">
-        <v>-0.0169285646092749</v>
+        <v>-0.0177245554191412</v>
       </c>
       <c r="F300" t="n">
-        <v>-0.0146121302770332</v>
+        <v>-0.0177245554191412</v>
       </c>
       <c r="G300" t="n">
         <v>0.0477211489729266</v>
       </c>
       <c r="H300" t="n">
-        <v>0.582776681732034</v>
+        <v>0.742347607629205</v>
       </c>
     </row>
     <row r="301">
@@ -64206,22 +64143,22 @@
         <v>8.30170976857109</v>
       </c>
       <c r="C301" t="n">
-        <v>0.00602772213637692</v>
+        <v>0.00602767259205894</v>
       </c>
       <c r="D301" t="n">
-        <v>0.029375532964333</v>
+        <v>0.0296585051558047</v>
       </c>
       <c r="E301" t="n">
-        <v>0.0271032257906407</v>
+        <v>0.0288904857644967</v>
       </c>
       <c r="F301" t="n">
-        <v>-0.0036977650555734</v>
+        <v>0.0288904857644967</v>
       </c>
       <c r="G301" t="n">
         <v>0.0467019446526944</v>
       </c>
       <c r="H301" t="n">
-        <v>1.94155901596754</v>
+        <v>1.94267236875842</v>
       </c>
     </row>
     <row r="302">
@@ -64232,22 +64169,22 @@
         <v>10.5359243419983</v>
       </c>
       <c r="C302" t="n">
-        <v>0.0012652678059526</v>
+        <v>0.00126530390563584</v>
       </c>
       <c r="D302" t="n">
-        <v>0.0138068576825168</v>
+        <v>0.0140772899635495</v>
       </c>
       <c r="E302" t="n">
-        <v>0.00943086457633235</v>
+        <v>0.00837101266342799</v>
       </c>
       <c r="F302" t="n">
-        <v>0.00716474837963066</v>
+        <v>0.00837101266342799</v>
       </c>
       <c r="G302" t="n">
         <v>-0.0395886896821818</v>
       </c>
       <c r="H302" t="n">
-        <v>3.99504953625604</v>
+        <v>3.81157158409665</v>
       </c>
     </row>
     <row r="303">
@@ -64258,22 +64195,22 @@
         <v>10.5061622043855</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.0104329496060274</v>
+        <v>-0.0104329996999981</v>
       </c>
       <c r="D303" t="n">
-        <v>-0.0145574730761302</v>
+        <v>-0.014835885136339</v>
       </c>
       <c r="E303" t="n">
-        <v>-0.0210551567812214</v>
+        <v>-0.0230859133368577</v>
       </c>
       <c r="F303" t="n">
-        <v>-0.00259595791874112</v>
+        <v>-0.0230859133368577</v>
       </c>
       <c r="G303" t="n">
         <v>-0.135999774734448</v>
       </c>
       <c r="H303" t="n">
-        <v>1.55022151872453</v>
+        <v>1.41355497032088</v>
       </c>
     </row>
     <row r="304">
@@ -64284,22 +64221,22 @@
         <v>-8.30646670299831</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.0397403192858441</v>
+        <v>-0.0397402959348723</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.173837481603356</v>
+        <v>-0.174661669904945</v>
       </c>
       <c r="E304" t="n">
-        <v>-0.144529543136564</v>
+        <v>-0.137175627911942</v>
       </c>
       <c r="F304" t="n">
-        <v>-0.102727045953708</v>
+        <v>-0.137175627911942</v>
       </c>
       <c r="G304" t="n">
         <v>-0.487829973067159</v>
       </c>
       <c r="H304" t="n">
-        <v>-16.926515420224</v>
+        <v>-16.4562501659559</v>
       </c>
     </row>
     <row r="305">
@@ -64310,22 +64247,22 @@
         <v>-18.9001491697191</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.0297446074366681</v>
+        <v>-0.0297444981877071</v>
       </c>
       <c r="D305" t="n">
-        <v>-0.177085086873767</v>
+        <v>-0.177741813647963</v>
       </c>
       <c r="E305" t="n">
-        <v>-0.110826796454799</v>
+        <v>-0.114879711324027</v>
       </c>
       <c r="F305" t="n">
-        <v>0.00539006427749644</v>
+        <v>-0.114879711324027</v>
       </c>
       <c r="G305" t="n">
         <v>-0.591412654212734</v>
       </c>
       <c r="H305" t="n">
-        <v>-36.9750295445735</v>
+        <v>-37.4185344960246</v>
       </c>
     </row>
     <row r="306">
@@ -64336,22 +64273,22 @@
         <v>-6.05710456142092</v>
       </c>
       <c r="C306" t="n">
-        <v>0.0180168939544236</v>
+        <v>0.0166220884703412</v>
       </c>
       <c r="D306" t="n">
-        <v>0.268096664054067</v>
+        <v>0.269043270185956</v>
       </c>
       <c r="E306" t="n">
-        <v>0.148077172885269</v>
+        <v>0.147230962497022</v>
       </c>
       <c r="F306" t="n">
-        <v>0.0507322371908447</v>
+        <v>0.147230962497022</v>
       </c>
       <c r="G306" t="n">
         <v>0.534642809427288</v>
       </c>
       <c r="H306" t="n">
-        <v>-18.347309575339</v>
+        <v>-18.3202264548504</v>
       </c>
     </row>
     <row r="307">
@@ -64362,22 +64299,22 @@
         <v>-10.4609667399947</v>
       </c>
       <c r="C307" t="n">
-        <v>0.0159767941711841</v>
+        <v>0.0156514313029961</v>
       </c>
       <c r="D307" t="n">
-        <v>0.0257900359180079</v>
+        <v>0.026061592006676</v>
       </c>
       <c r="E307" t="n">
-        <v>0.0509981184853894</v>
+        <v>0.0506401018551275</v>
       </c>
       <c r="F307" t="n">
-        <v>0.0674226690818553</v>
+        <v>0.0506401018551275</v>
       </c>
       <c r="G307" t="n">
         <v>0.277576484551273</v>
       </c>
       <c r="H307" t="n">
-        <v>-11.3263587798715</v>
+        <v>-10.7479407954802</v>
       </c>
     </row>
     <row r="308">
@@ -64388,22 +64325,22 @@
         <v>-28.3622182859195</v>
       </c>
       <c r="C308" t="n">
-        <v>0.0136182904028699</v>
+        <v>0.0131889641480711</v>
       </c>
       <c r="D308" t="n">
-        <v>-0.0132015986374379</v>
+        <v>-0.0134803898388745</v>
       </c>
       <c r="E308" t="n">
-        <v>0.021569562547934</v>
+        <v>0.0211983502517716</v>
       </c>
       <c r="F308" t="n">
-        <v>-0.040684664856256</v>
+        <v>0.0211983502517716</v>
       </c>
       <c r="G308" t="n">
         <v>0.0515522373283153</v>
       </c>
       <c r="H308" t="n">
-        <v>-11.1097467153719</v>
+        <v>-10.9909537062449</v>
       </c>
     </row>
     <row r="309">
@@ -64414,22 +64351,22 @@
         <v>-16.3781805243493</v>
       </c>
       <c r="C309" t="n">
-        <v>0.0122786331151721</v>
+        <v>0.0123047507898262</v>
       </c>
       <c r="D309" t="n">
-        <v>0.0751161306413319</v>
+        <v>0.0751355235024231</v>
       </c>
       <c r="E309" t="n">
-        <v>0.0183384971992968</v>
+        <v>0.019016148069948</v>
       </c>
       <c r="F309" t="n">
-        <v>0.0331480512305076</v>
+        <v>0.019016148069948</v>
       </c>
       <c r="G309" t="n">
         <v>0.0297788716036136</v>
       </c>
       <c r="H309" t="n">
-        <v>-6.63932399691845</v>
+        <v>-6.71426221443072</v>
       </c>
     </row>
     <row r="310">
@@ -64440,22 +64377,22 @@
         <v>-22.7548156052561</v>
       </c>
       <c r="C310" t="n">
-        <v>0.00220885096189072</v>
+        <v>0.00275040884080457</v>
       </c>
       <c r="D310" t="n">
-        <v>-0.0647788710425328</v>
+        <v>-0.0639302117337808</v>
       </c>
       <c r="E310" t="n">
-        <v>-0.029908413414379</v>
+        <v>-0.0281525226257422</v>
       </c>
       <c r="F310" t="n">
-        <v>0.00834894315281343</v>
+        <v>-0.0281525226257422</v>
       </c>
       <c r="G310" t="n">
         <v>-0.060148937991201</v>
       </c>
       <c r="H310" t="n">
-        <v>-7.19655337562797</v>
+        <v>-7.2127828635295</v>
       </c>
     </row>
     <row r="311">
@@ -64466,22 +64403,22 @@
         <v>-20.21896329243</v>
       </c>
       <c r="C311" t="n">
-        <v>0.000959704299166475</v>
+        <v>0.00111045800709775</v>
       </c>
       <c r="D311" t="n">
-        <v>-0.0947126896632398</v>
+        <v>-0.0956344480637865</v>
       </c>
       <c r="E311" t="n">
-        <v>-0.024374341560895</v>
+        <v>-0.0250810725442951</v>
       </c>
       <c r="F311" t="n">
-        <v>0.00925562547587067</v>
+        <v>-0.0250810725442951</v>
       </c>
       <c r="G311" t="n">
         <v>-0.0156172247618178</v>
       </c>
       <c r="H311" t="n">
-        <v>-10.7414220840465</v>
+        <v>-10.8396745870892</v>
       </c>
     </row>
     <row r="312">
@@ -64492,22 +64429,22 @@
         <v>-13.0168313744087</v>
       </c>
       <c r="C312" t="n">
-        <v>0.0111264925004635</v>
+        <v>0.0109887863403895</v>
       </c>
       <c r="D312" t="n">
-        <v>0.106935737813203</v>
+        <v>0.107202129625503</v>
       </c>
       <c r="E312" t="n">
-        <v>0.0750032353813168</v>
+        <v>0.0744499060855333</v>
       </c>
       <c r="F312" t="n">
-        <v>-0.0103804967470209</v>
+        <v>0.0744499060855333</v>
       </c>
       <c r="G312" t="n">
         <v>0.0298149041662175</v>
       </c>
       <c r="H312" t="n">
-        <v>-4.53475324988197</v>
+        <v>-4.55111663903602</v>
       </c>
     </row>
     <row r="313">
@@ -64518,22 +64455,22 @@
         <v>-11.8706394654076</v>
       </c>
       <c r="C313" t="n">
-        <v>0.00788842293354897</v>
+        <v>0.00785576916521258</v>
       </c>
       <c r="D313" t="n">
-        <v>0.0377257168220417</v>
+        <v>0.037480575148332</v>
       </c>
       <c r="E313" t="n">
-        <v>0.0148573637802789</v>
+        <v>0.0138047743265455</v>
       </c>
       <c r="F313" t="n">
-        <v>-0.00620940017173144</v>
+        <v>0.0138047743265455</v>
       </c>
       <c r="G313" t="n">
         <v>0.10576333119248</v>
       </c>
       <c r="H313" t="n">
-        <v>-2.27722911885247</v>
+        <v>-2.26913944669881</v>
       </c>
     </row>
     <row r="314">
@@ -64544,22 +64481,22 @@
         <v>-8.99180361766136</v>
       </c>
       <c r="C314" t="n">
-        <v>0.000927289463891867</v>
+        <v>0.00115060196508665</v>
       </c>
       <c r="D314" t="n">
-        <v>-0.120465086245408</v>
+        <v>-0.120499873897743</v>
       </c>
       <c r="E314" t="n">
-        <v>-0.0165959026876816</v>
+        <v>-0.0166096090837131</v>
       </c>
       <c r="F314" t="n">
-        <v>-0.0226694955585316</v>
+        <v>-0.0166096090837131</v>
       </c>
       <c r="G314" t="n">
         <v>0.0938826253104343</v>
       </c>
       <c r="H314" t="n">
-        <v>-9.21924707546097</v>
+        <v>-9.32882148653456</v>
       </c>
     </row>
     <row r="315">
@@ -64570,22 +64507,22 @@
         <v>-4.97079765942217</v>
       </c>
       <c r="C315" t="n">
-        <v>0.014154194678305</v>
+        <v>0.0141639646721563</v>
       </c>
       <c r="D315" t="n">
-        <v>0.0563341963601145</v>
+        <v>0.0563493340190728</v>
       </c>
       <c r="E315" t="n">
-        <v>0.0310538456047347</v>
+        <v>0.0303440281076064</v>
       </c>
       <c r="F315" t="n">
-        <v>-0.0117843261694714</v>
+        <v>0.0303440281076064</v>
       </c>
       <c r="G315" t="n">
         <v>0.138588175868698</v>
       </c>
       <c r="H315" t="n">
-        <v>-6.93268330754348</v>
+        <v>-6.97971367024335</v>
       </c>
     </row>
     <row r="316">
@@ -64596,22 +64533,22 @@
         <v>0.15403463330702</v>
       </c>
       <c r="C316" t="n">
-        <v>0.0170786589442722</v>
+        <v>0.0173888212953681</v>
       </c>
       <c r="D316" t="n">
-        <v>0.0871759439865016</v>
+        <v>0.0871978347692401</v>
       </c>
       <c r="E316" t="n">
-        <v>0.0360974563783962</v>
+        <v>0.0406666199544521</v>
       </c>
       <c r="F316" t="n">
-        <v>0.0506986136079748</v>
+        <v>0.0406666199544521</v>
       </c>
       <c r="G316" t="n">
         <v>0.0607968497688551</v>
       </c>
       <c r="H316" t="n">
-        <v>-2.21487743555097</v>
+        <v>-2.41008581331609</v>
       </c>
     </row>
     <row r="317">
@@ -64622,22 +64559,22 @@
         <v>4.40047254125122</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0132379556945672</v>
+        <v>0.0137537019999527</v>
       </c>
       <c r="D317" t="n">
-        <v>0.0293666097198404</v>
+        <v>0.027980502042861</v>
       </c>
       <c r="E317" t="n">
-        <v>0.0255775364990667</v>
+        <v>0.0308535491185644</v>
       </c>
       <c r="F317" t="n">
-        <v>-0.0152701891117921</v>
+        <v>0.0308535491185644</v>
       </c>
       <c r="G317" t="n">
         <v>-0.0237789627954506</v>
       </c>
       <c r="H317" t="n">
-        <v>0.288554673193546</v>
+        <v>0.427477482560138</v>
       </c>
     </row>
     <row r="318">
@@ -64648,22 +64585,22 @@
         <v>5.48931714016443</v>
       </c>
       <c r="C318" t="n">
-        <v>0.00678993906285719</v>
+        <v>0.00644368854995392</v>
       </c>
       <c r="D318" t="n">
-        <v>-0.059199243791328</v>
+        <v>-0.0571591852486764</v>
       </c>
       <c r="E318" t="n">
-        <v>-0.0197180990883119</v>
+        <v>-0.02799877483681</v>
       </c>
       <c r="F318" t="n">
-        <v>-0.0273755105971247</v>
+        <v>-0.02799877483681</v>
       </c>
       <c r="G318" t="n">
         <v>0.0464469759903059</v>
       </c>
       <c r="H318" t="n">
-        <v>-1.69101556288397</v>
+        <v>-1.58199058082964</v>
       </c>
     </row>
     <row r="319">
@@ -64674,22 +64611,22 @@
         <v>8.16675140202263</v>
       </c>
       <c r="C319" t="n">
-        <v>0.0101703339399624</v>
+        <v>0.0099297626685404</v>
       </c>
       <c r="D319" t="n">
-        <v>0.0608316807054807</v>
+        <v>0.0605938168404023</v>
       </c>
       <c r="E319" t="n">
-        <v>0.0617090668220532</v>
+        <v>0.0613313165487233</v>
       </c>
       <c r="F319" t="n">
-        <v>0.0617255214660242</v>
+        <v>0.0613313165487233</v>
       </c>
       <c r="G319" t="n">
         <v>0.0867791468568546</v>
       </c>
       <c r="H319" t="n">
-        <v>2.15050621716755</v>
+        <v>2.0690588189946</v>
       </c>
     </row>
     <row r="320">
@@ -64700,22 +64637,22 @@
         <v>6.17283859500082</v>
       </c>
       <c r="C320" t="n">
-        <v>0.00540109833723168</v>
+        <v>0.00536799955119882</v>
       </c>
       <c r="D320" t="n">
-        <v>0.00660520231813599</v>
+        <v>0.00637039660096672</v>
       </c>
       <c r="E320" t="n">
-        <v>-0.0206281695225314</v>
+        <v>-0.0207153682100962</v>
       </c>
       <c r="F320" t="n">
-        <v>-0.00161961223999185</v>
+        <v>-0.0207153682100962</v>
       </c>
       <c r="G320" t="n">
         <v>0.0172408004419902</v>
       </c>
       <c r="H320" t="n">
-        <v>1.54409828827304</v>
+        <v>1.40132173241082</v>
       </c>
     </row>
     <row r="321">
@@ -64726,22 +64663,22 @@
         <v>1.52884710064101</v>
       </c>
       <c r="C321" t="n">
-        <v>0.00594261467080059</v>
+        <v>0.00585384495274344</v>
       </c>
       <c r="D321" t="n">
-        <v>-0.00307675124876017</v>
+        <v>-0.00283961134798627</v>
       </c>
       <c r="E321" t="n">
-        <v>0.044145941423074</v>
+        <v>0.0442622459219297</v>
       </c>
       <c r="F321" t="n">
-        <v>-0.0220924697871094</v>
+        <v>0.0442622459219297</v>
       </c>
       <c r="G321" t="n">
         <v>-0.0852333114705548</v>
       </c>
       <c r="H321" t="n">
-        <v>2.65313095107154</v>
+        <v>2.74940039536007</v>
       </c>
     </row>
     <row r="322">
@@ -64752,22 +64689,22 @@
         <v>5.2320936072352</v>
       </c>
       <c r="C322" t="n">
-        <v>0.00542484439137159</v>
+        <v>0.00555194022693239</v>
       </c>
       <c r="D322" t="n">
-        <v>-0.0134292527917248</v>
+        <v>-0.0127004467274343</v>
       </c>
       <c r="E322" t="n">
-        <v>0.00454233562275785</v>
+        <v>0.00834294972228733</v>
       </c>
       <c r="F322" t="n">
-        <v>0.023989722898528</v>
+        <v>0.00834294972228733</v>
       </c>
       <c r="G322" t="n">
         <v>0.0483247970916638</v>
       </c>
       <c r="H322" t="n">
-        <v>4.38253331699004</v>
+        <v>4.5216783548093</v>
       </c>
     </row>
     <row r="323">
@@ -64778,22 +64715,22 @@
         <v>5.70982526032642</v>
       </c>
       <c r="C323" t="n">
-        <v>0.00618972962150721</v>
+        <v>0.00575875398803305</v>
       </c>
       <c r="D323" t="n">
-        <v>0.0576592846165234</v>
+        <v>0.0574067304365631</v>
       </c>
       <c r="E323" t="n">
-        <v>0.00582112963014847</v>
+        <v>0.000804597584160405</v>
       </c>
       <c r="F323" t="n">
-        <v>0.0325894587733071</v>
+        <v>0.000804597584160405</v>
       </c>
       <c r="G323" t="n">
         <v>0.130975070203333</v>
       </c>
       <c r="H323" t="n">
-        <v>8.58977086467955</v>
+        <v>8.33876186483553</v>
       </c>
     </row>
     <row r="324">
@@ -64804,22 +64741,22 @@
         <v>3.38991983925259</v>
       </c>
       <c r="C324" t="n">
-        <v>0.00345890728784415</v>
+        <v>0.00334441288969423</v>
       </c>
       <c r="D324" t="n">
-        <v>-0.0297920672053449</v>
+        <v>-0.0304983020707912</v>
       </c>
       <c r="E324" t="n">
-        <v>0.0141259499403077</v>
+        <v>0.0142952514505561</v>
       </c>
       <c r="F324" t="n">
-        <v>-0.0507937694937706</v>
+        <v>0.0142952514505561</v>
       </c>
       <c r="G324" t="n">
         <v>-0.0580160620084866</v>
       </c>
       <c r="H324" t="n">
-        <v>10.889806102076</v>
+        <v>10.9121061121998</v>
       </c>
     </row>
     <row r="325">
@@ -64830,22 +64767,22 @@
         <v>4.1979198174148</v>
       </c>
       <c r="C325" t="n">
-        <v>0.00308834959404169</v>
+        <v>0.00299387384274219</v>
       </c>
       <c r="D325" t="n">
-        <v>-0.0213949947490537</v>
+        <v>-0.021399171134691</v>
       </c>
       <c r="E325" t="n">
-        <v>-0.0138727409693509</v>
+        <v>-0.012753138609038</v>
       </c>
       <c r="F325" t="n">
-        <v>0.0760721291807194</v>
+        <v>-0.012753138609038</v>
       </c>
       <c r="G325" t="n">
         <v>-0.0979073650524187</v>
       </c>
       <c r="H325" t="n">
-        <v>9.71249507972554</v>
+        <v>9.679501491215</v>
       </c>
     </row>
     <row r="326">
@@ -64856,22 +64793,22 @@
         <v>-0.0429938749660064</v>
       </c>
       <c r="C326" t="n">
-        <v>0.00514056885182956</v>
+        <v>0.00489135239539351</v>
       </c>
       <c r="D326" t="n">
-        <v>0.0108158494507276</v>
+        <v>0.0108179984015635</v>
       </c>
       <c r="E326" t="n">
-        <v>0.00105674277709333</v>
+        <v>-0.000865319072739901</v>
       </c>
       <c r="F326" t="n">
-        <v>0.0177869028489601</v>
+        <v>-0.000865319072739901</v>
       </c>
       <c r="G326" t="n">
         <v>0.147642838983266</v>
       </c>
       <c r="H326" t="n">
-        <v>7.67146913045303</v>
+        <v>7.79258924737821</v>
       </c>
     </row>
     <row r="327">
@@ -64882,22 +64819,22 @@
         <v>-3.85651041564982</v>
       </c>
       <c r="C327" t="n">
-        <v>0.00343518397508191</v>
+        <v>0.0032432574830441</v>
       </c>
       <c r="D327" t="n">
-        <v>0.0155106275756705</v>
+        <v>0.0155139111870328</v>
       </c>
       <c r="E327" t="n">
-        <v>0.0346303468131319</v>
+        <v>0.0341620741740476</v>
       </c>
       <c r="F327" t="n">
-        <v>0.0307454250396599</v>
+        <v>0.0341620741740476</v>
       </c>
       <c r="G327" t="n">
         <v>0.114660637767444</v>
       </c>
       <c r="H327" t="n">
-        <v>7.52323681853552</v>
+        <v>7.45566443815545</v>
       </c>
     </row>
     <row r="328">
@@ -64908,22 +64845,22 @@
         <v>-6.94756946533761</v>
       </c>
       <c r="C328" t="n">
-        <v>0.00370235773874406</v>
+        <v>0.00372233995470683</v>
       </c>
       <c r="D328" t="n">
-        <v>-0.000695187632857142</v>
+        <v>-0.000231820356690449</v>
       </c>
       <c r="E328" t="n">
-        <v>-0.00956369936640122</v>
+        <v>-0.00802895944674464</v>
       </c>
       <c r="F328" t="n">
-        <v>-0.026630988820239</v>
+        <v>-0.00802895944674464</v>
       </c>
       <c r="G328" t="n">
         <v>0.172220685969803</v>
       </c>
       <c r="H328" t="n">
-        <v>7.30039959279302</v>
+        <v>7.14900337644268</v>
       </c>
     </row>
     <row r="329">
@@ -64934,22 +64871,22 @@
         <v>-2.55719802243641</v>
       </c>
       <c r="C329" t="n">
-        <v>0.00512226668943239</v>
+        <v>0.00548205382488565</v>
       </c>
       <c r="D329" t="n">
-        <v>0.0100892408085231</v>
+        <v>0.0105407641481596</v>
       </c>
       <c r="E329" t="n">
-        <v>0.00321570946029492</v>
+        <v>0.00472927933858802</v>
       </c>
       <c r="F329" t="n">
-        <v>-0.00741305087029875</v>
+        <v>0.00472927933858802</v>
       </c>
       <c r="G329" t="n">
         <v>-0.0719799159340155</v>
       </c>
       <c r="H329" t="n">
-        <v>10.1972733902255</v>
+        <v>10.0232940172869</v>
       </c>
     </row>
     <row r="330">
@@ -64960,22 +64897,22 @@
         <v>-4.54735921073222</v>
       </c>
       <c r="C330" t="n">
-        <v>0.00284283478742875</v>
+        <v>0.00265424086445432</v>
       </c>
       <c r="D330" t="n">
-        <v>0.00660602759854623</v>
+        <v>0.00592286006295772</v>
       </c>
       <c r="E330" t="n">
-        <v>0.00603987669102768</v>
+        <v>0.00610925899312864</v>
       </c>
       <c r="F330" t="n">
-        <v>0.0362217489303989</v>
+        <v>0.00610925899312864</v>
       </c>
       <c r="G330" t="n">
         <v>0.133961071976582</v>
       </c>
       <c r="H330" t="n">
-        <v>11.41843946591</v>
+        <v>11.5009186210702</v>
       </c>
     </row>
     <row r="331">
@@ -64986,22 +64923,22 @@
         <v>-5.58537674895904</v>
       </c>
       <c r="C331" t="n">
-        <v>0.00205119607438498</v>
+        <v>0.00215506469172233</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.00780565872254435</v>
+        <v>-0.0080368059255882</v>
       </c>
       <c r="E331" t="n">
-        <v>-0.00814986957383201</v>
+        <v>-0.00854098635599065</v>
       </c>
       <c r="F331" t="n">
-        <v>0.0204284945002282</v>
+        <v>-0.00854098635599065</v>
       </c>
       <c r="G331" t="n">
         <v>0.0280197668305524</v>
       </c>
       <c r="H331" t="n">
-        <v>9.56893978169553</v>
+        <v>9.6649490712414</v>
       </c>
     </row>
     <row r="332">
@@ -65012,22 +64949,22 @@
         <v>-8.12892041156983</v>
       </c>
       <c r="C332" t="n">
-        <v>0.000637080354794151</v>
+        <v>0.000381696595113112</v>
       </c>
       <c r="D332" t="n">
-        <v>-0.00740038304551671</v>
+        <v>-0.00716888018004802</v>
       </c>
       <c r="E332" t="n">
-        <v>-0.00884740777093729</v>
+        <v>-0.0090562960821714</v>
       </c>
       <c r="F332" t="n">
-        <v>-0.0667631590447488</v>
+        <v>-0.0090562960821714</v>
       </c>
       <c r="G332" t="n">
         <v>-0.117683152329239</v>
       </c>
       <c r="H332" t="n">
-        <v>8.08085959736803</v>
+        <v>7.76143102927461</v>
       </c>
     </row>
     <row r="333">
@@ -65038,22 +64975,22 @@
         <v>-3.83082528313765</v>
       </c>
       <c r="C333" t="n">
-        <v>0.00343712882477831</v>
+        <v>0.00337875533631582</v>
       </c>
       <c r="D333" t="n">
-        <v>0.0107533863002267</v>
+        <v>0.0102993275777727</v>
       </c>
       <c r="E333" t="n">
-        <v>-0.00691448408940065</v>
+        <v>-0.00691433267537001</v>
       </c>
       <c r="F333" t="n">
-        <v>0.0340253522603753</v>
+        <v>-0.00691433267537001</v>
       </c>
       <c r="G333" t="n">
         <v>-0.131254504894844</v>
       </c>
       <c r="H333" t="n">
-        <v>8.58389714031255</v>
+        <v>8.84483737059684</v>
       </c>
     </row>
     <row r="334">
@@ -65064,22 +65001,22 @@
         <v>-5.67347079838543</v>
       </c>
       <c r="C334" t="n">
-        <v>0.00417301478533449</v>
+        <v>0.00376151227191723</v>
       </c>
       <c r="D334" t="n">
-        <v>0.0188560481411422</v>
+        <v>0.0184246333689124</v>
       </c>
       <c r="E334" t="n">
-        <v>0.0169236292314947</v>
+        <v>0.0129279129497819</v>
       </c>
       <c r="F334" t="n">
-        <v>0.0188555424605124</v>
+        <v>0.0129279129497819</v>
       </c>
       <c r="G334" t="n">
         <v>-0.0619102180616062</v>
       </c>
       <c r="H334" t="n">
-        <v>9.94697736624304</v>
+        <v>10.0351721115661</v>
       </c>
     </row>
     <row r="335">
@@ -65090,22 +65027,22 @@
         <v>-3.93567972362924</v>
       </c>
       <c r="C335" t="n">
-        <v>0.00311724109937028</v>
+        <v>0.00301329255090721</v>
       </c>
       <c r="D335" t="n">
-        <v>0.00357836164172642</v>
+        <v>0.00291188745023074</v>
       </c>
       <c r="E335" t="n">
-        <v>0.0233312935291234</v>
+        <v>0.0221781721839385</v>
       </c>
       <c r="F335" t="n">
-        <v>-0.049466637077356</v>
+        <v>0.0221781721839385</v>
       </c>
       <c r="G335" t="n">
         <v>0.0630446672531519</v>
       </c>
       <c r="H335" t="n">
-        <v>10.1549157825745</v>
+        <v>10.1784824948923</v>
       </c>
     </row>
     <row r="336">
@@ -65116,22 +65053,22 @@
         <v>-4.15454088006605</v>
       </c>
       <c r="C336" t="n">
-        <v>0.00137308616307141</v>
+        <v>0.00163217381698733</v>
       </c>
       <c r="D336" t="n">
-        <v>-0.00471849452696471</v>
+        <v>-0.00337173558440806</v>
       </c>
       <c r="E336" t="n">
-        <v>-0.0160008673644416</v>
+        <v>-0.0117164174318516</v>
       </c>
       <c r="F336" t="n">
-        <v>0.020608767354263</v>
+        <v>-0.0117164174318516</v>
       </c>
       <c r="G336" t="n">
         <v>-0.0574342036079578</v>
       </c>
       <c r="H336" t="n">
-        <v>10.883662479271</v>
+        <v>10.8893746248456</v>
       </c>
     </row>
     <row r="337">
@@ -65142,22 +65079,22 @@
         <v>-7.83050282471185</v>
       </c>
       <c r="C337" t="n">
-        <v>0.000255210306578491</v>
+        <v>0.00035266379872656</v>
       </c>
       <c r="D337" t="n">
-        <v>-0.0152874346713876</v>
+        <v>-0.0152903507862057</v>
       </c>
       <c r="E337" t="n">
-        <v>-0.00683958993083511</v>
+        <v>-0.00962574030017915</v>
       </c>
       <c r="F337" t="n">
-        <v>0.0230587698888556</v>
+        <v>-0.00962574030017915</v>
       </c>
       <c r="G337" t="n">
         <v>-0.109609953721625</v>
       </c>
       <c r="H337" t="n">
-        <v>10.5842539445795</v>
+        <v>10.3219765434348</v>
       </c>
     </row>
     <row r="338">
@@ -65168,22 +65105,22 @@
         <v>-6.07509774202367</v>
       </c>
       <c r="C338" t="n">
-        <v>0.000901803738735829</v>
+        <v>0.00102753322800009</v>
       </c>
       <c r="D338" t="n">
-        <v>0.0143924761519036</v>
+        <v>0.0143957436820203</v>
       </c>
       <c r="E338" t="n">
-        <v>-0.00484682350379195</v>
+        <v>-0.00180120524762284</v>
       </c>
       <c r="F338" t="n">
-        <v>-0.0408020560815965</v>
+        <v>-0.00180120524762284</v>
       </c>
       <c r="G338" t="n">
         <v>0.00781136425934914</v>
       </c>
       <c r="H338" t="n">
-        <v>11.707192024437</v>
+        <v>11.622725362259</v>
       </c>
     </row>
     <row r="339">
@@ -65194,22 +65131,22 @@
         <v>-7.13224673949046</v>
       </c>
       <c r="C339" t="n">
-        <v>0.00200786594952973</v>
+        <v>0.0019987095421623</v>
       </c>
       <c r="D339" t="n">
-        <v>0.00581265939491438</v>
+        <v>0.00581347878815119</v>
       </c>
       <c r="E339" t="n">
-        <v>0.00932032713346764</v>
+        <v>0.00790717386840534</v>
       </c>
       <c r="F339" t="n">
-        <v>0.0773961032772146</v>
+        <v>0.00790717386840534</v>
       </c>
       <c r="G339" t="n">
         <v>0.015556690509392</v>
       </c>
       <c r="H339" t="n">
-        <v>12.7545393659825</v>
+        <v>12.4445512056652</v>
       </c>
     </row>
     <row r="340">
@@ -65220,22 +65157,22 @@
         <v>-7.35343024052726</v>
       </c>
       <c r="C340" t="n">
-        <v>0.00192559274909332</v>
+        <v>0.00256605461620385</v>
       </c>
       <c r="D340" t="n">
-        <v>-0.0124496551216726</v>
+        <v>-0.0122232123851802</v>
       </c>
       <c r="E340" t="n">
-        <v>0.00955454395867683</v>
+        <v>0.0209407899693632</v>
       </c>
       <c r="F340" t="n">
-        <v>-0.0285073674937966</v>
+        <v>0.0209407899693632</v>
       </c>
       <c r="G340" t="n">
         <v>-0.029810176880388</v>
       </c>
       <c r="H340" t="n">
-        <v>12.469069332585</v>
+        <v>12.5160283789375</v>
       </c>
     </row>
     <row r="341">
@@ -65246,22 +65183,22 @@
         <v>-10.8139013249451</v>
       </c>
       <c r="C341" t="n">
-        <v>0.00328561197824939</v>
+        <v>0.0028587484389595</v>
       </c>
       <c r="D341" t="n">
-        <v>0.00607480041913888</v>
+        <v>0.00495573146255968</v>
       </c>
       <c r="E341" t="n">
-        <v>-0.00667068418285588</v>
+        <v>-0.0140480495581441</v>
       </c>
       <c r="F341" t="n">
-        <v>-0.00732752380020507</v>
+        <v>-0.0140480495581441</v>
       </c>
       <c r="G341" t="n">
         <v>0.0781727943658606</v>
       </c>
       <c r="H341" t="n">
-        <v>12.5458540476005</v>
+        <v>12.6774312825237</v>
       </c>
     </row>
     <row r="342">
@@ -65272,22 +65209,22 @@
         <v>-12.4889359819719</v>
       </c>
       <c r="C342" t="n">
-        <v>0.00472338142674822</v>
+        <v>0.00463145349552807</v>
       </c>
       <c r="D342" t="n">
-        <v>0.0120023147522623</v>
+        <v>0.0128947835893349</v>
       </c>
       <c r="E342" t="n">
-        <v>0.00731008338638706</v>
+        <v>0.00666930653840314</v>
       </c>
       <c r="F342" t="n">
-        <v>-0.0377923674762402</v>
+        <v>0.00666930653840314</v>
       </c>
       <c r="G342" t="n">
         <v>-0.10025552330552</v>
       </c>
       <c r="H342" t="n">
-        <v>13.359622920146</v>
+        <v>13.3639187789129</v>
       </c>
     </row>
     <row r="343">
@@ -65298,22 +65235,22 @@
         <v>-9.53832626956467</v>
       </c>
       <c r="C343" t="n">
-        <v>0.00280872502587748</v>
+        <v>0.0031400278012006</v>
       </c>
       <c r="D343" t="n">
-        <v>0.00111067131695908</v>
+        <v>0.00155359608053907</v>
       </c>
       <c r="E343" t="n">
-        <v>-0.0138341537187552</v>
+        <v>-0.0147477971434151</v>
       </c>
       <c r="F343" t="n">
-        <v>-0.00279662175993511</v>
+        <v>-0.0147477971434151</v>
       </c>
       <c r="G343" t="n">
         <v>0.00767659369240192</v>
       </c>
       <c r="H343" t="n">
-        <v>11.9368202642556</v>
+        <v>12.1987901978882</v>
       </c>
     </row>
     <row r="344">
@@ -65324,22 +65261,22 @@
         <v>-7.90627273200948</v>
       </c>
       <c r="C344" t="n">
-        <v>0.00151543170884505</v>
+        <v>0.00145724014673121</v>
       </c>
       <c r="D344" t="n">
-        <v>-0.00423644877722662</v>
+        <v>-0.00445958816230885</v>
       </c>
       <c r="E344" t="n">
-        <v>-0.00783001768172298</v>
+        <v>-0.00845677516821741</v>
       </c>
       <c r="F344" t="n">
-        <v>0.000587413792453972</v>
+        <v>-0.00845677516821741</v>
       </c>
       <c r="G344" t="n">
         <v>0.0508966285065879</v>
       </c>
       <c r="H344" t="n">
-        <v>12.2226213979261</v>
+        <v>12.1237431354254</v>
       </c>
     </row>
     <row r="345">
@@ -65350,22 +65287,22 @@
         <v>-9.71138161134929</v>
       </c>
       <c r="C345" t="n">
-        <v>0.00153285155142324</v>
+        <v>0.00138413925049719</v>
       </c>
       <c r="D345" t="n">
-        <v>0.0422927921830114</v>
+        <v>0.0420891987498315</v>
       </c>
       <c r="E345" t="n">
-        <v>0.0386971816150856</v>
+        <v>0.0388762212871931</v>
       </c>
       <c r="F345" t="n">
-        <v>0.0461090023982242</v>
+        <v>0.0388762212871931</v>
       </c>
       <c r="G345" t="n">
         <v>0.0859020915955186</v>
       </c>
       <c r="H345" t="n">
-        <v>12.5364689664365</v>
+        <v>12.9095778061306</v>
       </c>
     </row>
     <row r="346">
@@ -65376,22 +65313,22 @@
         <v>-8.34278873041409</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.00633895703437481</v>
+        <v>-0.00622938518718907</v>
       </c>
       <c r="D346" t="n">
-        <v>-0.0321854184373445</v>
+        <v>-0.0324204126504828</v>
       </c>
       <c r="E346" t="n">
-        <v>-0.0427450300611874</v>
+        <v>-0.0442186719620405</v>
       </c>
       <c r="F346" t="n">
-        <v>-0.02704786085721</v>
+        <v>-0.0442186719620405</v>
       </c>
       <c r="G346" t="n">
         <v>0.114241868001319</v>
       </c>
       <c r="H346" t="n">
-        <v>8.98319473779203</v>
+        <v>8.79638433725086</v>
       </c>
     </row>
     <row r="347">
@@ -65402,22 +65339,22 @@
         <v>-11.8611423674259</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.024475223461458</v>
+        <v>-0.0235949581397019</v>
       </c>
       <c r="D347" t="n">
-        <v>-0.178115315860325</v>
+        <v>-0.177279220322491</v>
       </c>
       <c r="E347" t="n">
-        <v>-0.142485116438815</v>
+        <v>-0.140615062721304</v>
       </c>
       <c r="F347" t="n">
-        <v>-0.054681892940895</v>
+        <v>-0.140615062721304</v>
       </c>
       <c r="G347" t="n">
         <v>-0.00745252101052074</v>
       </c>
       <c r="H347" t="n">
-        <v>-6.24160001356646</v>
+        <v>-6.04091100986592</v>
       </c>
     </row>
     <row r="348">
@@ -65428,22 +65365,22 @@
         <v>-9.83902145226969</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.00596446315184185</v>
+        <v>-0.00592300583289251</v>
       </c>
       <c r="D348" t="n">
-        <v>0.061870245345224</v>
+        <v>0.0613982136964193</v>
       </c>
       <c r="E348" t="n">
-        <v>0.0307492470818982</v>
+        <v>0.0278207532170507</v>
       </c>
       <c r="F348" t="n">
-        <v>0.00596159325902068</v>
+        <v>0.0278207532170507</v>
       </c>
       <c r="G348" t="n">
         <v>-0.138963040772018</v>
       </c>
       <c r="H348" t="n">
-        <v>-5.93424066544397</v>
+        <v>-6.15263378999366</v>
       </c>
     </row>
     <row r="349">
@@ -65454,22 +65391,22 @@
         <v>-10.2040762272255</v>
       </c>
       <c r="C349" t="n">
-        <v>0.0046866436702464</v>
+        <v>0.00436957611823985</v>
       </c>
       <c r="D349" t="n">
-        <v>0.109116226448232</v>
+        <v>0.109139258796985</v>
       </c>
       <c r="E349" t="n">
-        <v>0.0771174831143755</v>
+        <v>0.0769702315111411</v>
       </c>
       <c r="F349" t="n">
-        <v>-0.0323164187672189</v>
+        <v>0.0769702315111411</v>
       </c>
       <c r="G349" t="n">
         <v>-0.112488944341681</v>
       </c>
       <c r="H349" t="n">
-        <v>-1.23281759683246</v>
+        <v>-1.49856546461945</v>
       </c>
     </row>
     <row r="350">
@@ -65480,22 +65417,22 @@
         <v>-10.4601955182863</v>
       </c>
       <c r="C350" t="n">
-        <v>0.00593544374947896</v>
+        <v>0.00528157978948851</v>
       </c>
       <c r="D350" t="n">
-        <v>0.0407938747402286</v>
+        <v>0.0406022153982644</v>
       </c>
       <c r="E350" t="n">
-        <v>0.0296229010166016</v>
+        <v>0.030509447074988</v>
       </c>
       <c r="F350" t="n">
-        <v>0.0411142609727815</v>
+        <v>0.030509447074988</v>
       </c>
       <c r="G350" t="n">
         <v>0.0454109968236418</v>
       </c>
       <c r="H350" t="n">
-        <v>3.13474803359804</v>
+        <v>2.90179263341079</v>
       </c>
     </row>
     <row r="351">
@@ -65506,22 +65443,22 @@
         <v>-10.3943395874101</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.000201056188191551</v>
+        <v>0.000257910396033623</v>
       </c>
       <c r="D351" t="n">
-        <v>-0.0293471701779051</v>
+        <v>-0.029138493401093</v>
       </c>
       <c r="E351" t="n">
-        <v>-0.0108522614782984</v>
+        <v>-0.0121533627139891</v>
       </c>
       <c r="F351" t="n">
-        <v>-0.0358324939032109</v>
+        <v>-0.0121533627139891</v>
       </c>
       <c r="G351" t="n">
         <v>0.0156698531287605</v>
       </c>
       <c r="H351" t="n">
-        <v>1.24330571698154</v>
+        <v>1.23043140060404</v>
       </c>
     </row>
     <row r="352">
@@ -65532,22 +65469,22 @@
         <v>-9.16134793973992</v>
       </c>
       <c r="C352" t="n">
-        <v>0.00180704196809511</v>
+        <v>0.0019543738847263</v>
       </c>
       <c r="D352" t="n">
-        <v>0.0205595809884187</v>
+        <v>0.0211800979154884</v>
       </c>
       <c r="E352" t="n">
-        <v>0.0175541664068337</v>
+        <v>0.0139053391511554</v>
       </c>
       <c r="F352" t="n">
-        <v>0.00820096981890917</v>
+        <v>0.0139053391511554</v>
       </c>
       <c r="G352" t="n">
         <v>0.0402134242337269</v>
       </c>
       <c r="H352" t="n">
-        <v>2.66613779705003</v>
+        <v>2.58280848698126</v>
       </c>
     </row>
     <row r="353">
@@ -65558,22 +65495,22 @@
         <v>-10.9506837463987</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.000421314093965286</v>
+        <v>0.000533284596984096</v>
       </c>
       <c r="D353" t="n">
-        <v>-0.00442420245957731</v>
+        <v>-0.00442327667152931</v>
       </c>
       <c r="E353" t="n">
-        <v>0.000238462062762679</v>
+        <v>0.0138078934340635</v>
       </c>
       <c r="F353" t="n">
-        <v>0.0215208121927137</v>
+        <v>0.0138078934340635</v>
       </c>
       <c r="G353" t="n">
         <v>0.071732176818907</v>
       </c>
       <c r="H353" t="n">
-        <v>1.51933640128853</v>
+        <v>1.88675490586749</v>
       </c>
     </row>
     <row r="354">
@@ -65584,22 +65521,22 @@
         <v>-14.0916133655875</v>
       </c>
       <c r="C354" t="n">
-        <v>0.000503939538729625</v>
+        <v>-0.0000208899554987596</v>
       </c>
       <c r="D354" t="n">
-        <v>0.00503100245698018</v>
+        <v>0.00482126197169297</v>
       </c>
       <c r="E354" t="n">
-        <v>0.0157648083678472</v>
+        <v>0.0108707863759143</v>
       </c>
       <c r="F354" t="n">
-        <v>0.0131465913823385</v>
+        <v>0.0108707863759143</v>
       </c>
       <c r="G354" t="n">
         <v>-0.0887468733343653</v>
       </c>
       <c r="H354" t="n">
-        <v>1.77874705346504</v>
+        <v>1.92624500630872</v>
       </c>
     </row>
     <row r="355">
@@ -65610,22 +65547,22 @@
         <v>-13.9289806310653</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.000417742620959061</v>
+        <v>0.000508400140113885</v>
       </c>
       <c r="D355" t="n">
-        <v>0.0132397008811251</v>
+        <v>0.0132371891124423</v>
       </c>
       <c r="E355" t="n">
-        <v>0.00990003661911132</v>
+        <v>0.00918128756633596</v>
       </c>
       <c r="F355" t="n">
-        <v>0.000321814320614067</v>
+        <v>0.00918128756633596</v>
       </c>
       <c r="G355" t="n">
         <v>0.0133548613268477</v>
       </c>
       <c r="H355" t="n">
-        <v>2.09533259127455</v>
+        <v>2.14589180891095</v>
       </c>
     </row>
     <row r="356">
@@ -65636,22 +65573,22 @@
         <v>-11.0996444180921</v>
       </c>
       <c r="C356" t="n">
-        <v>0.000570955359569858</v>
+        <v>-0.000621031767093605</v>
       </c>
       <c r="D356" t="n">
-        <v>0.0146768552522243</v>
+        <v>0.0144722563582995</v>
       </c>
       <c r="E356" t="n">
-        <v>0.0101082698338626</v>
+        <v>0.00856382047808335</v>
       </c>
       <c r="F356" t="n">
-        <v>0.0125824915063619</v>
+        <v>0.00856382047808335</v>
       </c>
       <c r="G356" t="n">
         <v>0.00789324660027191</v>
       </c>
       <c r="H356" t="n">
-        <v>4.62398794983903</v>
+        <v>4.12485985157818</v>
       </c>
     </row>
     <row r="357">
@@ -65662,22 +65599,22 @@
         <v>-12.1397375095399</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.00297624128645069</v>
+        <v>-0.00220947717456355</v>
       </c>
       <c r="D357" t="n">
-        <v>-0.0361220519135879</v>
+        <v>-0.0365592681378084</v>
       </c>
       <c r="E357" t="n">
-        <v>-0.0224609124760429</v>
+        <v>-0.0221539674091753</v>
       </c>
       <c r="F357" t="n">
-        <v>-0.0145463429921904</v>
+        <v>-0.0221539674091753</v>
       </c>
       <c r="G357" t="n">
         <v>-0.0602561443723069</v>
       </c>
       <c r="H357" t="n">
-        <v>2.36289839289554</v>
+        <v>2.74435629999242</v>
       </c>
     </row>
     <row r="358">
@@ -65688,22 +65625,22 @@
         <v>-10.5033179325077</v>
       </c>
       <c r="C358" t="n">
-        <v>0.00146136350813286</v>
+        <v>0.00159593689626902</v>
       </c>
       <c r="D358" t="n">
-        <v>0.0137480667114716</v>
+        <v>0.0141637181135508</v>
       </c>
       <c r="E358" t="n">
-        <v>0.00506962335348238</v>
+        <v>0.00266217699702942</v>
       </c>
       <c r="F358" t="n">
-        <v>0.0163100500824847</v>
+        <v>0.00266217699702942</v>
       </c>
       <c r="G358" t="n">
         <v>-0.0857007940461116</v>
       </c>
       <c r="H358" t="n">
-        <v>2.48978730202805</v>
+        <v>2.73392404110465</v>
       </c>
     </row>
     <row r="359">
@@ -65714,22 +65651,22 @@
         <v>-10.6300585687565</v>
       </c>
       <c r="C359" t="n">
-        <v>0.00167705369066251</v>
+        <v>0.00105238889149906</v>
       </c>
       <c r="D359" t="n">
-        <v>0.0107150625923325</v>
+        <v>0.00989894247925438</v>
       </c>
       <c r="E359" t="n">
-        <v>-0.0039430858017484</v>
+        <v>0.00286769370453044</v>
       </c>
       <c r="F359" t="n">
-        <v>0.0119352072368244</v>
+        <v>0.00286769370453044</v>
       </c>
       <c r="G359" t="n">
         <v>0.0250213846065046</v>
       </c>
       <c r="H359" t="n">
-        <v>0.934875677646537</v>
+        <v>1.43538975547187</v>
       </c>
     </row>
     <row r="360">
@@ -65740,22 +65677,22 @@
         <v>-13.0186618077753</v>
       </c>
       <c r="C360" t="n">
-        <v>0.00122556671304341</v>
+        <v>0.000594948302484077</v>
       </c>
       <c r="D360" t="n">
-        <v>0.0190021261416033</v>
+        <v>0.0194152576522892</v>
       </c>
       <c r="E360" t="n">
-        <v>0.0161810725765204</v>
+        <v>0.00767862168126854</v>
       </c>
       <c r="F360" t="n">
-        <v>-0.0181480724530001</v>
+        <v>0.00767862168126854</v>
       </c>
       <c r="G360" t="n">
         <v>-0.0332508378942515</v>
       </c>
       <c r="H360" t="n">
-        <v>0.0406477226300265</v>
+        <v>-0.119861646981877</v>
       </c>
     </row>
     <row r="361">
@@ -65766,22 +65703,22 @@
         <v>-11.9083646833462</v>
       </c>
       <c r="C361" t="n">
-        <v>0.00407065861426847</v>
+        <v>0.00468567218457316</v>
       </c>
       <c r="D361" t="n">
-        <v>0.0290528457570938</v>
+        <v>0.0294450152800545</v>
       </c>
       <c r="E361" t="n">
-        <v>0.0552228067294305</v>
+        <v>0.0551803786085854</v>
       </c>
       <c r="F361" t="n">
-        <v>0.0454763966368512</v>
+        <v>0.0551803786085854</v>
       </c>
       <c r="G361" t="n">
         <v>-0.0229392558187467</v>
       </c>
       <c r="H361" t="n">
-        <v>5.77930538145055</v>
+        <v>5.16182092345434</v>
       </c>
     </row>
     <row r="362">
@@ -65792,22 +65729,22 @@
         <v>-11.8591778143459</v>
       </c>
       <c r="C362" t="n">
-        <v>0.000504381466867265</v>
+        <v>-0.00303450136230055</v>
       </c>
       <c r="D362" t="n">
-        <v>-0.0177797479686701</v>
+        <v>-0.0183901357967677</v>
       </c>
       <c r="E362" t="n">
-        <v>-0.0563632606249982</v>
+        <v>-0.0542466548325971</v>
       </c>
       <c r="F362" t="n">
-        <v>-0.0347268276422303</v>
+        <v>-0.0542466548325971</v>
       </c>
       <c r="G362" t="n">
         <v>0.0487697737378134</v>
       </c>
       <c r="H362" t="n">
-        <v>2.35700031659704</v>
+        <v>2.14646401612359</v>
       </c>
     </row>
     <row r="363">
@@ -65818,22 +65755,22 @@
         <v>-6.24151559111076</v>
       </c>
       <c r="C363" t="n">
-        <v>0.000997169217985316</v>
+        <v>0.00072549140380751</v>
       </c>
       <c r="D363" t="n">
-        <v>0.0015957290938502</v>
+        <v>0.00199433991165154</v>
       </c>
       <c r="E363" t="n">
-        <v>0.0246124225167677</v>
+        <v>0.0235530465832943</v>
       </c>
       <c r="F363" t="n">
-        <v>0.0423437009543095</v>
+        <v>0.0235530465832943</v>
       </c>
       <c r="G363" t="n">
         <v>-0.0482903771460723</v>
       </c>
       <c r="H363" t="n">
-        <v>4.59476234348855</v>
+        <v>3.98699906524081</v>
       </c>
     </row>
     <row r="364">
@@ -65842,22 +65779,22 @@
       </c>
       <c r="B364"/>
       <c r="C364" t="n">
-        <v>0.00165270022768382</v>
+        <v>0.00322452592046307</v>
       </c>
       <c r="D364" t="n">
-        <v>0.0135743367211401</v>
+        <v>0.0147416385525725</v>
       </c>
       <c r="E364" t="n">
-        <v>-0.00814989871745908</v>
+        <v>0.00262201181792854</v>
       </c>
       <c r="F364" t="n">
-        <v>-0.00204507011964594</v>
+        <v>0.00262201181792854</v>
       </c>
       <c r="G364" t="n">
         <v>-0.0278838637695822</v>
       </c>
       <c r="H364" t="n">
-        <v>5.34546325138504</v>
+        <v>5.65439757000805</v>
       </c>
     </row>
     <row r="365">
@@ -65866,22 +65803,22 @@
       </c>
       <c r="B365"/>
       <c r="C365" t="n">
-        <v>-0.00297980234456841</v>
+        <v>-0.00386546696053802</v>
       </c>
       <c r="D365" t="n">
-        <v>-0.0107379341014253</v>
+        <v>-0.012336399678853</v>
       </c>
       <c r="E365" t="n">
-        <v>-0.00396880597650817</v>
+        <v>-0.00745381749883745</v>
       </c>
       <c r="F365" t="n">
-        <v>0.00577540357431694</v>
+        <v>-0.00745381749883745</v>
       </c>
       <c r="G365" t="n">
         <v>-0.0732225900928816</v>
       </c>
       <c r="H365" t="n">
-        <v>3.33582521126655</v>
+        <v>4.12520297072527</v>
       </c>
     </row>
     <row r="366">
@@ -65890,22 +65827,22 @@
       </c>
       <c r="B366"/>
       <c r="C366" t="n">
-        <v>-0.00143525928089172</v>
+        <v>-0.000375095741393494</v>
       </c>
       <c r="D366" t="n">
-        <v>0.00671609954728059</v>
+        <v>0.00770023905360784</v>
       </c>
       <c r="E366" t="n">
-        <v>0.00026257646993777</v>
+        <v>-0.00148500360788706</v>
       </c>
       <c r="F366" t="n">
-        <v>0.0686060086990627</v>
+        <v>-0.00148500360788706</v>
       </c>
       <c r="G366" t="n">
         <v>-0.0533773945248912</v>
       </c>
       <c r="H366" t="n">
-        <v>4.40470393118703</v>
+        <v>4.5043227682475</v>
       </c>
     </row>
     <row r="367">
@@ -65914,22 +65851,22 @@
       </c>
       <c r="B367"/>
       <c r="C367" t="n">
-        <v>-0.00994614227011592</v>
+        <v>-0.010666861744328</v>
       </c>
       <c r="D367" t="n">
-        <v>-0.116437393630652</v>
+        <v>-0.116632676939073</v>
       </c>
       <c r="E367" t="n">
-        <v>-0.10692614843264</v>
+        <v>-0.107753297613235</v>
       </c>
       <c r="F367" t="n">
-        <v>-0.127282554988592</v>
+        <v>-0.107753297613235</v>
       </c>
       <c r="G367" t="n">
         <v>0.066502064849975</v>
       </c>
       <c r="H367" t="n">
-        <v>-8.07511165690146</v>
+        <v>-7.94524597317724</v>
       </c>
     </row>
     <row r="368">
@@ -65938,22 +65875,22 @@
       </c>
       <c r="B368"/>
       <c r="C368" t="n">
-        <v>0.0144455042467646</v>
+        <v>0.0141998213141736</v>
       </c>
       <c r="D368" t="n">
-        <v>0.168845625693654</v>
+        <v>0.168813801864069</v>
       </c>
       <c r="E368" t="n">
-        <v>0.146634334679731</v>
+        <v>0.144561809533449</v>
       </c>
       <c r="F368" t="n">
-        <v>0.101113707037259</v>
+        <v>0.144561809533449</v>
       </c>
       <c r="G368" t="n">
         <v>-0.0387923065954858</v>
       </c>
       <c r="H368" t="n">
-        <v>6.32768422592203</v>
+        <v>6.00390328513599</v>
       </c>
     </row>
     <row r="369">
@@ -65962,22 +65899,22 @@
       </c>
       <c r="B369"/>
       <c r="C369" t="n">
-        <v>0.000171382128206332</v>
+        <v>-0.000646658418035351</v>
       </c>
       <c r="D369" t="n">
-        <v>-0.0446595669329826</v>
+        <v>-0.0450516341752465</v>
       </c>
       <c r="E369" t="n">
-        <v>-0.0374177304798637</v>
+        <v>-0.0369857619919669</v>
       </c>
       <c r="F369" t="n">
-        <v>0.049686878218683</v>
+        <v>-0.0369857619919669</v>
       </c>
       <c r="G369" t="n">
         <v>-0.0467641584441516</v>
       </c>
       <c r="H369" t="n">
-        <v>2.84878370725753</v>
+        <v>3.20873010946621</v>
       </c>
     </row>
     <row r="370">
@@ -65986,22 +65923,22 @@
       </c>
       <c r="B370"/>
       <c r="C370" t="n">
-        <v>0.00235562772610454</v>
+        <v>0.0023555842374412</v>
       </c>
       <c r="D370" t="n">
-        <v>0.0266729105849723</v>
+        <v>0.0261320866397696</v>
       </c>
       <c r="E370" t="n">
-        <v>0.0293572623974461</v>
+        <v>0.0316412925682092</v>
       </c>
       <c r="F370" t="n">
-        <v>-0.051832588014201</v>
+        <v>0.0316412925682092</v>
       </c>
       <c r="G370" t="n">
         <v>-0.0238759527660806</v>
       </c>
       <c r="H370" t="n">
-        <v>4.54006949050904</v>
+        <v>4.73288350930245</v>
       </c>
     </row>
     <row r="371">
@@ -66010,22 +65947,22 @@
       </c>
       <c r="B371"/>
       <c r="C371" t="n">
-        <v>0.00474417084919398</v>
+        <v>0.00390590273940372</v>
       </c>
       <c r="D371" t="n">
-        <v>-0.00562635552098989</v>
+        <v>-0.00468790042367573</v>
       </c>
       <c r="E371" t="n">
-        <v>0.000396488998574362</v>
+        <v>-0.00973909089480962</v>
       </c>
       <c r="F371" t="n">
-        <v>0.0162453550647008</v>
+        <v>-0.00973909089480962</v>
       </c>
       <c r="G371" t="n">
         <v>-0.0728257038510822</v>
       </c>
       <c r="H371" t="n">
-        <v>4.70583669644454</v>
+        <v>4.32399001684766</v>
       </c>
     </row>
     <row r="372">
@@ -66034,22 +65971,22 @@
       </c>
       <c r="B372"/>
       <c r="C372" t="n">
-        <v>0.00631708907914952</v>
+        <v>0.00619158840507339</v>
       </c>
       <c r="D372" t="n">
-        <v>0.0207544819426753</v>
+        <v>0.0202110342607025</v>
       </c>
       <c r="E372" t="n">
-        <v>-0.00012251501489402</v>
+        <v>0.00435999569653855</v>
       </c>
       <c r="F372" t="n">
-        <v>0.0604522006528718</v>
+        <v>0.00435999569653855</v>
       </c>
       <c r="G372" t="n">
         <v>-0.0168369827185195</v>
       </c>
       <c r="H372" t="n">
-        <v>6.67255843565705</v>
+        <v>6.1920809421229</v>
       </c>
     </row>
     <row r="373">
@@ -66058,22 +65995,22 @@
       </c>
       <c r="B373"/>
       <c r="C373" t="n">
-        <v>0.0031997597654474</v>
+        <v>0.00308296014079623</v>
       </c>
       <c r="D373" t="n">
-        <v>-0.00424194179540116</v>
+        <v>-0.00368811120056733</v>
       </c>
       <c r="E373" t="n">
-        <v>-0.0103321534644927</v>
+        <v>-0.0118983867245346</v>
       </c>
       <c r="F373" t="n">
-        <v>-0.0361584735401719</v>
+        <v>-0.0118983867245346</v>
       </c>
       <c r="G373" t="n">
         <v>-0.0476752606608901</v>
       </c>
       <c r="H373" t="n">
-        <v>4.04302949971753</v>
+        <v>4.34202817851713</v>
       </c>
     </row>
     <row r="374">
@@ -66082,22 +66019,22 @@
       </c>
       <c r="B374"/>
       <c r="C374" t="n">
-        <v>0.0045918971717045</v>
+        <v>0.00279159938063334</v>
       </c>
       <c r="D374" t="n">
-        <v>0.0107644075606901</v>
+        <v>0.00985947081647343</v>
       </c>
       <c r="E374" t="n">
-        <v>0.0316012053721799</v>
+        <v>0.034741634223125</v>
       </c>
       <c r="F374" t="n">
-        <v>0.0266420701713264</v>
+        <v>0.034741634223125</v>
       </c>
       <c r="G374" t="n">
         <v>0.0204186334910021</v>
       </c>
       <c r="H374" t="n">
-        <v>5.05566806323005</v>
+        <v>6.33128863858237</v>
       </c>
     </row>
     <row r="375">
@@ -66106,20 +66043,22 @@
       </c>
       <c r="B375"/>
       <c r="C375" t="n">
-        <v>-0.00250107448885295</v>
+        <v>-0.00435268224608265</v>
       </c>
       <c r="D375" t="n">
-        <v>-0.00109625583207951</v>
+        <v>-0.000730939866489422</v>
       </c>
       <c r="E375" t="n">
-        <v>0.00234093513540579</v>
-      </c>
-      <c r="F375"/>
+        <v>0.00193098335290465</v>
+      </c>
+      <c r="F375" t="n">
+        <v>0.00193098335290465</v>
+      </c>
       <c r="G375" t="n">
         <v>0.0517628118112174</v>
       </c>
       <c r="H375" t="n">
-        <v>3.41983625671353</v>
+        <v>5.42679652160959</v>
       </c>
     </row>
     <row r="376">
@@ -66128,18 +66067,22 @@
       </c>
       <c r="B376"/>
       <c r="C376" t="n">
-        <v>-0.0112101919402443</v>
+        <v>-0.018783434914746</v>
       </c>
       <c r="D376" t="n">
-        <v>-0.135111056732582</v>
-      </c>
-      <c r="E376"/>
-      <c r="F376"/>
+        <v>-0.134930636671271</v>
+      </c>
+      <c r="E376" t="n">
+        <v>-0.117861667448829</v>
+      </c>
+      <c r="F376" t="n">
+        <v>-0.117861667448829</v>
+      </c>
       <c r="G376" t="n">
         <v>0.348578534605599</v>
       </c>
       <c r="H376" t="n">
-        <v>-4.01681777008795</v>
+        <v>-9.79579796753519</v>
       </c>
     </row>
     <row r="377">
@@ -66147,15 +66090,19 @@
         <v>46113</v>
       </c>
       <c r="B377"/>
-      <c r="C377"/>
-      <c r="D377"/>
+      <c r="C377" t="n">
+        <v>-0.00450150318763942</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0.112664161403271</v>
+      </c>
       <c r="E377"/>
       <c r="F377"/>
       <c r="G377" t="n">
         <v>0.0490430357543703</v>
       </c>
       <c r="H377" t="n">
-        <v>1.83829116399155</v>
+        <v>0.148752484011064</v>
       </c>
     </row>
     <row r="378">
@@ -66168,7 +66115,9 @@
       <c r="E378"/>
       <c r="F378"/>
       <c r="G378"/>
-      <c r="H378"/>
+      <c r="H378" t="n">
+        <v>1.4235574989983</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -72464,10 +72413,10 @@
         <v>46082</v>
       </c>
       <c r="B376" t="n">
-        <v>-11391.0915647095</v>
+        <v>441.4488482867</v>
       </c>
       <c r="C376" t="n">
-        <v>-4387.2998046875</v>
+        <v>-341.59985351562</v>
       </c>
       <c r="D376" t="n">
         <v>0.0727768312778299</v>
@@ -72484,10 +72433,10 @@
         <v>46113</v>
       </c>
       <c r="B377" t="n">
-        <v>0</v>
+        <v>-11832.5404129962</v>
       </c>
       <c r="C377" t="n">
-        <v>0</v>
+        <v>-4045.69995117188</v>
       </c>
       <c r="D377"/>
       <c r="E377"/>
@@ -72497,21 +72446,13 @@
       <c r="A378" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="B378"/>
+      <c r="B378" t="n">
+        <v>0</v>
+      </c>
       <c r="C378"/>
       <c r="D378"/>
       <c r="E378"/>
       <c r="F378"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-      <c r="F379"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -78942,15 +78883,6 @@
         <v>0.0590178730921131</v>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
